--- a/upload/contratos_siad.xlsx
+++ b/upload/contratos_siad.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -669,9 +669,8 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DOS SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, DE FORMA CONTÍNUA,  DAS OBRAS DISCRIMINADAS NO OBJETO CONTRATUAL, RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 24ª CRG DO DER/MG - PASSOS/MG, INCLUÍDOS NO PROGRAMA PLURIANUAL DE AÇÃO GOVERNAMENTAL-PPAG._x000D_
-_x000D_
-PRC-22.018/11_x000D_
+          <t>EXECUÇÃO DOS SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, DE FORMA CONTÍNUA,  DAS OBRAS DISCRIMINADAS NO OBJETO CONTRATUAL, RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 24ª CRG DO DER/MG - PASSOS/MG, INCLUÍDOS NO PROGRAMA PLURIANUAL DE AÇÃO GOVERNAMENTAL-PPAG.
+PRC-22.018/11
 PAVIDEZ</t>
         </is>
       </c>
@@ -814,7 +813,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PRC-22.038/12 _x000D_
+          <t>PRC-22.038/12 
 Execução trabalhos de melhoramento e pavimentação do trecho: ENTRº BR/262 - ENTRº SÃO JOSÉ DO GOIABAL - CAVA GRANDE na Rodovia LMG/760 - MG/320, na extensão de 56,80 km.</t>
         </is>
       </c>
@@ -947,7 +946,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -957,9 +956,8 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-22.024/13 - Serviços de melhoramento e pavimentação do Trecho Caeté - Barão de Cocais, com 24,60km de Extensão, na Rodovia MGC/262._x000D_
-Implantação, pavimentação e restauração com aumento de capacidade no Contorno de Barão de Cocais, com 3,90km de extensão, na Rodovia Contorno._x000D_
-_x000D_
+          <t xml:space="preserve">PRC-22.024/13 - Serviços de melhoramento e pavimentação do Trecho Caeté - Barão de Cocais, com 24,60km de Extensão, na Rodovia MGC/262.
+Implantação, pavimentação e restauração com aumento de capacidade no Contorno de Barão de Cocais, com 3,90km de extensão, na Rodovia Contorno.
 </t>
         </is>
       </c>
@@ -1098,14 +1096,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.021/13 - Execução dos serviços de Apoio aos Trabalhos de Supervisão de Obras Rodoviárias dos Trechos Constantes do LOTE 02, discriminados abaixo: _x000D_
- -  Núcleo  02  e  nos trechos:_x000D_
- Carandaí ¿ Lagoa Dourada (Entrº BR/383) e OAE;_x000D_
- Nazareno ¿ Mercês de Água Limpa e OAE;_x000D_
- Santa Rita de Jacutinga ¿ Divisa MG/RJ;_x000D_
- Itabirito ¿ Rio Acima;_x000D_
- Pedra Bonita ¿ Entrº BR/116 e Variante em Pedra Bonita e OAE;_x000D_
- Ouro Preto (Entrº MG/129) ¿ Distrito de Lavras Novas._x000D_
+          <t xml:space="preserve">PRC-24.021/13 - Execução dos serviços de Apoio aos Trabalhos de Supervisão de Obras Rodoviárias dos Trechos Constantes do LOTE 02, discriminados abaixo: 
+ -  Núcleo  02  e  nos trechos:
+ Carandaí ¿ Lagoa Dourada (Entrº BR/383) e OAE;
+ Nazareno ¿ Mercês de Água Limpa e OAE;
+ Santa Rita de Jacutinga ¿ Divisa MG/RJ;
+ Itabirito ¿ Rio Acima;
+ Pedra Bonita ¿ Entrº BR/116 e Variante em Pedra Bonita e OAE;
+ Ouro Preto (Entrº MG/129) ¿ Distrito de Lavras Novas.
 </t>
         </is>
       </c>
@@ -1244,7 +1242,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.015/13 - Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 04, e  nos trechos:  Água Boa  -  Malacacheta; Entrº BR/262  -  Entrº São José do Goiabal  -  Cava  Grande e OAE; Dores de Guanhães  -  Joanésia (Entrº MG/232); Santa Bárbara  -  São Gonçalo do Rio Abaixo  e  OAE; Bom Jesus do Amparo  -  Nova União; Peçanha  -  Entrº Coroaci._x000D_
+          <t xml:space="preserve">PRC-24.015/13 - Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 04, e  nos trechos:  Água Boa  -  Malacacheta; Entrº BR/262  -  Entrº São José do Goiabal  -  Cava  Grande e OAE; Dores de Guanhães  -  Joanésia (Entrº MG/232); Santa Bárbara  -  São Gonçalo do Rio Abaixo  e  OAE; Bom Jesus do Amparo  -  Nova União; Peçanha  -  Entrº Coroaci.
 </t>
         </is>
       </c>
@@ -1383,9 +1381,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.011/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 07 e  nos trechos: Carmo do Paranaíba (Entrº BR/354)  -  Distrito Quintinos e OAE;  Entrº LMG/690 (Paracatu) - Entrº Entre Ribeiros - Ponte sobre o Rio Paracatu;  Ponte sobre o Rio Paracatu  -  Entrº MG/181  e  OAE;  Arinos (Entrº MGC/479)  -  Riachinho (Entrº MG/181)._x000D_
-_x000D_
-_x000D_
+          <t xml:space="preserve">PRC-24.011/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 07 e  nos trechos: Carmo do Paranaíba (Entrº BR/354)  -  Distrito Quintinos e OAE;  Entrº LMG/690 (Paracatu) - Entrº Entre Ribeiros - Ponte sobre o Rio Paracatu;  Ponte sobre o Rio Paracatu  -  Entrº MG/181  e  OAE;  Arinos (Entrº MGC/479)  -  Riachinho (Entrº MG/181).
 </t>
         </is>
       </c>
@@ -1524,8 +1520,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.008/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do Lote 06 e  nos trechos: Araguari (Entrº BR/050)  -  Entrº BR/365; Campina Verde -  Itapagipe  e OAE; Uberaba (Entrº BR/050)  -  Conceição das Alagoas; Frutal (Entrº BR/364)  -  Garimpo do Bandeira  e Frutal  -  Entrº Fazenda Boa Vista; Iraí de Minas (Entrº LMG/782)  -  Romaria (Entrº BR/365); Perdizes (Entrº BR/452)  -  Entrº BR/262; Serra do Salitre  -  Rio Paranaíba; Contorno Sul de Uberlândia  e OAE;  Conceição das Alagoas  -  Capelinha do Barreiro e Acesso à Poncianos._x000D_
-_x000D_
+          <t xml:space="preserve">PRC-24.008/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do Lote 06 e  nos trechos: Araguari (Entrº BR/050)  -  Entrº BR/365; Campina Verde -  Itapagipe  e OAE; Uberaba (Entrº BR/050)  -  Conceição das Alagoas; Frutal (Entrº BR/364)  -  Garimpo do Bandeira  e Frutal  -  Entrº Fazenda Boa Vista; Iraí de Minas (Entrº LMG/782)  -  Romaria (Entrº BR/365); Perdizes (Entrº BR/452)  -  Entrº BR/262; Serra do Salitre  -  Rio Paranaíba; Contorno Sul de Uberlândia  e OAE;  Conceição das Alagoas  -  Capelinha do Barreiro e Acesso à Poncianos.
 </t>
         </is>
       </c>
@@ -1668,8 +1663,8 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.010/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 01 e  nos trechos: Nova Lima  -  Sabará; Papagaios  -  Entrº BR/352 (Pitangui)  e OAE;  Anel Viário de Sete Lagoas (Av. Norte/Sul -  MG424) e OAE; Esmeraldas -  São José da Varginha;_x000D_
-LMG/800 -  Sete Lagoas; Contorno de Matozinhos e Contorno de Prudente de Morais;  Contorno Norte de Lagoa Santa e OAE; Baldim  -  Santana do Riacho;  Acesso à Inhotim._x000D_
+          <t xml:space="preserve">PRC-24.010/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 01 e  nos trechos: Nova Lima  -  Sabará; Papagaios  -  Entrº BR/352 (Pitangui)  e OAE;  Anel Viário de Sete Lagoas (Av. Norte/Sul -  MG424) e OAE; Esmeraldas -  São José da Varginha;
+LMG/800 -  Sete Lagoas; Contorno de Matozinhos e Contorno de Prudente de Morais;  Contorno Norte de Lagoa Santa e OAE; Baldim  -  Santana do Riacho;  Acesso à Inhotim.
 </t>
         </is>
       </c>
@@ -1808,7 +1803,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC- 24.009/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 03 e  nos trechos: Contorno de Andradas; Entrº LMG/827 (para Bambuí)  -  Entrº MG/341 (para Piumhi); Nova Resende  -  Bom Jesus da Penha; Luz  -  Esteios  -  Lagoa da Prata  e OAE; Pimenta  -  Entrº BR/265 (Guapé) e OAE; Cordislândia  -  Carvalhópolis; Medeiros  -  Pratinha._x000D_
+          <t xml:space="preserve">PRC- 24.009/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 03 e  nos trechos: Contorno de Andradas; Entrº LMG/827 (para Bambuí)  -  Entrº MG/341 (para Piumhi); Nova Resende  -  Bom Jesus da Penha; Luz  -  Esteios  -  Lagoa da Prata  e OAE; Pimenta  -  Entrº BR/265 (Guapé) e OAE; Cordislândia  -  Carvalhópolis; Medeiros  -  Pratinha.
 </t>
         </is>
       </c>
@@ -1951,9 +1946,9 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CONTRATO DP-001/2022 _x000D_
-ELABORAÇÃO DE PROJETO DE ENGENHARIA_x000D_
-RODOVIÁRIA PARA MELHORAMENTO, PAVIMENTAÇÃO E OAE DOS TRECHOS A SEGUIR IDENTIFICADOS:_x000D_
+          <t>CONTRATO DP-001/2022 
+ELABORAÇÃO DE PROJETO DE ENGENHARIA
+RODOVIÁRIA PARA MELHORAMENTO, PAVIMENTAÇÃO E OAE DOS TRECHOS A SEGUIR IDENTIFICADOS:
 RODOVIA - MUNICIPAL; TRECHO: JABUTICATUBAS - LAGOA SANTA, INCLUÍDO NO PPAG .</t>
         </is>
       </c>
@@ -2798,8 +2793,8 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>É objeto do presente contrato, em regime de empreitada, por preços unitários, a_x000D_
-Contratação de empresa de engenharia consultiva para a Elaboração de Projeto de Engenharia Rodoviária para Melhoramento, Pavimentação e OAE dos trechos Araçaí - Sete Lagoas - RodoviaMunicipal_x000D_
+          <t>É objeto do presente contrato, em regime de empreitada, por preços unitários, a
+Contratação de empresa de engenharia consultiva para a Elaboração de Projeto de Engenharia Rodoviária para Melhoramento, Pavimentação e OAE dos trechos Araçaí - Sete Lagoas - RodoviaMunicipal
 , inserida no Programa de Governo "Infraestrutura Rodoviária", cujos quantitati vos encontram-se discriminados na planilha "Quadro de Quanti dades e Preços Unitários", que integra o presente contrato.</t>
         </is>
       </c>
@@ -4342,7 +4337,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Contra to PRC 24.017/2018 _x000D_
+          <t>Contra to PRC 24.017/2018 
 Elaboração de projeto de Engenharia Rodoviária para melhoramentos e Pavimentação do trecho Ipoema - Entr. LMG 776 (Senhora do carmo) na Rodovia Municipal</t>
         </is>
       </c>
@@ -4627,8 +4622,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.005/2018 - Serviços de Apoio à Supervisão da Construção da Ponte sobre o Rio São Francisco com dimensão de 1.120,00m x 13,80m e melhoramento e pavimentação da variante de acesso à Ponte sobre o Rio São Francisco, com 3,060 km de extensão, no trecho São Francisco - Pintópolis, na Rodovia MG/402._x000D_
-_x000D_
+          <t xml:space="preserve">PRC-24.005/2018 - Serviços de Apoio à Supervisão da Construção da Ponte sobre o Rio São Francisco com dimensão de 1.120,00m x 13,80m e melhoramento e pavimentação da variante de acesso à Ponte sobre o Rio São Francisco, com 3,060 km de extensão, no trecho São Francisco - Pintópolis, na Rodovia MG/402.
 </t>
         </is>
       </c>
@@ -6617,7 +6611,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PRC-22.003/2019 - Execução da obra de implantação e pavimentação do Acesso ao Distrito de Jacutinga Estrada Municipal, extensão 640,00 m, na Rodovia Municipal e implantação da interseção no Acesso ao Distrito de Jacutinga Interseção MG/290, extensão 700,00 m. Incluídos no PPAG Plano Plurianual da Ação_x000D_
+          <t>PRC-22.003/2019 - Execução da obra de implantação e pavimentação do Acesso ao Distrito de Jacutinga Estrada Municipal, extensão 640,00 m, na Rodovia Municipal e implantação da interseção no Acesso ao Distrito de Jacutinga Interseção MG/290, extensão 700,00 m. Incluídos no PPAG Plano Plurianual da Ação
 Governamental e contemplados no Programa de Governo Estradas de Minas: Infraestrutura e Logística</t>
         </is>
       </c>
@@ -7324,7 +7318,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-22.015/2020 - Restauração do pavimento da Pista de Pouso e Decolagem, da Taxiways, do Pátio de Aeronave e Execução da nova sinalização horizontal das Taxiways e do Pátio de Aeronaves do Aeroporto de Ipatinga (SBIP), localizado no município de Santana do Paraíso/MG, com extensão de 2.005 m_x000D_
+          <t xml:space="preserve">DC-22.015/2020 - Restauração do pavimento da Pista de Pouso e Decolagem, da Taxiways, do Pátio de Aeronave e Execução da nova sinalização horizontal das Taxiways e do Pátio de Aeronaves do Aeroporto de Ipatinga (SBIP), localizado no município de Santana do Paraíso/MG, com extensão de 2.005 m
 </t>
         </is>
       </c>
@@ -14275,7 +14269,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>DM-031/2021_x000D_
+          <t>DM-031/2021
 Recuperação funcional do pavimento na rodovia MGC-497, no trecho Entrº BR-365/452 (Uberlândia) - Entrº BR-153 (Prata), com 77,60 km de extensão. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 11ª URG do DER/MG ¿ UBERLÂNDIA</t>
         </is>
       </c>
@@ -14844,8 +14838,8 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrato   DC 004/2022_x000D_
-Restauração e Aumento de Capacidade do trecho Três Pontas - Varginha (Estaca 80 a 610) - 10,60 km_x000D_
+          <t xml:space="preserve">contrato   DC 004/2022
+Restauração e Aumento de Capacidade do trecho Três Pontas - Varginha (Estaca 80 a 610) - 10,60 km
 </t>
         </is>
       </c>
@@ -15840,7 +15834,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>DM-033/2022._x000D_
+          <t>DM-033/2022.
 ESTABILIZAÇÃO DE TALUDE DE CORTE (RETALUDAMENTO) NA RODOVIA MG-442, KM 5,0 E 5,4, TRECHO ENTRº BR-040 - BELO VALE. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 01ª URG DO DER/MG ¿ BELO HORIZONTE. INSERIDA NO PROGRAMA DE GOVERNO "INFRAESTRUTURA RODOVIÁRIA", NA AÇÃO ¿RECUPERAÇÃO E MANUTENÇÃO DA MALHA VIÁRIA¿.</t>
         </is>
       </c>
@@ -18945,7 +18939,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>A CONTRATAÇÃO DE EMPRESA DE ENGENHARIA CONSULTIVA PARA A PRESTAÇÃO DE SERVIÇOS DE APOIO_x000D_
+          <t>A CONTRATAÇÃO DE EMPRESA DE ENGENHARIA CONSULTIVA PARA A PRESTAÇÃO DE SERVIÇOS DE APOIO
 TÉCNICO AO DER/MG, NA ÁREA DE PROJETO DE ENGENHARIA RODOVIÁRIA</t>
         </is>
       </c>
@@ -20930,7 +20924,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>DC 015-2022 -A EXECUÇÃO DOS SERVIÇOS DE SINALIZAÇÃO_x000D_
+          <t>DC 015-2022 -A EXECUÇÃO DOS SERVIÇOS DE SINALIZAÇÃO
 HORIZONTAL E VERTICAL DA RODOVIA MGC-259, NO TRECHO SERRO - DATAS (MORRO DO PAIOL), I</t>
         </is>
       </c>
@@ -21641,7 +21635,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>DM-039/2022._x000D_
+          <t>DM-039/2022.
 Recuperação funcional do pavimento na Rodovia AMG-0150, Trecho Entrº MG-030 - Raposos. a execução dos serviços descritos está restrita ao âmbito de Circunscrição da 1ª URG do DER/MG ¿ Belo Horizonte.</t>
         </is>
       </c>
@@ -23744,8 +23738,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CONTRATO DP- 016/2023 - LOTE 10 - DER/DG/LICITAÇÕES _x000D_
-_x000D_
+          <t>CONTRATO DP- 016/2023 - LOTE 10 - DER/DG/LICITAÇÕES 
 -serviços comuns de engenharia para a realização de sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I do Termo de Referência e Anexos.</t>
         </is>
       </c>
@@ -24164,8 +24157,8 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>contratação de serviços comuns de engenharia_x000D_
-para a realização de sondagens SPT e PDL para atender a demanda existente no Departamento de_x000D_
+          <t>contratação de serviços comuns de engenharia
+para a realização de sondagens SPT e PDL para atender a demanda existente no Departamento de
 Edificações e Estradas de Rodagem de Minas Gerais (DER-MG</t>
         </is>
       </c>
@@ -24368,7 +24361,7 @@
         <v>3944409.52</v>
       </c>
       <c r="AR169" t="n">
-        <v>2429927.56</v>
+        <v>2445090.88</v>
       </c>
     </row>
     <row r="170">
@@ -25444,7 +25437,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>DM-022/2023_x000D_
+          <t>DM-022/2023
 Implantação de Variante na Rodovia MGC-383 - km 46, trecho Entre Rios de Minas- Lagoa Dourada. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 4ª URG do DER-MG ¿ Barbacena.</t>
         </is>
       </c>
@@ -25587,8 +25580,8 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Termo Contrato DP 007/2023 - LOTE -01 - DER/DG/LICITAÇÕES _x000D_
-Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de_x000D_
+          <t>Termo Contrato DP 007/2023 - LOTE -01 - DER/DG/LICITAÇÕES 
+Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
 sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I do Termo de Referência e Anexos.</t>
         </is>
       </c>
@@ -25727,10 +25720,10 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>CONTRATO DP- 008/2023- LOTE 02 - DER/DG/LICITAÇÕES -Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de_x000D_
-sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas_x000D_
-de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações_x000D_
-técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I Termo de Referência e_x000D_
+          <t>CONTRATO DP- 008/2023- LOTE 02 - DER/DG/LICITAÇÕES -Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
+sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas
+de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações
+técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I Termo de Referência e
 Anexos.</t>
         </is>
       </c>
@@ -27699,7 +27692,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Contrato: DM-9437231 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES_x000D_
+          <t>Contrato: DM-9437231 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
 Objeto: Execução, em regime de empreitada por preços unitários dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 2ª Unidade Regional Guanhães, do DER-MG.</t>
         </is>
       </c>
@@ -27842,7 +27835,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440657/2024 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES_x000D_
+          <t>Contrato: DM-9440657/2024 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
 Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 11ª Unidade Regional Uberlânida, do DER-MG. Edital 2301762 000008/2024 - LOTE 7.</t>
         </is>
       </c>
@@ -28127,7 +28120,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>DM-9440661/2024_x000D_
+          <t>DM-9440661/2024
 LOTE 9: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 19ª URG - Itajubá</t>
         </is>
       </c>
@@ -28554,7 +28547,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440649/2024 - Empresa: CONSTRUTORA TERRAYAMA LTDA_x000D_
+          <t>Contrato: DM-9440649/2024 - Empresa: CONSTRUTORA TERRAYAMA LTDA
 Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 01ª Unidade Regional Belo Horizonte - Norte, do DER-MG. Edital 2301762 000008/2024 - LOTE 2.</t>
         </is>
       </c>
@@ -29180,7 +29173,7 @@
         <v>44916025.03</v>
       </c>
       <c r="AQ203" t="n">
-        <v>44916025.03</v>
+        <v>43616025.03</v>
       </c>
       <c r="AR203" t="n">
         <v>41553481.03</v>
@@ -29407,7 +29400,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>DM-9440658/2024_x000D_
+          <t>DM-9440658/2024
 LOTE 8: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 15ª URG</t>
         </is>
       </c>
@@ -29465,10 +29458,10 @@
         <v>47005570.55</v>
       </c>
       <c r="AQ205" t="n">
-        <v>28836039.98</v>
+        <v>28236039.98</v>
       </c>
       <c r="AR205" t="n">
-        <v>25496571.6</v>
+        <v>26058069.45</v>
       </c>
     </row>
     <row r="206">
@@ -29550,8 +29543,8 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>Contrato: 9445821/2024_x000D_
-Empresa: ETHOS ENGENHARIA DE INFRAESTRUTURA S/A_x000D_
+          <t>Contrato: 9445821/2024
+Empresa: ETHOS ENGENHARIA DE INFRAESTRUTURA S/A
 Objeto: Recuperação Funcional do Pavimento e Tratamento de Erosões na Rodovia MG-424, trecho Entrº MG-010 - Sete Lagoas, com 50 km de extensão</t>
         </is>
       </c>
@@ -29747,7 +29740,7 @@
         <v>66127329.89</v>
       </c>
       <c r="AQ207" t="n">
-        <v>35164106.01</v>
+        <v>34764106.01</v>
       </c>
       <c r="AR207" t="n">
         <v>32074743.87</v>
@@ -30388,7 +30381,7 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>DM-9440654/2024_x000D_
+          <t>DM-9440654/2024
 LOTE 5: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 9ª URG - Curvelo.</t>
         </is>
       </c>
@@ -30673,7 +30666,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>DM-9440650/2024_x000D_
+          <t>DM-9440650/2024
 LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 5ª Unidade Regional Ubá, do DER-MG. Edital nº: 2301762 00008/2024. Processo nº: 2300.01.0094168/2024-52</t>
         </is>
       </c>
@@ -31299,7 +31292,7 @@
         <v>49131721.25</v>
       </c>
       <c r="AQ218" t="n">
-        <v>30686287.07</v>
+        <v>29186287.07</v>
       </c>
       <c r="AR218" t="n">
         <v>28199966.48</v>
@@ -33222,7 +33215,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>Contrato: 9445781/2024 - Empresa: PAVIDEZ ENGENHARIA LTDA_x000D_
+          <t>Contrato: 9445781/2024 - Empresa: PAVIDEZ ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia LMG-886, Trecho: Final do Per. Urbano de Monte Verde - Início do Per. Urbano de Camanducaia, com 28,60 km de extensão</t>
         </is>
       </c>
@@ -33365,8 +33358,8 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Contrato: DM-9447057/2024_x000D_
-Empresa: PAVIDEZ ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9447057/2024
+Empresa: PAVIDEZ ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia MG-347, no trecho Entrº BR-460 (Carmo de Minas) Entrº p/ Cristina, com 17,60 km de extensão.</t>
         </is>
       </c>
@@ -34491,7 +34484,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440647/2024 - Empresa: SEISAN ENGENHARIA E CONSTRUÇÕES LTDA_x000D_
+          <t>Contrato: DM-9440647/2024 - Empresa: SEISAN ENGENHARIA E CONSTRUÇÕES LTDA
 Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 1ª Unidade Regional Belo Horizonte - Sul, do DER-MG. Edital 2301762 000008/2024 - LOTE 1.</t>
         </is>
       </c>
@@ -34914,8 +34907,8 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 01 MG-050: Concessão PATROCINADA. Rodovia MG-050: km 57,60 no entr. BR-262 (Juatuba) ao km 402,00 no entr. BR-491 (São Sebastião do Paraíso);_x000D_
-Rodovia BR-491: km 0,00 no entr. MG-050 (São Sebastião do Paraíso) ao km 4,65 no entr. BR-265;_x000D_
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 01 MG-050: Concessão PATROCINADA. Rodovia MG-050: km 57,60 no entr. BR-262 (Juatuba) ao km 402,00 no entr. BR-491 (São Sebastião do Paraíso);
+Rodovia BR-491: km 0,00 no entr. MG-050 (São Sebastião do Paraíso) ao km 4,65 no entr. BR-265;
 Rodovia BR-265: km 637,20 no entr. BR-491 ao km 659,50 na divisa MG/SP.</t>
         </is>
       </c>
@@ -35058,12 +35051,12 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 02 Vias do Café: Concessão Outorgada, com 432,80 km:_x000D_
-Rodovia MG-167: km 0,00 no entr. BR-265 (Santana da Vargem) ao km 43,80 no entr. CMG-491 (Varginha);_x000D_
-Rodovia BR-265: km 338,40 no entr. BR-381 (Lavras) ao km 403,00 no entr. LMG-863 (Boa Esperança);_x000D_
-Rodovia LMG-863: km 0,00 ao km 5,00 no entr. BR-265 (Boa Esperança);_x000D_
-Rodovia CMG-491: km 4,65 no entr. CMG-265 (São Sebastião do Paraíso) ao km 81,05 no entr. BR-146-A/MG-450 (Guaxupé) e entre o km 108,25 no entr. BR-146-B (Muzambinho) ao km 259,95 no entr. BR-381 (Três Corações);_x000D_
-Rodovia BR-146: km 505,30 no entr. CMG-491 (Guaxupé) ao km 532,50 no entr. CMG-491 (Muzambinho);_x000D_
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 02 Vias do Café: Concessão Outorgada, com 432,80 km:
+Rodovia MG-167: km 0,00 no entr. BR-265 (Santana da Vargem) ao km 43,80 no entr. CMG-491 (Varginha);
+Rodovia BR-265: km 338,40 no entr. BR-381 (Lavras) ao km 403,00 no entr. LMG-863 (Boa Esperança);
+Rodovia LMG-863: km 0,00 ao km 5,00 no entr. BR-265 (Boa Esperança);
+Rodovia CMG-491: km 4,65 no entr. CMG-265 (São Sebastião do Paraíso) ao km 81,05 no entr. BR-146-A/MG-450 (Guaxupé) e entre o km 108,25 no entr. BR-146-B (Muzambinho) ao km 259,95 no entr. BR-381 (Três Corações);
+Rodovia BR-146: km 505,30 no entr. CMG-491 (Guaxupé) ao km 532,50 no entr. CMG-491 (Muzambinho);
 Rodovia CMG-369: km 124,40 no entr. BR-265 (Boa Esperança) ao km 188,50 no entr. CMG-491 (Alfenas).</t>
         </is>
       </c>
@@ -35206,7 +35199,7 @@
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>DM-9471880/2025_x000D_
+          <t>DM-9471880/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 26ª Unidade Regional Paracatu</t>
         </is>
       </c>
@@ -35633,7 +35626,7 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>DM-9471835/2025_x000D_
+          <t>DM-9471835/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 34ª Unidade Regional Salinas, do DER-MG.</t>
         </is>
       </c>
@@ -35691,7 +35684,7 @@
         <v>44573000</v>
       </c>
       <c r="AQ249" t="n">
-        <v>6828453.93</v>
+        <v>6351337.93</v>
       </c>
       <c r="AR249" t="n">
         <v>5198379.09</v>
@@ -35776,7 +35769,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>DM-9471881/2025_x000D_
+          <t>DM-9471881/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 30ª Unidade Regional Juiz de Fora, do DER-MG.</t>
         </is>
       </c>
@@ -35834,7 +35827,7 @@
         <v>53358800</v>
       </c>
       <c r="AQ250" t="n">
-        <v>18336026.7</v>
+        <v>16336026.7</v>
       </c>
       <c r="AR250" t="n">
         <v>12226202.87</v>
@@ -35919,10 +35912,10 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 5: Contratação de empresa para a_x000D_
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos_x000D_
-equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 02ª, 08ª, 21ª, 22ª, 23ª, 27ª, 28ª, 34ª e 38ª_x000D_
-URGs do DER-MG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e_x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 5: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
+equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 02ª, 08ª, 21ª, 22ª, 23ª, 27ª, 28ª, 34ª e 38ª
+URGs do DER-MG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e
 seus anexos.</t>
         </is>
       </c>
@@ -36065,8 +36058,8 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio_x000D_
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 2: Contratação de empresa para aprestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dosequipamentos fixos de fiscalização eletrônica abrangendo os trechos das 04ª, 10ª, 15ª, 19ª e 30ª URGs do DERMG._x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 2: Contratação de empresa para aprestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dosequipamentos fixos de fiscalização eletrônica abrangendo os trechos das 04ª, 10ª, 15ª, 19ª e 30ª URGs do DERMG.
 Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
@@ -36489,8 +36482,8 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de instalação, sinalização,_x000D_
-aferição,operação, monitoramento e manutenção dos equipamentos fi xos de fi scalização_x000D_
+          <t>Contratação de empresa para a prestação de serviços de instalação, sinalização,
+aferição,operação, monitoramento e manutenção dos equipamentos fi xos de fi scalização
 eletrônicaabrangendo os trechos das 07ª, 11ª, 14ª, 18ª, 24ª, 25ª, 26ª e 31ª URGs do DER-MG</t>
         </is>
       </c>
@@ -36775,7 +36768,7 @@
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>DM-9473163/2025_x000D_
+          <t>DM-9473163/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 29ª Unidade Regional Manhumirim, do DER-MG.</t>
         </is>
       </c>
@@ -36918,8 +36911,8 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>Contrato: DM-9485592/2025_x000D_
-Empresa: HWN ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9485592/2025
+Empresa: HWN ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia AMG - 1705 - Trecho: Santa Cruz do Escalvado - Entr° MG 329 , com 17,30 km de extensão.</t>
         </is>
       </c>
@@ -37062,8 +37055,8 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>Contrato: DM-9485591/2025_x000D_
-Empresa: HWN ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9485591/2025
+Empresa: HWN ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia: LMG-845 - Trecho: Sericita - Entr° 262, com 19,00 km de extensão.</t>
         </is>
       </c>
@@ -37206,8 +37199,8 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>Contrato: DM-9459013/2025_x000D_
-Empresa: HWN ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9459013/2025
+Empresa: HWN ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia MG-188, no Trecho Guarda-Mor a Coromandel, com 92,50 km de extensão.</t>
         </is>
       </c>
@@ -37265,7 +37258,7 @@
         <v>52239647.93</v>
       </c>
       <c r="AQ260" t="n">
-        <v>41536496.54</v>
+        <v>39171496.54</v>
       </c>
       <c r="AR260" t="n">
         <v>37883322.64</v>
@@ -37350,8 +37343,8 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Contrato: DM-9492723/2025_x000D_
-Empresa: HWN ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9492723/2025
+Empresa: HWN ENGENHARIA LTDA
 Objeto: Recuperação do Pavimento na Rodovia: MGC-452, trecho: Tupaciguara - Araporã, com 59,00 Km de extensão.</t>
         </is>
       </c>
@@ -37409,7 +37402,7 @@
         <v>41984578.11</v>
       </c>
       <c r="AQ261" t="n">
-        <v>26033213.8</v>
+        <v>23668213.8</v>
       </c>
       <c r="AR261" t="n">
         <v>22075692.06</v>
@@ -37636,7 +37629,7 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>DM-9471834/2025_x000D_
+          <t>DM-9471834/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 31ª Unidade Regional Ituiutaba, do DER-MG.</t>
         </is>
       </c>
@@ -37694,7 +37687,7 @@
         <v>50960749.38</v>
       </c>
       <c r="AQ263" t="n">
-        <v>10062963.81</v>
+        <v>8062963.81</v>
       </c>
       <c r="AR263" t="n">
         <v>5930572.79</v>
@@ -37779,7 +37772,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>DM-9471830/2025_x000D_
+          <t>DM-9471830/2025
 LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 20ª Unidade Regional Formiga, do DER-MG. Processo nº: 2300.01.0120269/2025-27</t>
         </is>
       </c>
@@ -37837,7 +37830,7 @@
         <v>53573999.99</v>
       </c>
       <c r="AQ264" t="n">
-        <v>12835313.79</v>
+        <v>10112429.79</v>
       </c>
       <c r="AR264" t="n">
         <v>7795111</v>
@@ -37922,7 +37915,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>DM-9471879/2025_x000D_
+          <t>DM-9471879/2025
 Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 18ª Unidade Regional Monte Carmelo, do DER-MG.</t>
         </is>
       </c>
@@ -38207,7 +38200,7 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>DM-9471832/2025_x000D_
+          <t>DM-9471832/2025
 LOTE 4: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 24ª Unidade Regional Passos, do DER-MG.</t>
         </is>
       </c>
@@ -38350,8 +38343,8 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>Contrato: DM-9453530/2025_x000D_
-Empresa: PAVIDEZ ENGENHARIA LTDA_x000D_
+          <t>Contrato: DM-9453530/2025
+Empresa: PAVIDEZ ENGENHARIA LTDA
 Objeto: Recuperação Funcional do Pavimento na Rodovia AMG-1615, no trecho Cristais - Entrº MGC-369, extensão de 11,70 km.</t>
         </is>
       </c>
@@ -38920,11 +38913,11 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para_x000D_
-apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para_x000D_
-detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio_x000D_
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a_x000D_
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos_x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
+apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
+detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
 equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 01ª, 03ª, 16ª, 20ª e 35ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
@@ -39067,11 +39060,11 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para_x000D_
-apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para_x000D_
-detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio_x000D_
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a_x000D_
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos_x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
+apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
+detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
 equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 01ª, 03ª, 16ª, 20ª e 35ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
@@ -39356,7 +39349,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 5: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 01ª URG - Belo Horizonte, 02ª URG ¿_x000D_
+          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 5: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 01ª URG - Belo Horizonte, 02ª URG ¿
 Guanhães, 03ª URG - Pará de Minas, 08ª URG ¿ Diamantina, 09ª URG - Curvelo, 12ª URG ¿ Itabira, 35ª URG ¿ Abaeté e 38ª URG ¿ Capelinha.</t>
         </is>
       </c>
@@ -39499,7 +39492,7 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 6: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos_x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 6: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
 equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 05ª, 12ª, 17ª, 29ª e 40ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
@@ -39926,8 +39919,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão Geral, Monitoramento dos Parâmetros de Desempenho, Avaliação e Análise de Projetos, da exploração mediante Concessão, dos trechos rodoviários abaixo descritos, conforme especificações, exigências e quantidades estabelecidas._x000D_
-_x000D_
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão Geral, Monitoramento dos Parâmetros de Desempenho, Avaliação e Análise de Projetos, da exploração mediante Concessão, dos trechos rodoviários abaixo descritos, conforme especificações, exigências e quantidades estabelecidas.
 BR-135: Concessão OUTORGADA, com 374,95 km.</t>
         </is>
       </c>
@@ -40070,8 +40062,8 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Contrato: DM-9493202/2026_x000D_
-Empresa: AGR Botelho Engenharia Ltda_x000D_
+          <t>Contrato: DM-9493202/2026
+Empresa: AGR Botelho Engenharia Ltda
 Objeto: Recuperação de erosões na MG-406, Km 118,9/120,9/123/123,3/132,4, trecho: Palmópolis - Rio do Prado e Estabilização de aterro de encabeçamento de ponte na MG-205, ponte sobre o Ribeirão José Ferreira.</t>
         </is>
       </c>
@@ -40214,8 +40206,8 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>CONTRATO: DM-9493180/2026_x000D_
-EMPRESA: Construtora Sagendra Ltda_x000D_
+          <t>CONTRATO: DM-9493180/2026
+EMPRESA: Construtora Sagendra Ltda
 OBJETO: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 17ª Unidade Regional Ponte Nova, do DER-MG.</t>
         </is>
       </c>
@@ -40358,7 +40350,7 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 4: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 06ª, 09ª, 13ª, 32ª, 33ª, 36ª, 37ª e 39ª_x000D_
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 4: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 06ª, 09ª, 13ª, 32ª, 33ª, 36ª, 37ª e 39ª
 URGs do DER-MG. Incluso no PPAG.</t>
         </is>
       </c>
@@ -40781,8 +40773,8 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apoio a Supervisão de Obras Rodoviárias da Rodovia MG402, da Complementação_x000D_
-da Construção da Ponte sobre o Rio São Francisco, dimensões 1.120,00x13,80 m, no trecho São Francisco Pintópolis, e Complementação das obras de Melhoramento e Pavimentação de Variante de acesso à Ponte sobre o Rio São Francisco, com 3,06 km, no trecho São Francisco Pintópolis._x000D_
+          <t xml:space="preserve"> Apoio a Supervisão de Obras Rodoviárias da Rodovia MG402, da Complementação
+da Construção da Ponte sobre o Rio São Francisco, dimensões 1.120,00x13,80 m, no trecho São Francisco Pintópolis, e Complementação das obras de Melhoramento e Pavimentação de Variante de acesso à Ponte sobre o Rio São Francisco, com 3,06 km, no trecho São Francisco Pintópolis.
 </t>
         </is>
       </c>
@@ -40925,8 +40917,8 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Contrato: DM-9502116/2026_x000D_
-Empresa: PLANEP Planejamento e Estudos e Projetos Ltda_x000D_
+          <t>Contrato: DM-9502116/2026
+Empresa: PLANEP Planejamento e Estudos e Projetos Ltda
 Objeto: Prestação de serviços de Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional gerenciados pela Diretoria de Manutenção.</t>
         </is>
       </c>

--- a/upload/contratos_siad.xlsx
+++ b/upload/contratos_siad.xlsx
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-C</t>
+          <t>PRC-22.032/2017-B</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-D</t>
+          <t>PRC-22.032/2017-C</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-E</t>
+          <t>PRC-22.032/2017-D</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PRC-22.032/2017-B</t>
+          <t>PRC-22.032/2017-E</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-D</t>
+          <t>PRC-22.013/2018-B</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-E</t>
+          <t>PRC-22.013/2018-C</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-B</t>
+          <t>PRC-22.013/2018-D</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PRC-22.013/2018-C</t>
+          <t>PRC-22.013/2018-E</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -20558,7 +20558,7 @@
         <v>36226043.57</v>
       </c>
       <c r="AR142" t="n">
-        <v>32252258.61</v>
+        <v>33309671.76</v>
       </c>
     </row>
     <row r="143">
@@ -20700,7 +20700,7 @@
         <v>36226043.57</v>
       </c>
       <c r="AR143" t="n">
-        <v>32252258.61</v>
+        <v>33309671.76</v>
       </c>
     </row>
     <row r="144">
@@ -20842,7 +20842,7 @@
         <v>36226043.57</v>
       </c>
       <c r="AR144" t="n">
-        <v>32252258.61</v>
+        <v>33309671.76</v>
       </c>
     </row>
     <row r="145">
@@ -21127,7 +21127,7 @@
         <v>37262388.96</v>
       </c>
       <c r="AR146" t="n">
-        <v>31572208.14</v>
+        <v>32692410.09</v>
       </c>
     </row>
     <row r="147">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -21269,7 +21269,7 @@
         <v>37262388.96</v>
       </c>
       <c r="AR147" t="n">
-        <v>31572208.14</v>
+        <v>32692410.09</v>
       </c>
     </row>
     <row r="148">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -21411,7 +21411,7 @@
         <v>37262388.96</v>
       </c>
       <c r="AR148" t="n">
-        <v>31572208.14</v>
+        <v>32692410.09</v>
       </c>
     </row>
     <row r="149">
@@ -22122,7 +22122,7 @@
         <v>9934256.32</v>
       </c>
       <c r="AR153" t="n">
-        <v>5596490.06</v>
+        <v>9066774.59</v>
       </c>
     </row>
     <row r="154">
@@ -26474,7 +26474,7 @@
         <v>14934015.08</v>
       </c>
       <c r="AR184" t="n">
-        <v>13122882.82</v>
+        <v>13283422.44</v>
       </c>
     </row>
     <row r="185">
@@ -26613,7 +26613,7 @@
         <v>80307166.26000001</v>
       </c>
       <c r="AQ185" t="n">
-        <v>31643599.2</v>
+        <v>32071599.2</v>
       </c>
       <c r="AR185" t="n">
         <v>29288803.54</v>
@@ -26755,7 +26755,7 @@
         <v>80307166.26000001</v>
       </c>
       <c r="AQ186" t="n">
-        <v>31643599.2</v>
+        <v>32071599.2</v>
       </c>
       <c r="AR186" t="n">
         <v>29288803.54</v>
@@ -26897,7 +26897,7 @@
         <v>63836492.6</v>
       </c>
       <c r="AQ187" t="n">
-        <v>32374693.01</v>
+        <v>33404237.55</v>
       </c>
       <c r="AR187" t="n">
         <v>30267701.8</v>
@@ -27039,7 +27039,7 @@
         <v>63836492.6</v>
       </c>
       <c r="AQ188" t="n">
-        <v>32374693.01</v>
+        <v>33404237.55</v>
       </c>
       <c r="AR188" t="n">
         <v>30267701.8</v>
@@ -27181,7 +27181,7 @@
         <v>61251552.99</v>
       </c>
       <c r="AQ189" t="n">
-        <v>22945392.67</v>
+        <v>23099392.67</v>
       </c>
       <c r="AR189" t="n">
         <v>22209094.15</v>
@@ -27323,7 +27323,7 @@
         <v>61251552.99</v>
       </c>
       <c r="AQ190" t="n">
-        <v>22945392.67</v>
+        <v>23099392.67</v>
       </c>
       <c r="AR190" t="n">
         <v>22209094.15</v>
@@ -27465,7 +27465,7 @@
         <v>61251552.99</v>
       </c>
       <c r="AQ191" t="n">
-        <v>22945392.67</v>
+        <v>23099392.67</v>
       </c>
       <c r="AR191" t="n">
         <v>22209094.15</v>
@@ -27607,7 +27607,7 @@
         <v>29912995.31</v>
       </c>
       <c r="AQ192" t="n">
-        <v>29912994.46</v>
+        <v>26797830.61</v>
       </c>
       <c r="AR192" t="n">
         <v>26797830.61</v>
@@ -27747,10 +27747,10 @@
         </is>
       </c>
       <c r="AP193" t="n">
-        <v>52662607.4</v>
+        <v>52694394.72</v>
       </c>
       <c r="AQ193" t="n">
-        <v>47487781.22</v>
+        <v>48335460.12</v>
       </c>
       <c r="AR193" t="n">
         <v>44361494.24</v>
@@ -27893,7 +27893,7 @@
         <v>47634588.04</v>
       </c>
       <c r="AQ194" t="n">
-        <v>33948471.9</v>
+        <v>34727471.9</v>
       </c>
       <c r="AR194" t="n">
         <v>33369920.69</v>
@@ -28178,7 +28178,7 @@
         <v>50062054.28</v>
       </c>
       <c r="AQ196" t="n">
-        <v>29465954.37</v>
+        <v>29806954.37</v>
       </c>
       <c r="AR196" t="n">
         <v>28894601.15</v>
@@ -28320,10 +28320,10 @@
         <v>74107976.59999999</v>
       </c>
       <c r="AQ197" t="n">
-        <v>34556777.17</v>
+        <v>35558777.17</v>
       </c>
       <c r="AR197" t="n">
-        <v>34336741.94</v>
+        <v>35558300.42</v>
       </c>
     </row>
     <row r="198">
@@ -28462,10 +28462,10 @@
         <v>74107976.59999999</v>
       </c>
       <c r="AQ198" t="n">
-        <v>34556777.17</v>
+        <v>35558777.17</v>
       </c>
       <c r="AR198" t="n">
-        <v>34336741.94</v>
+        <v>35558300.42</v>
       </c>
     </row>
     <row r="199">
@@ -28605,7 +28605,7 @@
         <v>47758833.23</v>
       </c>
       <c r="AQ199" t="n">
-        <v>32778044.78</v>
+        <v>32716263.85</v>
       </c>
       <c r="AR199" t="n">
         <v>32591495.13</v>
@@ -28812,7 +28812,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-012/2024</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -28889,10 +28889,10 @@
         <v>59018711.64</v>
       </c>
       <c r="AQ201" t="n">
-        <v>26937657.34</v>
+        <v>26815269.59</v>
       </c>
       <c r="AR201" t="n">
-        <v>24813709.58</v>
+        <v>26335112.82</v>
       </c>
     </row>
     <row r="202">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>DM-012/2024</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -29031,10 +29031,10 @@
         <v>59018711.64</v>
       </c>
       <c r="AQ202" t="n">
-        <v>26937657.34</v>
+        <v>26815269.59</v>
       </c>
       <c r="AR202" t="n">
-        <v>24813709.58</v>
+        <v>26335112.82</v>
       </c>
     </row>
     <row r="203">
@@ -29173,7 +29173,7 @@
         <v>44916025.03</v>
       </c>
       <c r="AQ203" t="n">
-        <v>43616025.03</v>
+        <v>43774025.03</v>
       </c>
       <c r="AR203" t="n">
         <v>41553481.03</v>
@@ -29315,7 +29315,7 @@
         <v>33721624.27</v>
       </c>
       <c r="AQ204" t="n">
-        <v>21233744.35</v>
+        <v>21518766.52</v>
       </c>
       <c r="AR204" t="n">
         <v>20363121.77</v>
@@ -29458,7 +29458,7 @@
         <v>47005570.55</v>
       </c>
       <c r="AQ205" t="n">
-        <v>28236039.98</v>
+        <v>28902039.98</v>
       </c>
       <c r="AR205" t="n">
         <v>26058069.45</v>
@@ -29740,7 +29740,7 @@
         <v>66127329.89</v>
       </c>
       <c r="AQ207" t="n">
-        <v>34764106.01</v>
+        <v>35648106.01</v>
       </c>
       <c r="AR207" t="n">
         <v>32074743.87</v>
@@ -30020,7 +30020,7 @@
         <v>1000000</v>
       </c>
       <c r="AQ209" t="n">
-        <v>167867.01</v>
+        <v>131764.82</v>
       </c>
       <c r="AR209" t="n">
         <v>131764.82</v>
@@ -30158,7 +30158,7 @@
         <v>1100000</v>
       </c>
       <c r="AQ210" t="n">
-        <v>441279.76</v>
+        <v>421279.76</v>
       </c>
       <c r="AR210" t="n">
         <v>421279.76</v>
@@ -30296,7 +30296,7 @@
         <v>1224000</v>
       </c>
       <c r="AQ211" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AR211" t="n">
         <v>0</v>
@@ -30439,7 +30439,7 @@
         <v>48158605.21</v>
       </c>
       <c r="AQ212" t="n">
-        <v>32480321.71</v>
+        <v>32461139.42</v>
       </c>
       <c r="AR212" t="n">
         <v>32153234.58</v>
@@ -30866,10 +30866,10 @@
         <v>65019900.51</v>
       </c>
       <c r="AQ215" t="n">
-        <v>37139150.09</v>
+        <v>37513150.09</v>
       </c>
       <c r="AR215" t="n">
-        <v>31256867.19</v>
+        <v>33297386.61</v>
       </c>
     </row>
     <row r="216">
@@ -31008,10 +31008,10 @@
         <v>65019900.51</v>
       </c>
       <c r="AQ216" t="n">
-        <v>37139150.09</v>
+        <v>37513150.09</v>
       </c>
       <c r="AR216" t="n">
-        <v>31256867.19</v>
+        <v>33297386.61</v>
       </c>
     </row>
     <row r="217">
@@ -31292,7 +31292,7 @@
         <v>49131721.25</v>
       </c>
       <c r="AQ218" t="n">
-        <v>29186287.07</v>
+        <v>28201287.07</v>
       </c>
       <c r="AR218" t="n">
         <v>28199966.48</v>
@@ -31434,10 +31434,10 @@
         <v>76784767.68000001</v>
       </c>
       <c r="AQ219" t="n">
-        <v>40061689.32</v>
+        <v>46633450.4</v>
       </c>
       <c r="AR219" t="n">
-        <v>39314315.02</v>
+        <v>39329098.76</v>
       </c>
     </row>
     <row r="220">
@@ -31576,10 +31576,10 @@
         <v>76784767.68000001</v>
       </c>
       <c r="AQ220" t="n">
-        <v>40061689.32</v>
+        <v>46633450.4</v>
       </c>
       <c r="AR220" t="n">
-        <v>39314315.02</v>
+        <v>39329098.76</v>
       </c>
     </row>
     <row r="221">
@@ -31718,7 +31718,7 @@
         <v>37050167.95</v>
       </c>
       <c r="AQ221" t="n">
-        <v>35528221.55</v>
+        <v>36687589.24</v>
       </c>
       <c r="AR221" t="n">
         <v>34348802.25</v>
@@ -31860,7 +31860,7 @@
         <v>37050167.95</v>
       </c>
       <c r="AQ222" t="n">
-        <v>35528221.55</v>
+        <v>36687589.24</v>
       </c>
       <c r="AR222" t="n">
         <v>34348802.25</v>
@@ -32144,7 +32144,7 @@
         <v>66684490.34</v>
       </c>
       <c r="AQ224" t="n">
-        <v>23888614.98</v>
+        <v>24210614.98</v>
       </c>
       <c r="AR224" t="n">
         <v>23789762.18</v>
@@ -32286,7 +32286,7 @@
         <v>66684490.34</v>
       </c>
       <c r="AQ225" t="n">
-        <v>23888614.98</v>
+        <v>24210614.98</v>
       </c>
       <c r="AR225" t="n">
         <v>23789762.18</v>
@@ -32428,10 +32428,10 @@
         <v>51333755.33</v>
       </c>
       <c r="AQ226" t="n">
-        <v>27177270.16</v>
+        <v>27932835.16</v>
       </c>
       <c r="AR226" t="n">
-        <v>27134948.8</v>
+        <v>27931835.24</v>
       </c>
     </row>
     <row r="227">
@@ -32570,7 +32570,7 @@
         <v>74261373.36</v>
       </c>
       <c r="AQ227" t="n">
-        <v>36008380.49</v>
+        <v>37087380.49</v>
       </c>
       <c r="AR227" t="n">
         <v>35940756.74</v>
@@ -32712,7 +32712,7 @@
         <v>74261373.36</v>
       </c>
       <c r="AQ228" t="n">
-        <v>36008380.49</v>
+        <v>37087380.49</v>
       </c>
       <c r="AR228" t="n">
         <v>35940756.74</v>
@@ -32787,7 +32787,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -32991,7 +32991,7 @@
         <v>65669404.68</v>
       </c>
       <c r="AR230" t="n">
-        <v>57166116.31</v>
+        <v>62871375.98</v>
       </c>
     </row>
     <row r="231">
@@ -33130,7 +33130,7 @@
         <v>45768946.45</v>
       </c>
       <c r="AQ231" t="n">
-        <v>23163920.2</v>
+        <v>23736159.27</v>
       </c>
       <c r="AR231" t="n">
         <v>22375853.15</v>
@@ -33701,10 +33701,10 @@
         <v>42788655.89</v>
       </c>
       <c r="AQ235" t="n">
-        <v>31277837.24</v>
+        <v>33119572.24</v>
       </c>
       <c r="AR235" t="n">
-        <v>30858295.1</v>
+        <v>33118572.64</v>
       </c>
     </row>
     <row r="236">
@@ -33843,10 +33843,10 @@
         <v>42788655.89</v>
       </c>
       <c r="AQ236" t="n">
-        <v>31277837.24</v>
+        <v>33119572.24</v>
       </c>
       <c r="AR236" t="n">
-        <v>30858295.1</v>
+        <v>33118572.64</v>
       </c>
     </row>
     <row r="237">
@@ -34119,7 +34119,7 @@
         <v>1247750</v>
       </c>
       <c r="AQ238" t="n">
-        <v>807537.27</v>
+        <v>787537.27</v>
       </c>
       <c r="AR238" t="n">
         <v>787537.27</v>
@@ -34257,7 +34257,7 @@
         <v>1244600</v>
       </c>
       <c r="AQ239" t="n">
-        <v>201298.47</v>
+        <v>166388.81</v>
       </c>
       <c r="AR239" t="n">
         <v>166388.81</v>
@@ -34542,7 +34542,7 @@
         <v>47556790.26</v>
       </c>
       <c r="AQ241" t="n">
-        <v>34704096.52</v>
+        <v>34676037.57</v>
       </c>
       <c r="AR241" t="n">
         <v>34445238.35</v>
@@ -34680,7 +34680,7 @@
         <v>797999.85</v>
       </c>
       <c r="AQ242" t="n">
-        <v>487778.27</v>
+        <v>428070.96</v>
       </c>
       <c r="AR242" t="n">
         <v>428070.96</v>
@@ -35257,7 +35257,7 @@
         <v>51814575.44</v>
       </c>
       <c r="AQ246" t="n">
-        <v>9606369.130000001</v>
+        <v>10462369.13</v>
       </c>
       <c r="AR246" t="n">
         <v>7703559.16</v>
@@ -35541,7 +35541,7 @@
         <v>29717994.42</v>
       </c>
       <c r="AQ248" t="n">
-        <v>29634826.73</v>
+        <v>27434826.73</v>
       </c>
       <c r="AR248" t="n">
         <v>16632566.89</v>
@@ -35684,7 +35684,7 @@
         <v>44573000</v>
       </c>
       <c r="AQ249" t="n">
-        <v>6351337.93</v>
+        <v>5821337.93</v>
       </c>
       <c r="AR249" t="n">
         <v>5198379.09</v>
@@ -35827,7 +35827,7 @@
         <v>53358800</v>
       </c>
       <c r="AQ250" t="n">
-        <v>16336026.7</v>
+        <v>15689188.17</v>
       </c>
       <c r="AR250" t="n">
         <v>12226202.87</v>
@@ -36259,7 +36259,7 @@
         <v>45918998.95</v>
       </c>
       <c r="AQ253" t="n">
-        <v>15639477.54</v>
+        <v>13205099.01</v>
       </c>
       <c r="AR253" t="n">
         <v>3970214.87</v>
@@ -36826,7 +36826,7 @@
         <v>59299394.97</v>
       </c>
       <c r="AQ257" t="n">
-        <v>27385744.23</v>
+        <v>33169918.01</v>
       </c>
       <c r="AR257" t="n">
         <v>26777072.2</v>
@@ -36970,7 +36970,7 @@
         <v>10929975.56</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1015369.35</v>
+        <v>1107834.98</v>
       </c>
       <c r="AR258" t="n">
         <v>405673.71</v>
@@ -37114,7 +37114,7 @@
         <v>6199729.76</v>
       </c>
       <c r="AQ259" t="n">
-        <v>3131274.11</v>
+        <v>2578424.04</v>
       </c>
       <c r="AR259" t="n">
         <v>2369404.54</v>
@@ -37258,7 +37258,7 @@
         <v>52239647.93</v>
       </c>
       <c r="AQ260" t="n">
-        <v>39171496.54</v>
+        <v>49484496.54</v>
       </c>
       <c r="AR260" t="n">
         <v>37883322.64</v>
@@ -37402,7 +37402,7 @@
         <v>41984578.11</v>
       </c>
       <c r="AQ261" t="n">
-        <v>23668213.8</v>
+        <v>30683880.42</v>
       </c>
       <c r="AR261" t="n">
         <v>22075692.06</v>
@@ -37687,10 +37687,10 @@
         <v>50960749.38</v>
       </c>
       <c r="AQ263" t="n">
-        <v>8062963.81</v>
+        <v>7583539.81</v>
       </c>
       <c r="AR263" t="n">
-        <v>5930572.79</v>
+        <v>6623750.95</v>
       </c>
     </row>
     <row r="264">
@@ -37973,7 +37973,7 @@
         <v>53241874.38</v>
       </c>
       <c r="AQ265" t="n">
-        <v>15301311</v>
+        <v>15680311</v>
       </c>
       <c r="AR265" t="n">
         <v>13759262.25</v>
@@ -38258,7 +38258,7 @@
         <v>49093539.45</v>
       </c>
       <c r="AQ267" t="n">
-        <v>7298182.42</v>
+        <v>7052723.42</v>
       </c>
       <c r="AR267" t="n">
         <v>5774272.98</v>
@@ -38402,10 +38402,10 @@
         <v>7109673.15</v>
       </c>
       <c r="AQ268" t="n">
-        <v>3081629.3</v>
+        <v>4452559.37</v>
       </c>
       <c r="AR268" t="n">
-        <v>2382394.83</v>
+        <v>4309693.56</v>
       </c>
     </row>
     <row r="269">
@@ -38689,7 +38689,7 @@
         <v>1396977.52</v>
       </c>
       <c r="AR270" t="n">
-        <v>50664.73</v>
+        <v>243707.59</v>
       </c>
     </row>
     <row r="271">
@@ -38831,7 +38831,7 @@
         <v>3186565.34</v>
       </c>
       <c r="AR271" t="n">
-        <v>1586687.32</v>
+        <v>1933519.48</v>
       </c>
     </row>
     <row r="272">
@@ -38978,7 +38978,7 @@
         <v>563974</v>
       </c>
       <c r="AR272" t="n">
-        <v>0</v>
+        <v>86680.78999999999</v>
       </c>
     </row>
     <row r="273">
@@ -39125,7 +39125,7 @@
         <v>563974</v>
       </c>
       <c r="AR273" t="n">
-        <v>0</v>
+        <v>86680.78999999999</v>
       </c>
     </row>
     <row r="274">
@@ -40265,7 +40265,7 @@
         <v>64984305.34</v>
       </c>
       <c r="AQ281" t="n">
-        <v>11445621.85</v>
+        <v>16467076</v>
       </c>
       <c r="AR281" t="n">
         <v>4492931.06</v>
@@ -40691,7 +40691,7 @@
         <v>3200000</v>
       </c>
       <c r="AR284" t="n">
-        <v>304498.36</v>
+        <v>485632.24</v>
       </c>
     </row>
     <row r="285">
@@ -40979,7 +40979,7 @@
         <v>500000</v>
       </c>
       <c r="AR286" t="n">
-        <v>1552.5</v>
+        <v>112220.23</v>
       </c>
     </row>
     <row r="287">

--- a/upload/contratos_siad.xlsx
+++ b/upload/contratos_siad.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR292"/>
+  <dimension ref="A1:AR293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,8 +669,8 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DOS SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, DE FORMA CONTÍNUA,  DAS OBRAS DISCRIMINADAS NO OBJETO CONTRATUAL, RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 24ª CRG DO DER/MG - PASSOS/MG, INCLUÍDOS NO PROGRAMA PLURIANUAL DE AÇÃO GOVERNAMENTAL-PPAG.
-PRC-22.018/11
+          <t>EXECUÇÃO DOS SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, DE FORMA CONTÍNUA,  DAS OBRAS DISCRIMINADAS NO OBJETO CONTRATUAL, RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 24ª CRG DO DER/MG - PASSOS/MG, INCLUÍDOS NO PROGRAMA PLURIANUAL DE AÇÃO GOVERNAMENTAL-PPAG.
+PRC-22.018/11
 PAVIDEZ</t>
         </is>
       </c>
@@ -813,7 +813,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PRC-22.038/12 
+          <t>PRC-22.038/12 
 Execução trabalhos de melhoramento e pavimentação do trecho: ENTRº BR/262 - ENTRº SÃO JOSÉ DO GOIABAL - CAVA GRANDE na Rodovia LMG/760 - MG/320, na extensão de 56,80 km.</t>
         </is>
       </c>
@@ -956,8 +956,8 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-22.024/13 - Serviços de melhoramento e pavimentação do Trecho Caeté - Barão de Cocais, com 24,60km de Extensão, na Rodovia MGC/262.
-Implantação, pavimentação e restauração com aumento de capacidade no Contorno de Barão de Cocais, com 3,90km de extensão, na Rodovia Contorno.
+          <t xml:space="preserve">PRC-22.024/13 - Serviços de melhoramento e pavimentação do Trecho Caeté - Barão de Cocais, com 24,60km de Extensão, na Rodovia MGC/262.
+Implantação, pavimentação e restauração com aumento de capacidade no Contorno de Barão de Cocais, com 3,90km de extensão, na Rodovia Contorno.
 </t>
         </is>
       </c>
@@ -1018,7 +1018,7 @@
         <v>115582671.78</v>
       </c>
       <c r="AR4" t="n">
-        <v>107034418.25</v>
+        <v>107315898.33</v>
       </c>
     </row>
     <row r="5">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.021/13 - Execução dos serviços de Apoio aos Trabalhos de Supervisão de Obras Rodoviárias dos Trechos Constantes do LOTE 02, discriminados abaixo: 
- -  Núcleo  02  e  nos trechos:
- Carandaí ¿ Lagoa Dourada (Entrº BR/383) e OAE;
- Nazareno ¿ Mercês de Água Limpa e OAE;
- Santa Rita de Jacutinga ¿ Divisa MG/RJ;
- Itabirito ¿ Rio Acima;
- Pedra Bonita ¿ Entrº BR/116 e Variante em Pedra Bonita e OAE;
- Ouro Preto (Entrº MG/129) ¿ Distrito de Lavras Novas.
+          <t xml:space="preserve">PRC-24.021/13 - Execução dos serviços de Apoio aos Trabalhos de Supervisão de Obras Rodoviárias dos Trechos Constantes do LOTE 02, discriminados abaixo: 
+ -  Núcleo  02  e  nos trechos:
+ Carandaí ¿ Lagoa Dourada (Entrº BR/383) e OAE;
+ Nazareno ¿ Mercês de Água Limpa e OAE;
+ Santa Rita de Jacutinga ¿ Divisa MG/RJ;
+ Itabirito ¿ Rio Acima;
+ Pedra Bonita ¿ Entrº BR/116 e Variante em Pedra Bonita e OAE;
+ Ouro Preto (Entrº MG/129) ¿ Distrito de Lavras Novas.
 </t>
         </is>
       </c>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.015/13 - Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 04, e  nos trechos:  Água Boa  -  Malacacheta; Entrº BR/262  -  Entrº São José do Goiabal  -  Cava  Grande e OAE; Dores de Guanhães  -  Joanésia (Entrº MG/232); Santa Bárbara  -  São Gonçalo do Rio Abaixo  e  OAE; Bom Jesus do Amparo  -  Nova União; Peçanha  -  Entrº Coroaci.
+          <t xml:space="preserve">PRC-24.015/13 - Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 04, e  nos trechos:  Água Boa  -  Malacacheta; Entrº BR/262  -  Entrº São José do Goiabal  -  Cava  Grande e OAE; Dores de Guanhães  -  Joanésia (Entrº MG/232); Santa Bárbara  -  São Gonçalo do Rio Abaixo  e  OAE; Bom Jesus do Amparo  -  Nova União; Peçanha  -  Entrº Coroaci.
 </t>
         </is>
       </c>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.011/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 07 e  nos trechos: Carmo do Paranaíba (Entrº BR/354)  -  Distrito Quintinos e OAE;  Entrº LMG/690 (Paracatu) - Entrº Entre Ribeiros - Ponte sobre o Rio Paracatu;  Ponte sobre o Rio Paracatu  -  Entrº MG/181  e  OAE;  Arinos (Entrº MGC/479)  -  Riachinho (Entrº MG/181).
+          <t xml:space="preserve">PRC-24.011/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 07 e  nos trechos: Carmo do Paranaíba (Entrº BR/354)  -  Distrito Quintinos e OAE;  Entrº LMG/690 (Paracatu) - Entrº Entre Ribeiros - Ponte sobre o Rio Paracatu;  Ponte sobre o Rio Paracatu  -  Entrº MG/181  e  OAE;  Arinos (Entrº MGC/479)  -  Riachinho (Entrº MG/181).
 </t>
         </is>
       </c>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.008/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do Lote 06 e  nos trechos: Araguari (Entrº BR/050)  -  Entrº BR/365; Campina Verde -  Itapagipe  e OAE; Uberaba (Entrº BR/050)  -  Conceição das Alagoas; Frutal (Entrº BR/364)  -  Garimpo do Bandeira  e Frutal  -  Entrº Fazenda Boa Vista; Iraí de Minas (Entrº LMG/782)  -  Romaria (Entrº BR/365); Perdizes (Entrº BR/452)  -  Entrº BR/262; Serra do Salitre  -  Rio Paranaíba; Contorno Sul de Uberlândia  e OAE;  Conceição das Alagoas  -  Capelinha do Barreiro e Acesso à Poncianos.
+          <t xml:space="preserve">PRC-24.008/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do Lote 06 e  nos trechos: Araguari (Entrº BR/050)  -  Entrº BR/365; Campina Verde -  Itapagipe  e OAE; Uberaba (Entrº BR/050)  -  Conceição das Alagoas; Frutal (Entrº BR/364)  -  Garimpo do Bandeira  e Frutal  -  Entrº Fazenda Boa Vista; Iraí de Minas (Entrº LMG/782)  -  Romaria (Entrº BR/365); Perdizes (Entrº BR/452)  -  Entrº BR/262; Serra do Salitre  -  Rio Paranaíba; Contorno Sul de Uberlândia  e OAE;  Conceição das Alagoas  -  Capelinha do Barreiro e Acesso à Poncianos.
 </t>
         </is>
       </c>
@@ -1663,8 +1663,8 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.010/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 01 e  nos trechos: Nova Lima  -  Sabará; Papagaios  -  Entrº BR/352 (Pitangui)  e OAE;  Anel Viário de Sete Lagoas (Av. Norte/Sul -  MG424) e OAE; Esmeraldas -  São José da Varginha;
-LMG/800 -  Sete Lagoas; Contorno de Matozinhos e Contorno de Prudente de Morais;  Contorno Norte de Lagoa Santa e OAE; Baldim  -  Santana do Riacho;  Acesso à Inhotim.
+          <t xml:space="preserve">PRC-24.010/13 - Serviços de Apoio aos trabalhos de Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 01 e  nos trechos: Nova Lima  -  Sabará; Papagaios  -  Entrº BR/352 (Pitangui)  e OAE;  Anel Viário de Sete Lagoas (Av. Norte/Sul -  MG424) e OAE; Esmeraldas -  São José da Varginha;
+LMG/800 -  Sete Lagoas; Contorno de Matozinhos e Contorno de Prudente de Morais;  Contorno Norte de Lagoa Santa e OAE; Baldim  -  Santana do Riacho;  Acesso à Inhotim.
 </t>
         </is>
       </c>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC- 24.009/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 03 e  nos trechos: Contorno de Andradas; Entrº LMG/827 (para Bambuí)  -  Entrº MG/341 (para Piumhi); Nova Resende  -  Bom Jesus da Penha; Luz  -  Esteios  -  Lagoa da Prata  e OAE; Pimenta  -  Entrº BR/265 (Guapé) e OAE; Cordislândia  -  Carvalhópolis; Medeiros  -  Pratinha.
+          <t xml:space="preserve">PRC- 24.009/13 - Serviços de Apoio à Supervisão de Obras Rodoviárias dos trechos constantes do LOTE 03 e  nos trechos: Contorno de Andradas; Entrº LMG/827 (para Bambuí)  -  Entrº MG/341 (para Piumhi); Nova Resende  -  Bom Jesus da Penha; Luz  -  Esteios  -  Lagoa da Prata  e OAE; Pimenta  -  Entrº BR/265 (Guapé) e OAE; Cordislândia  -  Carvalhópolis; Medeiros  -  Pratinha.
 </t>
         </is>
       </c>
@@ -1946,9 +1946,9 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CONTRATO DP-001/2022 
-ELABORAÇÃO DE PROJETO DE ENGENHARIA
-RODOVIÁRIA PARA MELHORAMENTO, PAVIMENTAÇÃO E OAE DOS TRECHOS A SEGUIR IDENTIFICADOS:
+          <t>CONTRATO DP-001/2022 
+ELABORAÇÃO DE PROJETO DE ENGENHARIA
+RODOVIÁRIA PARA MELHORAMENTO, PAVIMENTAÇÃO E OAE DOS TRECHOS A SEGUIR IDENTIFICADOS:
 RODOVIA - MUNICIPAL; TRECHO: JABUTICATUBAS - LAGOA SANTA, INCLUÍDO NO PPAG .</t>
         </is>
       </c>
@@ -2793,8 +2793,8 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>É objeto do presente contrato, em regime de empreitada, por preços unitários, a
-Contratação de empresa de engenharia consultiva para a Elaboração de Projeto de Engenharia Rodoviária para Melhoramento, Pavimentação e OAE dos trechos Araçaí - Sete Lagoas - RodoviaMunicipal
+          <t>É objeto do presente contrato, em regime de empreitada, por preços unitários, a
+Contratação de empresa de engenharia consultiva para a Elaboração de Projeto de Engenharia Rodoviária para Melhoramento, Pavimentação e OAE dos trechos Araçaí - Sete Lagoas - RodoviaMunicipal
 , inserida no Programa de Governo "Infraestrutura Rodoviária", cujos quantitati vos encontram-se discriminados na planilha "Quadro de Quanti dades e Preços Unitários", que integra o presente contrato.</t>
         </is>
       </c>
@@ -3561,7 +3561,7 @@
         <v>18109045.69</v>
       </c>
       <c r="AR22" t="n">
-        <v>16951910.66</v>
+        <v>17262783.23</v>
       </c>
     </row>
     <row r="23">
@@ -3699,7 +3699,7 @@
         <v>18109045.69</v>
       </c>
       <c r="AR23" t="n">
-        <v>16951910.66</v>
+        <v>17262783.23</v>
       </c>
     </row>
     <row r="24">
@@ -3837,7 +3837,7 @@
         <v>18109045.69</v>
       </c>
       <c r="AR24" t="n">
-        <v>16951910.66</v>
+        <v>17262783.23</v>
       </c>
     </row>
     <row r="25">
@@ -3975,7 +3975,7 @@
         <v>18109045.69</v>
       </c>
       <c r="AR25" t="n">
-        <v>16951910.66</v>
+        <v>17262783.23</v>
       </c>
     </row>
     <row r="26">
@@ -4113,7 +4113,7 @@
         <v>18109045.69</v>
       </c>
       <c r="AR26" t="n">
-        <v>16951910.66</v>
+        <v>17262783.23</v>
       </c>
     </row>
     <row r="27">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Contra to PRC 24.017/2018 
+          <t>Contra to PRC 24.017/2018 
 Elaboração de projeto de Engenharia Rodoviária para melhoramentos e Pavimentação do trecho Ipoema - Entr. LMG 776 (Senhora do carmo) na Rodovia Municipal</t>
         </is>
       </c>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRC-24.005/2018 - Serviços de Apoio à Supervisão da Construção da Ponte sobre o Rio São Francisco com dimensão de 1.120,00m x 13,80m e melhoramento e pavimentação da variante de acesso à Ponte sobre o Rio São Francisco, com 3,060 km de extensão, no trecho São Francisco - Pintópolis, na Rodovia MG/402.
+          <t xml:space="preserve">PRC-24.005/2018 - Serviços de Apoio à Supervisão da Construção da Ponte sobre o Rio São Francisco com dimensão de 1.120,00m x 13,80m e melhoramento e pavimentação da variante de acesso à Ponte sobre o Rio São Francisco, com 3,060 km de extensão, no trecho São Francisco - Pintópolis, na Rodovia MG/402.
 </t>
         </is>
       </c>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PRC-22.003/2019 - Execução da obra de implantação e pavimentação do Acesso ao Distrito de Jacutinga Estrada Municipal, extensão 640,00 m, na Rodovia Municipal e implantação da interseção no Acesso ao Distrito de Jacutinga Interseção MG/290, extensão 700,00 m. Incluídos no PPAG Plano Plurianual da Ação
+          <t>PRC-22.003/2019 - Execução da obra de implantação e pavimentação do Acesso ao Distrito de Jacutinga Estrada Municipal, extensão 640,00 m, na Rodovia Municipal e implantação da interseção no Acesso ao Distrito de Jacutinga Interseção MG/290, extensão 700,00 m. Incluídos no PPAG Plano Plurianual da Ação
 Governamental e contemplados no Programa de Governo Estradas de Minas: Infraestrutura e Logística</t>
         </is>
       </c>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-22.015/2020 - Restauração do pavimento da Pista de Pouso e Decolagem, da Taxiways, do Pátio de Aeronave e Execução da nova sinalização horizontal das Taxiways e do Pátio de Aeronaves do Aeroporto de Ipatinga (SBIP), localizado no município de Santana do Paraíso/MG, com extensão de 2.005 m
+          <t xml:space="preserve">DC-22.015/2020 - Restauração do pavimento da Pista de Pouso e Decolagem, da Taxiways, do Pátio de Aeronave e Execução da nova sinalização horizontal das Taxiways e do Pátio de Aeronaves do Aeroporto de Ipatinga (SBIP), localizado no município de Santana do Paraíso/MG, com extensão de 2.005 m
 </t>
         </is>
       </c>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>DM-031/2021
+          <t>DM-031/2021
 Recuperação funcional do pavimento na rodovia MGC-497, no trecho Entrº BR-365/452 (Uberlândia) - Entrº BR-153 (Prata), com 77,60 km de extensão. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 11ª URG do DER/MG ¿ UBERLÂNDIA</t>
         </is>
       </c>
@@ -14838,8 +14838,8 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrato   DC 004/2022
-Restauração e Aumento de Capacidade do trecho Três Pontas - Varginha (Estaca 80 a 610) - 10,60 km
+          <t xml:space="preserve">contrato   DC 004/2022
+Restauração e Aumento de Capacidade do trecho Três Pontas - Varginha (Estaca 80 a 610) - 10,60 km
 </t>
         </is>
       </c>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>DM-033/2022.
+          <t>DM-033/2022.
 ESTABILIZAÇÃO DE TALUDE DE CORTE (RETALUDAMENTO) NA RODOVIA MG-442, KM 5,0 E 5,4, TRECHO ENTRº BR-040 - BELO VALE. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 01ª URG DO DER/MG ¿ BELO HORIZONTE. INSERIDA NO PROGRAMA DE GOVERNO "INFRAESTRUTURA RODOVIÁRIA", NA AÇÃO ¿RECUPERAÇÃO E MANUTENÇÃO DA MALHA VIÁRIA¿.</t>
         </is>
       </c>
@@ -16877,7 +16877,7 @@
         <v>36562290.78</v>
       </c>
       <c r="AR116" t="n">
-        <v>33365401.61</v>
+        <v>34407873.7</v>
       </c>
     </row>
     <row r="117">
@@ -17019,7 +17019,7 @@
         <v>36562290.78</v>
       </c>
       <c r="AR117" t="n">
-        <v>33365401.61</v>
+        <v>34407873.7</v>
       </c>
     </row>
     <row r="118">
@@ -17161,7 +17161,7 @@
         <v>36562290.78</v>
       </c>
       <c r="AR118" t="n">
-        <v>33365401.61</v>
+        <v>34407873.7</v>
       </c>
     </row>
     <row r="119">
@@ -17721,7 +17721,7 @@
         <v>12965985.3</v>
       </c>
       <c r="AR122" t="n">
-        <v>11574419.7</v>
+        <v>11913431.53</v>
       </c>
     </row>
     <row r="123">
@@ -17863,7 +17863,7 @@
         <v>12965985.3</v>
       </c>
       <c r="AR123" t="n">
-        <v>11574419.7</v>
+        <v>11913431.53</v>
       </c>
     </row>
     <row r="124">
@@ -18005,7 +18005,7 @@
         <v>12965985.3</v>
       </c>
       <c r="AR124" t="n">
-        <v>11574419.7</v>
+        <v>11913431.53</v>
       </c>
     </row>
     <row r="125">
@@ -18147,7 +18147,7 @@
         <v>42224996.38</v>
       </c>
       <c r="AR125" t="n">
-        <v>37845553.81</v>
+        <v>38921158.5</v>
       </c>
     </row>
     <row r="126">
@@ -18289,7 +18289,7 @@
         <v>42224996.38</v>
       </c>
       <c r="AR126" t="n">
-        <v>37845553.81</v>
+        <v>38921158.5</v>
       </c>
     </row>
     <row r="127">
@@ -18431,7 +18431,7 @@
         <v>42224996.38</v>
       </c>
       <c r="AR127" t="n">
-        <v>37845553.81</v>
+        <v>38921158.5</v>
       </c>
     </row>
     <row r="128">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>A CONTRATAÇÃO DE EMPRESA DE ENGENHARIA CONSULTIVA PARA A PRESTAÇÃO DE SERVIÇOS DE APOIO
+          <t>A CONTRATAÇÃO DE EMPRESA DE ENGENHARIA CONSULTIVA PARA A PRESTAÇÃO DE SERVIÇOS DE APOIO
 TÉCNICO AO DER/MG, NA ÁREA DE PROJETO DE ENGENHARIA RODOVIÁRIA</t>
         </is>
       </c>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>DC 015-2022 -A EXECUÇÃO DOS SERVIÇOS DE SINALIZAÇÃO
+          <t>DC 015-2022 -A EXECUÇÃO DOS SERVIÇOS DE SINALIZAÇÃO
 HORIZONTAL E VERTICAL DA RODOVIA MGC-259, NO TRECHO SERRO - DATAS (MORRO DO PAIOL), I</t>
         </is>
       </c>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>DM-039/2022.
+          <t>DM-039/2022.
 Recuperação funcional do pavimento na Rodovia AMG-0150, Trecho Entrº MG-030 - Raposos. a execução dos serviços descritos está restrita ao âmbito de Circunscrição da 1ª URG do DER/MG ¿ Belo Horizonte.</t>
         </is>
       </c>
@@ -22958,7 +22958,7 @@
         <v>6200946.11</v>
       </c>
       <c r="AR159" t="n">
-        <v>2735332.16</v>
+        <v>2740897.7</v>
       </c>
     </row>
     <row r="160">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>CONTRATO DP- 016/2023 - LOTE 10 - DER/DG/LICITAÇÕES 
+          <t>CONTRATO DP- 016/2023 - LOTE 10 - DER/DG/LICITAÇÕES 
 -serviços comuns de engenharia para a realização de sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I do Termo de Referência e Anexos.</t>
         </is>
       </c>
@@ -24157,8 +24157,8 @@
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>contratação de serviços comuns de engenharia
-para a realização de sondagens SPT e PDL para atender a demanda existente no Departamento de
+          <t>contratação de serviços comuns de engenharia
+para a realização de sondagens SPT e PDL para atender a demanda existente no Departamento de
 Edificações e Estradas de Rodagem de Minas Gerais (DER-MG</t>
         </is>
       </c>
@@ -25437,7 +25437,7 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>DM-022/2023
+          <t>DM-022/2023
 Implantação de Variante na Rodovia MGC-383 - km 46, trecho Entre Rios de Minas- Lagoa Dourada. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 4ª URG do DER-MG ¿ Barbacena.</t>
         </is>
       </c>
@@ -25580,8 +25580,8 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Termo Contrato DP 007/2023 - LOTE -01 - DER/DG/LICITAÇÕES 
-Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
+          <t>Termo Contrato DP 007/2023 - LOTE -01 - DER/DG/LICITAÇÕES 
+Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
 sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I do Termo de Referência e Anexos.</t>
         </is>
       </c>
@@ -25720,10 +25720,10 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>CONTRATO DP- 008/2023- LOTE 02 - DER/DG/LICITAÇÕES -Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
-sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas
-de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações
-técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I Termo de Referência e
+          <t>CONTRATO DP- 008/2023- LOTE 02 - DER/DG/LICITAÇÕES -Constitui objeto do presente Termo de Contrato os serviços comuns de engenharia para a realização de
+sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas
+de Rodagem de Minas Gerais (DER-MG), na forma, nas quantidades e em conformidade com as especificações
+técnicas e demais condições, que serão prestados nas condições estabelecidas no ANEXO I Termo de Referência e
 Anexos.</t>
         </is>
       </c>
@@ -26616,7 +26616,7 @@
         <v>32071599.2</v>
       </c>
       <c r="AR185" t="n">
-        <v>29288803.54</v>
+        <v>30220987.47</v>
       </c>
     </row>
     <row r="186">
@@ -26758,7 +26758,7 @@
         <v>32071599.2</v>
       </c>
       <c r="AR186" t="n">
-        <v>29288803.54</v>
+        <v>30220987.47</v>
       </c>
     </row>
     <row r="187">
@@ -26900,7 +26900,7 @@
         <v>33404237.55</v>
       </c>
       <c r="AR187" t="n">
-        <v>30267701.8</v>
+        <v>31744384.29</v>
       </c>
     </row>
     <row r="188">
@@ -27042,7 +27042,7 @@
         <v>33404237.55</v>
       </c>
       <c r="AR188" t="n">
-        <v>30267701.8</v>
+        <v>31744384.29</v>
       </c>
     </row>
     <row r="189">
@@ -27184,7 +27184,7 @@
         <v>23099392.67</v>
       </c>
       <c r="AR189" t="n">
-        <v>22209094.15</v>
+        <v>23099334.6</v>
       </c>
     </row>
     <row r="190">
@@ -27326,7 +27326,7 @@
         <v>23099392.67</v>
       </c>
       <c r="AR190" t="n">
-        <v>22209094.15</v>
+        <v>23099334.6</v>
       </c>
     </row>
     <row r="191">
@@ -27468,7 +27468,7 @@
         <v>23099392.67</v>
       </c>
       <c r="AR191" t="n">
-        <v>22209094.15</v>
+        <v>23099334.6</v>
       </c>
     </row>
     <row r="192">
@@ -27692,7 +27692,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Contrato: DM-9437231 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
+          <t>Contrato: DM-9437231 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
 Objeto: Execução, em regime de empreitada por preços unitários dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 2ª Unidade Regional Guanhães, do DER-MG.</t>
         </is>
       </c>
@@ -27750,10 +27750,10 @@
         <v>52694394.72</v>
       </c>
       <c r="AQ193" t="n">
-        <v>48335460.12</v>
+        <v>52694394.71</v>
       </c>
       <c r="AR193" t="n">
-        <v>44361494.24</v>
+        <v>45342661.98</v>
       </c>
     </row>
     <row r="194">
@@ -27835,7 +27835,7 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440657/2024 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
+          <t>Contrato: DM-9440657/2024 - Empresa: CIMCOP S/A - ENGENHARIA E CONSTRUÇÕES
 Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 11ª Unidade Regional Uberlânida, do DER-MG. Edital 2301762 000008/2024 - LOTE 7.</t>
         </is>
       </c>
@@ -27896,7 +27896,7 @@
         <v>34727471.9</v>
       </c>
       <c r="AR194" t="n">
-        <v>33369920.69</v>
+        <v>34678394.49</v>
       </c>
     </row>
     <row r="195">
@@ -28038,7 +28038,7 @@
         <v>1922644.28</v>
       </c>
       <c r="AR195" t="n">
-        <v>426990.88</v>
+        <v>441663.63</v>
       </c>
     </row>
     <row r="196">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>DM-9440661/2024
+          <t>DM-9440661/2024
 LOTE 9: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 19ª URG - Itajubá</t>
         </is>
       </c>
@@ -28181,7 +28181,7 @@
         <v>29806954.37</v>
       </c>
       <c r="AR196" t="n">
-        <v>28894601.15</v>
+        <v>29806350.61</v>
       </c>
     </row>
     <row r="197">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440649/2024 - Empresa: CONSTRUTORA TERRAYAMA LTDA
+          <t>Contrato: DM-9440649/2024 - Empresa: CONSTRUTORA TERRAYAMA LTDA
 Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 01ª Unidade Regional Belo Horizonte - Norte, do DER-MG. Edital 2301762 000008/2024 - LOTE 2.</t>
         </is>
       </c>
@@ -28605,10 +28605,10 @@
         <v>47758833.23</v>
       </c>
       <c r="AQ199" t="n">
-        <v>32716263.85</v>
+        <v>35064506.55</v>
       </c>
       <c r="AR199" t="n">
-        <v>32591495.13</v>
+        <v>35063980.08</v>
       </c>
     </row>
     <row r="200">
@@ -29142,7 +29142,7 @@
         <v>45391</v>
       </c>
       <c r="AJ203" s="2" t="n">
-        <v>46485</v>
+        <v>46904</v>
       </c>
       <c r="AK203" t="inlineStr">
         <is>
@@ -29170,13 +29170,13 @@
         </is>
       </c>
       <c r="AP203" t="n">
-        <v>44916025.03</v>
+        <v>86564215.42</v>
       </c>
       <c r="AQ203" t="n">
         <v>43774025.03</v>
       </c>
       <c r="AR203" t="n">
-        <v>41553481.03</v>
+        <v>43773293.41</v>
       </c>
     </row>
     <row r="204">
@@ -29228,17 +29228,17 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>9424447</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>DM-015/2024</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>DM-015/2024 - MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 06ª UNIDADE REGIONAL MONTES CLAROS, DO DER-MG. (LOTE 02)</t>
+          <t>DM-007/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 04ª UNIDADE REGIONAL BARBACENA, DO DER-MG. (LOTE 01)</t>
         </is>
       </c>
       <c r="R204" t="inlineStr"/>
@@ -29278,13 +29278,13 @@
       <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" s="2" t="n">
-        <v>45411</v>
+        <v>45390</v>
       </c>
       <c r="AI204" s="2" t="n">
-        <v>45412</v>
+        <v>45391</v>
       </c>
       <c r="AJ204" s="2" t="n">
-        <v>46506</v>
+        <v>46904</v>
       </c>
       <c r="AK204" t="inlineStr">
         <is>
@@ -29303,22 +29303,22 @@
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187702</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187442</t>
         </is>
       </c>
       <c r="AP204" t="n">
-        <v>33721624.27</v>
+        <v>86564215.42</v>
       </c>
       <c r="AQ204" t="n">
-        <v>21518766.52</v>
+        <v>43774025.03</v>
       </c>
       <c r="AR204" t="n">
-        <v>20363121.77</v>
+        <v>43773293.41</v>
       </c>
     </row>
     <row r="205">
@@ -29340,27 +29340,27 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>19.758.779/0001-37</t>
+          <t>00.329.295/0001-44</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
+          <t>EMPAV EMPREENDIMENTOS E PAVIMENTACAO LTDA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -29370,17 +29370,17 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>9440658</t>
+          <t>9424447</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>DM-9440658/2024</t>
+          <t>DM-015/2024</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -29400,8 +29400,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>DM-9440658/2024
-LOTE 8: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 15ª URG</t>
+          <t>DM-015/2024 - MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 06ª UNIDADE REGIONAL MONTES CLAROS, DO DER-MG. (LOTE 02)</t>
         </is>
       </c>
       <c r="R205" t="inlineStr"/>
@@ -29421,17 +29420,17 @@
       <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" s="2" t="n">
-        <v>45585</v>
+        <v>45411</v>
       </c>
       <c r="AI205" s="2" t="n">
-        <v>45586</v>
+        <v>45412</v>
       </c>
       <c r="AJ205" s="2" t="n">
-        <v>46680</v>
+        <v>46506</v>
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL205" t="inlineStr">
@@ -29441,27 +29440,27 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190618</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187702</t>
         </is>
       </c>
       <c r="AP205" t="n">
-        <v>47005570.55</v>
+        <v>33721624.27</v>
       </c>
       <c r="AQ205" t="n">
-        <v>28902039.98</v>
+        <v>21518766.52</v>
       </c>
       <c r="AR205" t="n">
-        <v>26058069.45</v>
+        <v>21518766.52</v>
       </c>
     </row>
     <row r="206">
@@ -29513,17 +29512,17 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2301762 000012/2024</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>9445821</t>
+          <t>9440658</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>DM-9445821/2024</t>
+          <t>DM-9440658/2024</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -29543,9 +29542,8 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>Contrato: 9445821/2024
-Empresa: ETHOS ENGENHARIA DE INFRAESTRUTURA S/A
-Objeto: Recuperação Funcional do Pavimento e Tratamento de Erosões na Rodovia MG-424, trecho Entrº MG-010 - Sete Lagoas, com 50 km de extensão</t>
+          <t>DM-9440658/2024
+LOTE 8: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 15ª URG</t>
         </is>
       </c>
       <c r="R206" t="inlineStr"/>
@@ -29565,13 +29563,13 @@
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" s="2" t="n">
-        <v>45642</v>
+        <v>45585</v>
       </c>
       <c r="AI206" s="2" t="n">
-        <v>45643</v>
+        <v>45586</v>
       </c>
       <c r="AJ206" s="2" t="n">
-        <v>46554</v>
+        <v>46680</v>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
@@ -29590,22 +29588,22 @@
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=611060</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192264</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190618</t>
         </is>
       </c>
       <c r="AP206" t="n">
-        <v>61821473.21</v>
+        <v>47005570.55</v>
       </c>
       <c r="AQ206" t="n">
-        <v>54741060</v>
+        <v>28902039.98</v>
       </c>
       <c r="AR206" t="n">
-        <v>47721091.26</v>
+        <v>27437186.41</v>
       </c>
     </row>
     <row r="207">
@@ -29657,15 +29655,19 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000012/2024</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>9414640</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr"/>
+          <t>9445821</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>DM-9445821/2024</t>
+        </is>
+      </c>
       <c r="N207" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -29683,7 +29685,9 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>DM-005/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 25ª URG, DO DER-MG. (LOTE 05)</t>
+          <t>Contrato: 9445821/2024
+Empresa: ETHOS ENGENHARIA DE INFRAESTRUTURA S/A
+Objeto: Recuperação Funcional do Pavimento e Tratamento de Erosões na Rodovia MG-424, trecho Entrº MG-010 - Sete Lagoas, com 50 km de extensão</t>
         </is>
       </c>
       <c r="R207" t="inlineStr"/>
@@ -29703,17 +29707,17 @@
       <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" s="2" t="n">
-        <v>45364</v>
+        <v>45642</v>
       </c>
       <c r="AI207" s="2" t="n">
-        <v>45365</v>
+        <v>45643</v>
       </c>
       <c r="AJ207" s="2" t="n">
-        <v>46829</v>
+        <v>46554</v>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
@@ -29723,27 +29727,27 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=611060</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187191</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192264</t>
         </is>
       </c>
       <c r="AP207" t="n">
-        <v>66127329.89</v>
+        <v>61821473.21</v>
       </c>
       <c r="AQ207" t="n">
-        <v>35648106.01</v>
+        <v>54741060</v>
       </c>
       <c r="AR207" t="n">
-        <v>32074743.87</v>
+        <v>49514902.21</v>
       </c>
     </row>
     <row r="208">
@@ -29765,27 +29769,27 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>16.578.361/0001-50</t>
+          <t>19.758.779/0001-37</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
+          <t>ETHOS ENGENHARIA DE INFRAESTRUTURA S/A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -29795,19 +29799,15 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2301601 000006/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>9417534</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>DPEI-007/2024</t>
-        </is>
-      </c>
+          <t>9414640</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -29820,12 +29820,12 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>REALIZAÇÃO DE PESQUISA DE PREÇOS DE MERCADO PARA OS INSUMOS UTILIZADOS NO SISTEMA DE CUSTOS E ORÇAMENTOS REFERENCIAIS DE OBRAS E SERVIÇOS DE ENGENHARIA DO ESTADO DE MINAS GERAIS (SICOR-MG) E PRESTAÇÃO DE APOIO TÉCNICO NA ELABORAÇÃO DE ORÇAMENTOS PARA AS OBRAS DO ESTADO DE MINAS GERAIS</t>
+          <t>DM-005/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 25ª URG, DO DER-MG. (LOTE 05)</t>
         </is>
       </c>
       <c r="R208" t="inlineStr"/>
@@ -29845,47 +29845,47 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" s="2" t="n">
+        <v>45364</v>
+      </c>
+      <c r="AI208" s="2" t="n">
         <v>45365</v>
       </c>
-      <c r="AI208" s="2" t="n">
-        <v>45367</v>
-      </c>
       <c r="AJ208" s="2" t="n">
-        <v>46433</v>
+        <v>46829</v>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>Pregão</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>Pregão - Pregão eletrônico</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=581355</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187253</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187191</t>
         </is>
       </c>
       <c r="AP208" t="n">
-        <v>1413414.8</v>
+        <v>66127329.89</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1215020.81</v>
+        <v>35648106.01</v>
       </c>
       <c r="AR208" t="n">
-        <v>1172242.28</v>
+        <v>33586471.75</v>
       </c>
     </row>
     <row r="209">
@@ -29907,27 +29907,27 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>18.258.450/0001-44</t>
+          <t>16.578.361/0001-50</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>FUNDACAO INSTITUTO DE PESQUISAS ECONOMICAS, ADMINISTRATIVAS E CONTABEIS DE MINAS GERAIS - IPEAD</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -29937,17 +29937,17 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301601 000006/2023</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>9416600</t>
+          <t>9417534</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>DPEI-004/2024</t>
+          <t>DPEI-007/2024</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -29967,7 +29967,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>CONTRATANTE: Departamento de Estradas de Rodagem do Estado de Minas Gerais ¿ DER-MG. Contratada: UGLEISSON ALMEIDA RAMALHO LTDA. Objeto: Serviços comuns de engenharia para a realização de sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG). Instrumento: Ordem de Paralisação em 18/03/2024 dos serviços referente ao Contrato DP-014/2023. Processo SEI Nº 2300.01.0080142/2023-69.</t>
+          <t>REALIZAÇÃO DE PESQUISA DE PREÇOS DE MERCADO PARA OS INSUMOS UTILIZADOS NO SISTEMA DE CUSTOS E ORÇAMENTOS REFERENCIAIS DE OBRAS E SERVIÇOS DE ENGENHARIA DO ESTADO DE MINAS GERAIS (SICOR-MG) E PRESTAÇÃO DE APOIO TÉCNICO NA ELABORAÇÃO DE ORÇAMENTOS PARA AS OBRAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="R209" t="inlineStr"/>
@@ -29990,10 +29990,10 @@
         <v>45365</v>
       </c>
       <c r="AI209" s="2" t="n">
-        <v>45370</v>
+        <v>45367</v>
       </c>
       <c r="AJ209" s="2" t="n">
-        <v>46283</v>
+        <v>46433</v>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
@@ -30002,28 +30002,32 @@
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>Outras Contratações</t>
+          <t>Pregão</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>Outras Contratações - Recadastramento de processos</t>
-        </is>
-      </c>
-      <c r="AN209" t="inlineStr"/>
+          <t>Pregão - Pregão eletrônico</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=581355</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187204</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187253</t>
         </is>
       </c>
       <c r="AP209" t="n">
-        <v>1000000</v>
+        <v>1413414.8</v>
       </c>
       <c r="AQ209" t="n">
-        <v>131764.82</v>
+        <v>1413414.8</v>
       </c>
       <c r="AR209" t="n">
-        <v>131764.82</v>
+        <v>1251492.65</v>
       </c>
     </row>
     <row r="210">
@@ -30080,12 +30084,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>9416621</t>
+          <t>9416600</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>DPEI-006/2024</t>
+          <t>DPEI-004/2024</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -30105,7 +30109,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral)</t>
+          <t>CONTRATANTE: Departamento de Estradas de Rodagem do Estado de Minas Gerais ¿ DER-MG. Contratada: UGLEISSON ALMEIDA RAMALHO LTDA. Objeto: Serviços comuns de engenharia para a realização de sondagens, amostragens e ensaios geotécnicos para atender a demanda do Departamento de Edificações e Estradas de Rodagem de Minas Gerais (DER-MG). Instrumento: Ordem de Paralisação em 18/03/2024 dos serviços referente ao Contrato DP-014/2023. Processo SEI Nº 2300.01.0080142/2023-69.</t>
         </is>
       </c>
       <c r="R210" t="inlineStr"/>
@@ -30151,17 +30155,17 @@
       <c r="AN210" t="inlineStr"/>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187169</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187204</t>
         </is>
       </c>
       <c r="AP210" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="AQ210" t="n">
-        <v>421279.76</v>
+        <v>131764.82</v>
       </c>
       <c r="AR210" t="n">
-        <v>421279.76</v>
+        <v>131764.82</v>
       </c>
     </row>
     <row r="211">
@@ -30218,12 +30222,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>9417600</t>
+          <t>9416621</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>DPEI-003/2024</t>
+          <t>DPEI-006/2024</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -30243,7 +30247,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
+          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral)</t>
         </is>
       </c>
       <c r="R211" t="inlineStr"/>
@@ -30263,13 +30267,13 @@
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" s="2" t="n">
-        <v>45373</v>
+        <v>45365</v>
       </c>
       <c r="AI211" s="2" t="n">
-        <v>45377</v>
+        <v>45370</v>
       </c>
       <c r="AJ211" s="2" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
@@ -30289,17 +30293,17 @@
       <c r="AN211" t="inlineStr"/>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187303</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187169</t>
         </is>
       </c>
       <c r="AP211" t="n">
-        <v>1224000</v>
+        <v>1100000</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0</v>
+        <v>421279.76</v>
       </c>
       <c r="AR211" t="n">
-        <v>0</v>
+        <v>421279.76</v>
       </c>
     </row>
     <row r="212">
@@ -30321,27 +30325,27 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>HORIZONTE CONSTRUTORA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>HORIZONTE CONSTRUTORA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>78.134.194/0001-05</t>
+          <t>18.258.450/0001-44</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>HORIZONTE CONSTRUTORA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>HORIZONTE CONSTRUTORA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -30351,17 +30355,17 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>9440654</t>
+          <t>9417600</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>DM-9440654/2024</t>
+          <t>DPEI-003/2024</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -30376,13 +30380,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>DM-9440654/2024
-LOTE 5: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 9ª URG - Curvelo.</t>
+          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
         </is>
       </c>
       <c r="R212" t="inlineStr"/>
@@ -30402,47 +30405,43 @@
       <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" s="2" t="n">
-        <v>45581</v>
+        <v>45373</v>
       </c>
       <c r="AI212" s="2" t="n">
-        <v>45582</v>
+        <v>45377</v>
       </c>
       <c r="AJ212" s="2" t="n">
-        <v>46676</v>
+        <v>46290</v>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Outras Contratações</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
-        </is>
-      </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
-        </is>
-      </c>
+          <t>Outras Contratações - Recadastramento de processos</t>
+        </is>
+      </c>
+      <c r="AN212" t="inlineStr"/>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190614</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187303</t>
         </is>
       </c>
       <c r="AP212" t="n">
-        <v>48158605.21</v>
+        <v>1224000</v>
       </c>
       <c r="AQ212" t="n">
-        <v>32461139.42</v>
+        <v>0</v>
       </c>
       <c r="AR212" t="n">
-        <v>32153234.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -30464,27 +30463,27 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>HORIZONTE CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>HORIZONTE CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>18.578.135/0001-02</t>
+          <t>78.134.194/0001-05</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>HORIZONTE CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>HOUER ENGENHARIA LTDA</t>
+          <t>HORIZONTE CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -30494,17 +30493,17 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2301520 000008/2024</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>9445668</t>
+          <t>9440654</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>DC-9445668/2024</t>
+          <t>DM-9440654/2024</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -30524,7 +30523,8 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA DE ENGENHARIA PARA A ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS E PAVIMENTAÇÃO DO TRECHO CONTORNO DE CAETÉ, COM USO DA METODOLOGIA BIM (BUILDING INFORMATION MODELING OU MODELAGEM DA INFORMAÇÃO PARA CONSTRUÇÃO), 17,000 KM DE EXTENSÃO.</t>
+          <t>DM-9440654/2024
+LOTE 5: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 9ª URG - Curvelo.</t>
         </is>
       </c>
       <c r="R213" t="inlineStr"/>
@@ -30544,13 +30544,13 @@
       <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" s="2" t="n">
-        <v>45631</v>
+        <v>45581</v>
       </c>
       <c r="AI213" s="2" t="n">
-        <v>45637</v>
+        <v>45582</v>
       </c>
       <c r="AJ213" s="2" t="n">
-        <v>46537</v>
+        <v>46676</v>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
@@ -30564,27 +30564,27 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência presencial</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=601737</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192101</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190614</t>
         </is>
       </c>
       <c r="AP213" t="n">
-        <v>2086583.52</v>
+        <v>48158605.21</v>
       </c>
       <c r="AQ213" t="n">
-        <v>500000</v>
+        <v>33058639.42</v>
       </c>
       <c r="AR213" t="n">
-        <v>183445.01</v>
+        <v>33058382.47</v>
       </c>
     </row>
     <row r="214">
@@ -30606,27 +30606,27 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>19.256.565/0001-62</t>
+          <t>18.578.135/0001-02</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>HOUER ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -30636,17 +30636,17 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301520 000008/2024</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>9440650</t>
+          <t>9445668</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>DM-9440650/2024</t>
+          <t>DC-9445668/2024</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -30666,8 +30666,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>DM-9440650/2024
-LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 5ª Unidade Regional Ubá, do DER-MG. Edital nº: 2301762 00008/2024. Processo nº: 2300.01.0094168/2024-52</t>
+          <t>CONTRATAÇÃO DE EMPRESA DE ENGENHARIA PARA A ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS E PAVIMENTAÇÃO DO TRECHO CONTORNO DE CAETÉ, COM USO DA METODOLOGIA BIM (BUILDING INFORMATION MODELING OU MODELAGEM DA INFORMAÇÃO PARA CONSTRUÇÃO), 17,000 KM DE EXTENSÃO.</t>
         </is>
       </c>
       <c r="R214" t="inlineStr"/>
@@ -30687,13 +30686,13 @@
       <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" s="2" t="n">
-        <v>45581</v>
+        <v>45631</v>
       </c>
       <c r="AI214" s="2" t="n">
-        <v>45582</v>
+        <v>45637</v>
       </c>
       <c r="AJ214" s="2" t="n">
-        <v>46676</v>
+        <v>46537</v>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
@@ -30707,27 +30706,27 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência - Concorrência presencial</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=601737</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190613</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192101</t>
         </is>
       </c>
       <c r="AP214" t="n">
-        <v>52604103.19</v>
+        <v>2086583.52</v>
       </c>
       <c r="AQ214" t="n">
-        <v>38194742.87</v>
+        <v>500000</v>
       </c>
       <c r="AR214" t="n">
-        <v>37309639.75</v>
+        <v>183445.01</v>
       </c>
     </row>
     <row r="215">
@@ -30779,17 +30778,17 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9440650</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DM-9440650/2024</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -30809,7 +30808,8 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>DM-008/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 07ª UNIDADE REGIONAL ARAXÁ, DO DER-MG. (LOTE 02)</t>
+          <t>DM-9440650/2024
+LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 5ª Unidade Regional Ubá, do DER-MG. Edital nº: 2301762 00008/2024. Processo nº: 2300.01.0094168/2024-52</t>
         </is>
       </c>
       <c r="R215" t="inlineStr"/>
@@ -30829,17 +30829,17 @@
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" s="2" t="n">
-        <v>45390</v>
+        <v>45581</v>
       </c>
       <c r="AI215" s="2" t="n">
-        <v>45391</v>
+        <v>45582</v>
       </c>
       <c r="AJ215" s="2" t="n">
-        <v>46851</v>
+        <v>46676</v>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
@@ -30849,27 +30849,27 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187456</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190613</t>
         </is>
       </c>
       <c r="AP215" t="n">
-        <v>65019900.51</v>
+        <v>53158788.85</v>
       </c>
       <c r="AQ215" t="n">
-        <v>37513150.09</v>
+        <v>39629742.87</v>
       </c>
       <c r="AR215" t="n">
-        <v>33297386.61</v>
+        <v>37309639.75</v>
       </c>
     </row>
     <row r="216">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -31011,7 +31011,7 @@
         <v>37513150.09</v>
       </c>
       <c r="AR216" t="n">
-        <v>33297386.61</v>
+        <v>37512950.79</v>
       </c>
     </row>
     <row r="217">
@@ -31063,17 +31063,17 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2301762 000049/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>9423384</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>DM-013/2024</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -31093,7 +31093,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>DM-013/2023 - Recuperação funcional do pavimento na rodovia MGC-496 e aterro sobre solo mole no km 102, trecho Entrº BR-365 (Pirapora) - Entrº br-135 (Corinto). A execução dos serviços descritos está restrita ao âmbito de circunscrição da 33ª URG do DER-MG - Pirapora.</t>
+          <t>DM-008/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 07ª UNIDADE REGIONAL ARAXÁ, DO DER-MG. (LOTE 02)</t>
         </is>
       </c>
       <c r="R217" t="inlineStr"/>
@@ -31113,13 +31113,13 @@
       <c r="AF217" t="inlineStr"/>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" s="2" t="n">
-        <v>45398</v>
+        <v>45390</v>
       </c>
       <c r="AI217" s="2" t="n">
-        <v>45399</v>
+        <v>45391</v>
       </c>
       <c r="AJ217" s="2" t="n">
-        <v>46128</v>
+        <v>46851</v>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
@@ -31138,22 +31138,22 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=593940</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187574</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187456</t>
         </is>
       </c>
       <c r="AP217" t="n">
-        <v>88345526.89</v>
+        <v>65019900.51</v>
       </c>
       <c r="AQ217" t="n">
-        <v>78989719.14</v>
+        <v>37513150.09</v>
       </c>
       <c r="AR217" t="n">
-        <v>78989719.14</v>
+        <v>37512950.79</v>
       </c>
     </row>
     <row r="218">
@@ -31175,27 +31175,27 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>25.955.246/0001-48</t>
+          <t>19.256.565/0001-62</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -31205,17 +31205,17 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301762 000049/2023</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>9440653</t>
+          <t>9423384</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>DM-9440653/2024</t>
+          <t>DM-013/2024</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>LOTE 4: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 8ª URG - Diamantina</t>
+          <t>DM-013/2023 - Recuperação funcional do pavimento na rodovia MGC-496 e aterro sobre solo mole no km 102, trecho Entrº BR-365 (Pirapora) - Entrº br-135 (Corinto). A execução dos serviços descritos está restrita ao âmbito de circunscrição da 33ª URG do DER-MG - Pirapora.</t>
         </is>
       </c>
       <c r="R218" t="inlineStr"/>
@@ -31255,17 +31255,17 @@
       <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" s="2" t="n">
-        <v>45582</v>
+        <v>45398</v>
       </c>
       <c r="AI218" s="2" t="n">
-        <v>45583</v>
+        <v>45399</v>
       </c>
       <c r="AJ218" s="2" t="n">
-        <v>46677</v>
+        <v>46128</v>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
@@ -31275,27 +31275,27 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=593940</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190601</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187574</t>
         </is>
       </c>
       <c r="AP218" t="n">
-        <v>49131721.25</v>
+        <v>88345526.89</v>
       </c>
       <c r="AQ218" t="n">
-        <v>28201287.07</v>
+        <v>78989719.14</v>
       </c>
       <c r="AR218" t="n">
-        <v>28199966.48</v>
+        <v>78989719.14</v>
       </c>
     </row>
     <row r="219">
@@ -31347,17 +31347,17 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9440653</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>DM-010/2024</t>
+          <t>DM-9440653/2024</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -31377,7 +31377,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>DM-010/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 23ª URG, DO DER-MG. (LOTE 04)</t>
+          <t>LOTE 4: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 8ª URG - Diamantina</t>
         </is>
       </c>
       <c r="R219" t="inlineStr"/>
@@ -31397,17 +31397,17 @@
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" s="2" t="n">
-        <v>45386</v>
+        <v>45582</v>
       </c>
       <c r="AI219" s="2" t="n">
-        <v>45387</v>
+        <v>45583</v>
       </c>
       <c r="AJ219" s="2" t="n">
-        <v>46850</v>
+        <v>46677</v>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
@@ -31417,27 +31417,27 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187417</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190601</t>
         </is>
       </c>
       <c r="AP219" t="n">
-        <v>76784767.68000001</v>
+        <v>49131721.25</v>
       </c>
       <c r="AQ219" t="n">
-        <v>46633450.4</v>
+        <v>29464787.07</v>
       </c>
       <c r="AR219" t="n">
-        <v>39329098.76</v>
+        <v>29463651.49</v>
       </c>
     </row>
     <row r="220">
@@ -31499,7 +31499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-010/2024</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -31576,10 +31576,10 @@
         <v>76784767.68000001</v>
       </c>
       <c r="AQ220" t="n">
-        <v>46633450.4</v>
+        <v>55487113.01</v>
       </c>
       <c r="AR220" t="n">
-        <v>39329098.76</v>
+        <v>40581155.21</v>
       </c>
     </row>
     <row r="221">
@@ -31631,17 +31631,17 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -31661,7 +31661,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>DM-020/2024 - MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 28ª UNIDADE REGIONAL TEÓFILO OTONI, DO DER-MG. (LOTE 06)</t>
+          <t>DM-010/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 23ª URG, DO DER-MG. (LOTE 04)</t>
         </is>
       </c>
       <c r="R221" t="inlineStr"/>
@@ -31681,13 +31681,13 @@
       <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" s="2" t="n">
-        <v>45425</v>
+        <v>45386</v>
       </c>
       <c r="AI221" s="2" t="n">
-        <v>45426</v>
+        <v>45387</v>
       </c>
       <c r="AJ221" s="2" t="n">
-        <v>46520</v>
+        <v>46850</v>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
@@ -31706,22 +31706,22 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=586271</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187911</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187417</t>
         </is>
       </c>
       <c r="AP221" t="n">
-        <v>37050167.95</v>
+        <v>76784767.68000001</v>
       </c>
       <c r="AQ221" t="n">
-        <v>36687589.24</v>
+        <v>55487113.01</v>
       </c>
       <c r="AR221" t="n">
-        <v>34348802.25</v>
+        <v>40581155.21</v>
       </c>
     </row>
     <row r="222">
@@ -31783,7 +31783,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -31829,7 +31829,7 @@
         <v>45426</v>
       </c>
       <c r="AJ222" s="2" t="n">
-        <v>46520</v>
+        <v>46887</v>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
@@ -31857,13 +31857,13 @@
         </is>
       </c>
       <c r="AP222" t="n">
-        <v>37050167.95</v>
+        <v>71547943.06999999</v>
       </c>
       <c r="AQ222" t="n">
-        <v>36687589.24</v>
+        <v>36689346.54</v>
       </c>
       <c r="AR222" t="n">
-        <v>34348802.25</v>
+        <v>36681100.75</v>
       </c>
     </row>
     <row r="223">
@@ -31885,27 +31885,27 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>19.758.842/0001-35</t>
+          <t>25.955.246/0001-48</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -31915,17 +31915,17 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2301762 000048/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>9412570</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>DM-003/2024</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>DM-003/2024 - Recuperação funcional do pavimento da rodovia LMG-601, trecho Entrº LMG-634 p/ Almenara - Mata Verde / Estabilidade de taludes nos KMs: 28,30 - 36,10 - 42,80 - 51,60 - 58,30 - 58,50 - 58,80 e 59,20. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 27ª URG do DER-MG - Pedra Azul.</t>
+          <t>DM-020/2024 - MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 28ª UNIDADE REGIONAL TEÓFILO OTONI, DO DER-MG. (LOTE 06)</t>
         </is>
       </c>
       <c r="R223" t="inlineStr"/>
@@ -31965,13 +31965,13 @@
       <c r="AF223" t="inlineStr"/>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" s="2" t="n">
-        <v>45344</v>
+        <v>45425</v>
       </c>
       <c r="AI223" s="2" t="n">
-        <v>45345</v>
+        <v>45426</v>
       </c>
       <c r="AJ223" s="2" t="n">
-        <v>46075</v>
+        <v>46887</v>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
@@ -31990,22 +31990,22 @@
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=591928</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=186720</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187911</t>
         </is>
       </c>
       <c r="AP223" t="n">
-        <v>53015964.8</v>
+        <v>71547943.06999999</v>
       </c>
       <c r="AQ223" t="n">
-        <v>51881430.27</v>
+        <v>36689346.54</v>
       </c>
       <c r="AR223" t="n">
-        <v>51881430.27</v>
+        <v>36681100.75</v>
       </c>
     </row>
     <row r="224">
@@ -32057,17 +32057,17 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000048/2023</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9412570</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-003/2024</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -32077,7 +32077,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -32087,7 +32087,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>DM-016/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 13ª URG, DO DER-MG. (LOTE 03)</t>
+          <t>DM-003/2024 - Recuperação funcional do pavimento da rodovia LMG-601, trecho Entrº LMG-634 p/ Almenara - Mata Verde / Estabilidade de taludes nos KMs: 28,30 - 36,10 - 42,80 - 51,60 - 58,30 - 58,50 - 58,80 e 59,20. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 27ª URG do DER-MG - Pedra Azul.</t>
         </is>
       </c>
       <c r="R224" t="inlineStr"/>
@@ -32107,13 +32107,13 @@
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" s="2" t="n">
-        <v>45406</v>
+        <v>45344</v>
       </c>
       <c r="AI224" s="2" t="n">
-        <v>45407</v>
+        <v>45345</v>
       </c>
       <c r="AJ224" s="2" t="n">
-        <v>46868</v>
+        <v>46075</v>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
@@ -32132,22 +32132,22 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=591928</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187662</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=186720</t>
         </is>
       </c>
       <c r="AP224" t="n">
-        <v>66684490.34</v>
+        <v>53015964.8</v>
       </c>
       <c r="AQ224" t="n">
-        <v>24210614.98</v>
+        <v>51881430.27</v>
       </c>
       <c r="AR224" t="n">
-        <v>23789762.18</v>
+        <v>51881430.27</v>
       </c>
     </row>
     <row r="225">
@@ -32209,7 +32209,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -32289,7 +32289,7 @@
         <v>24210614.98</v>
       </c>
       <c r="AR225" t="n">
-        <v>23789762.18</v>
+        <v>24210504.37</v>
       </c>
     </row>
     <row r="226">
@@ -32311,27 +32311,27 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>22.026.959/0001-39</t>
+          <t>19.758.842/0001-35</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -32341,17 +32341,17 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>9440655</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>DM-9440655/2024</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -32371,7 +32371,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>LOTE 6: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços está restrita a 10ª - Varginha.</t>
+          <t>DM-016/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 13ª URG, DO DER-MG. (LOTE 03)</t>
         </is>
       </c>
       <c r="R226" t="inlineStr"/>
@@ -32391,17 +32391,17 @@
       <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" s="2" t="n">
-        <v>45582</v>
+        <v>45406</v>
       </c>
       <c r="AI226" s="2" t="n">
-        <v>45583</v>
+        <v>45407</v>
       </c>
       <c r="AJ226" s="2" t="n">
-        <v>46677</v>
+        <v>46868</v>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
@@ -32411,27 +32411,27 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190616</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187662</t>
         </is>
       </c>
       <c r="AP226" t="n">
-        <v>51333755.33</v>
+        <v>66684490.34</v>
       </c>
       <c r="AQ226" t="n">
-        <v>27932835.16</v>
+        <v>24210614.98</v>
       </c>
       <c r="AR226" t="n">
-        <v>27931835.24</v>
+        <v>24210504.37</v>
       </c>
     </row>
     <row r="227">
@@ -32483,17 +32483,17 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9440655</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DM-9440655/2024</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>DM-014/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 03ª URG, DO DER-MG. (LOTE 01)</t>
+          <t>LOTE 6: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços está restrita a 10ª - Varginha.</t>
         </is>
       </c>
       <c r="R227" t="inlineStr"/>
@@ -32533,17 +32533,17 @@
       <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" s="2" t="n">
-        <v>45405</v>
+        <v>45582</v>
       </c>
       <c r="AI227" s="2" t="n">
-        <v>45406</v>
+        <v>45583</v>
       </c>
       <c r="AJ227" s="2" t="n">
-        <v>46873</v>
+        <v>46677</v>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
@@ -32553,27 +32553,27 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187654</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190616</t>
         </is>
       </c>
       <c r="AP227" t="n">
-        <v>74261373.36</v>
+        <v>51333755.33</v>
       </c>
       <c r="AQ227" t="n">
-        <v>37087380.49</v>
+        <v>27932835.16</v>
       </c>
       <c r="AR227" t="n">
-        <v>35940756.74</v>
+        <v>27931835.24</v>
       </c>
     </row>
     <row r="228">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -32715,7 +32715,7 @@
         <v>37087380.49</v>
       </c>
       <c r="AR228" t="n">
-        <v>35940756.74</v>
+        <v>37086516.12</v>
       </c>
     </row>
     <row r="229">
@@ -32737,27 +32737,27 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>10.913.161/0001-20</t>
+          <t>22.026.959/0001-39</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>MAIS CONSTRUTORA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -32767,17 +32767,17 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>9417858</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -32797,7 +32797,7 @@
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>DC 002-2024-Complementação do Melhoramento e pavimentação do trecho Pintópolis - Urucuia (Lote 1), extensão de 21,753,km,.</t>
+          <t>DM-014/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 03ª URG, DO DER-MG. (LOTE 01)</t>
         </is>
       </c>
       <c r="R229" t="inlineStr"/>
@@ -32817,13 +32817,13 @@
       <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" s="2" t="n">
-        <v>45364</v>
+        <v>45405</v>
       </c>
       <c r="AI229" s="2" t="n">
-        <v>45365</v>
+        <v>45406</v>
       </c>
       <c r="AJ229" s="2" t="n">
-        <v>46188</v>
+        <v>46873</v>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
@@ -32832,28 +32832,32 @@
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>Outras Contratações</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>Outras Contratações - Correção de processos</t>
-        </is>
-      </c>
-      <c r="AN229" t="inlineStr"/>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187364</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187654</t>
         </is>
       </c>
       <c r="AP229" t="n">
-        <v>35199977.08</v>
+        <v>74261373.36</v>
       </c>
       <c r="AQ229" t="n">
-        <v>35198999.84</v>
+        <v>37087380.49</v>
       </c>
       <c r="AR229" t="n">
-        <v>31120868</v>
+        <v>37086516.12</v>
       </c>
     </row>
     <row r="230">
@@ -32910,12 +32914,12 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9417858</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -32925,7 +32929,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -32935,7 +32939,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>DC 003/2024-Complementação do Melhoramento e pavimentação do trecho Pintópolis - Urucuia  (Lote 2), extensão de 51,440 km, na rodovia MG-402.</t>
+          <t>DC 002-2024-Complementação do Melhoramento e pavimentação do trecho Pintópolis - Urucuia (Lote 1), extensão de 21,753,km,.</t>
         </is>
       </c>
       <c r="R230" t="inlineStr"/>
@@ -32961,7 +32965,7 @@
         <v>45365</v>
       </c>
       <c r="AJ230" s="2" t="n">
-        <v>46278</v>
+        <v>46188</v>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
@@ -32981,17 +32985,17 @@
       <c r="AN230" t="inlineStr"/>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187367</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187364</t>
         </is>
       </c>
       <c r="AP230" t="n">
-        <v>71319967.31999999</v>
+        <v>35199977.08</v>
       </c>
       <c r="AQ230" t="n">
-        <v>65669404.68</v>
+        <v>35198999.84</v>
       </c>
       <c r="AR230" t="n">
-        <v>62871375.98</v>
+        <v>31120868</v>
       </c>
     </row>
     <row r="231">
@@ -33013,27 +33017,27 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>01.744.153/0001-06</t>
+          <t>10.913.161/0001-20</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MAIS CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -33043,17 +33047,17 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>9440662</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>DM-9440662/2024</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -33073,7 +33077,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>LOTE 10: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita a 39ª Unidade Regional João Pinheiro.</t>
+          <t>DC 003/2024-Complementação do Melhoramento e pavimentação do trecho Pintópolis - Urucuia  (Lote 2), extensão de 51,440 km, na rodovia MG-402.</t>
         </is>
       </c>
       <c r="R231" t="inlineStr"/>
@@ -33093,47 +33097,43 @@
       <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" s="2" t="n">
-        <v>45581</v>
+        <v>45364</v>
       </c>
       <c r="AI231" s="2" t="n">
-        <v>45582</v>
+        <v>45365</v>
       </c>
       <c r="AJ231" s="2" t="n">
-        <v>46676</v>
+        <v>46278</v>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Outras Contratações</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
-        </is>
-      </c>
-      <c r="AN231" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
-        </is>
-      </c>
+          <t>Outras Contratações - Correção de processos</t>
+        </is>
+      </c>
+      <c r="AN231" t="inlineStr"/>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190620</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187367</t>
         </is>
       </c>
       <c r="AP231" t="n">
-        <v>45768946.45</v>
+        <v>75282924.23</v>
       </c>
       <c r="AQ231" t="n">
-        <v>23736159.27</v>
+        <v>73469404.68000001</v>
       </c>
       <c r="AR231" t="n">
-        <v>22375853.15</v>
+        <v>62871375.98</v>
       </c>
     </row>
     <row r="232">
@@ -33185,17 +33185,17 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2301762 000015/2024</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>9445781</t>
+          <t>9440662</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>DM-9445781/2024</t>
+          <t>DM-9440662/2024</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -33215,8 +33215,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>Contrato: 9445781/2024 - Empresa: PAVIDEZ ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia LMG-886, Trecho: Final do Per. Urbano de Monte Verde - Início do Per. Urbano de Camanducaia, com 28,60 km de extensão</t>
+          <t>LOTE 10: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita a 39ª Unidade Regional João Pinheiro.</t>
         </is>
       </c>
       <c r="R232" t="inlineStr"/>
@@ -33236,13 +33235,13 @@
       <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" s="2" t="n">
-        <v>45637</v>
+        <v>45581</v>
       </c>
       <c r="AI232" s="2" t="n">
-        <v>45638</v>
+        <v>45582</v>
       </c>
       <c r="AJ232" s="2" t="n">
-        <v>46854</v>
+        <v>46676</v>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
@@ -33261,22 +33260,22 @@
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=612900</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192217</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190620</t>
         </is>
       </c>
       <c r="AP232" t="n">
-        <v>8991651.619999999</v>
+        <v>45768946.45</v>
       </c>
       <c r="AQ232" t="n">
-        <v>8787226.720000001</v>
+        <v>23736159.27</v>
       </c>
       <c r="AR232" t="n">
-        <v>8787226.720000001</v>
+        <v>23735237.53</v>
       </c>
     </row>
     <row r="233">
@@ -33328,17 +33327,17 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2301762 000016/2024</t>
+          <t>2301762 000015/2024</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>9447057</t>
+          <t>9445781</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>DM-9447057/2024</t>
+          <t>DM-9445781/2024</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -33358,9 +33357,8 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Contrato: DM-9447057/2024
-Empresa: PAVIDEZ ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia MG-347, no trecho Entrº BR-460 (Carmo de Minas) Entrº p/ Cristina, com 17,60 km de extensão.</t>
+          <t>Contrato: 9445781/2024 - Empresa: PAVIDEZ ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia LMG-886, Trecho: Final do Per. Urbano de Monte Verde - Início do Per. Urbano de Camanducaia, com 28,60 km de extensão</t>
         </is>
       </c>
       <c r="R233" t="inlineStr"/>
@@ -33380,13 +33378,13 @@
       <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" s="2" t="n">
-        <v>45651</v>
+        <v>45637</v>
       </c>
       <c r="AI233" s="2" t="n">
-        <v>45652</v>
+        <v>45638</v>
       </c>
       <c r="AJ233" s="2" t="n">
-        <v>46563</v>
+        <v>46854</v>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
@@ -33405,22 +33403,22 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=613313</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=612900</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192468</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192217</t>
         </is>
       </c>
       <c r="AP233" t="n">
-        <v>8742912.960000001</v>
+        <v>8991651.619999999</v>
       </c>
       <c r="AQ233" t="n">
-        <v>692143.53</v>
+        <v>8787226.720000001</v>
       </c>
       <c r="AR233" t="n">
-        <v>386795.7</v>
+        <v>8787226.720000001</v>
       </c>
     </row>
     <row r="234">
@@ -33472,17 +33470,17 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2301762 000041/2023</t>
+          <t>2301762 000016/2024</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>9410175</t>
+          <t>9447057</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>DM-031/2023</t>
+          <t>DM-9447057/2024</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -33492,7 +33490,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -33502,7 +33500,9 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>DM-031/2023. RECUPERAÇÃO FUNCIONAL DO PAVIMENTO NA RODOVIA AMG-0520, TRECHO ARACITABA - ENTRº MG-452 (P/ OLIVEIRA FORTES) E NA RODOVIA MG-452, TRECHO OLIVEIRA FORTES - PAIVA/ IMPLANTAÇÃO DE VARIANTES NA RODOVIA MG-452 (KM 14,5) E (KM 17)/ RECUPERAÇÃO DE TALUDE DE ATERRO COM MURO (KM12,5) / SUBSTITUIÇÃO DE BUEIRO EXISTENTE NO KM 24. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 05ª URG DO DER-MG ¿ UBÁ.</t>
+          <t>Contrato: DM-9447057/2024
+Empresa: PAVIDEZ ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia MG-347, no trecho Entrº BR-460 (Carmo de Minas) Entrº p/ Cristina, com 17,60 km de extensão.</t>
         </is>
       </c>
       <c r="R234" t="inlineStr"/>
@@ -33522,17 +33522,17 @@
       <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" s="2" t="n">
-        <v>45294</v>
+        <v>45651</v>
       </c>
       <c r="AI234" s="2" t="n">
-        <v>45297</v>
+        <v>45652</v>
       </c>
       <c r="AJ234" s="2" t="n">
-        <v>46027</v>
+        <v>46563</v>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -33542,27 +33542,27 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=587446</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=613313</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=186384</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192468</t>
         </is>
       </c>
       <c r="AP234" t="n">
-        <v>19946327.83</v>
+        <v>8742912.960000001</v>
       </c>
       <c r="AQ234" t="n">
-        <v>18808468.19</v>
+        <v>1269648.72</v>
       </c>
       <c r="AR234" t="n">
-        <v>18808468.19</v>
+        <v>1268648.72</v>
       </c>
     </row>
     <row r="235">
@@ -33614,17 +33614,17 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000041/2023</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9410175</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-031/2023</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -33634,7 +33634,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -33644,7 +33644,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>DM-022/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 16ª UNIDADE REGIONAL OLIVEIRA, DO DER-MG. (LOTE 04)</t>
+          <t>DM-031/2023. RECUPERAÇÃO FUNCIONAL DO PAVIMENTO NA RODOVIA AMG-0520, TRECHO ARACITABA - ENTRº MG-452 (P/ OLIVEIRA FORTES) E NA RODOVIA MG-452, TRECHO OLIVEIRA FORTES - PAIVA/ IMPLANTAÇÃO DE VARIANTES NA RODOVIA MG-452 (KM 14,5) E (KM 17)/ RECUPERAÇÃO DE TALUDE DE ATERRO COM MURO (KM12,5) / SUBSTITUIÇÃO DE BUEIRO EXISTENTE NO KM 24. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 05ª URG DO DER-MG ¿ UBÁ.</t>
         </is>
       </c>
       <c r="R235" t="inlineStr"/>
@@ -33664,13 +33664,13 @@
       <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" s="2" t="n">
-        <v>45426</v>
+        <v>45294</v>
       </c>
       <c r="AI235" s="2" t="n">
-        <v>45427</v>
+        <v>45297</v>
       </c>
       <c r="AJ235" s="2" t="n">
-        <v>46521</v>
+        <v>46027</v>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
@@ -33689,22 +33689,22 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=587446</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187887</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=186384</t>
         </is>
       </c>
       <c r="AP235" t="n">
-        <v>42788655.89</v>
+        <v>19946327.83</v>
       </c>
       <c r="AQ235" t="n">
-        <v>33119572.24</v>
+        <v>18808468.19</v>
       </c>
       <c r="AR235" t="n">
-        <v>33118572.64</v>
+        <v>18808468.19</v>
       </c>
     </row>
     <row r="236">
@@ -33766,7 +33766,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -33812,7 +33812,7 @@
         <v>45427</v>
       </c>
       <c r="AJ236" s="2" t="n">
-        <v>46521</v>
+        <v>46888</v>
       </c>
       <c r="AK236" t="inlineStr">
         <is>
@@ -33840,13 +33840,13 @@
         </is>
       </c>
       <c r="AP236" t="n">
-        <v>42788655.89</v>
+        <v>85330856.28</v>
       </c>
       <c r="AQ236" t="n">
-        <v>33119572.24</v>
+        <v>34215072.24</v>
       </c>
       <c r="AR236" t="n">
-        <v>33118572.64</v>
+        <v>34214260.27</v>
       </c>
     </row>
     <row r="237">
@@ -33868,27 +33868,27 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>06.045.864/0001-06</t>
+          <t>01.744.153/0001-06</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -33898,17 +33898,17 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2301617 000002/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>9436677</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>DG/AMA-009436677/2024</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -33918,7 +33918,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -33928,7 +33928,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t xml:space="preserve"> objeto do presente instrumento é a Prestação de Serviços de Elaboração de Projeto de Recuperação de Áreas Degradadas na rodovia MG-161, trecho: São Romão - Santa Fé de Minas, conforme condições, quantidades e exigências estabelecidas neste Edital e seus anexos.</t>
+          <t>DM-022/2024 - SERVIÇOS DE MANUTENÇÃO RODOVIÁRIA, CONSERVAÇÃO ROTINEIRA E PERIÓDICA, SERVIÇOS DE URGÊNCIA E PEQUENOS MELHORAMENTOS, BEM COMO REPARAÇÕES DO CORPO ESTRADAL E SEUS DISPOSITIVOS. A EXECUÇÃO DOS SERVIÇOS DESCRITOS ESTÁ RESTRITA AO ÂMBITO DE CIRCUNSCRIÇÃO DA 16ª UNIDADE REGIONAL OLIVEIRA, DO DER-MG. (LOTE 04)</t>
         </is>
       </c>
       <c r="R237" t="inlineStr"/>
@@ -33948,43 +33948,47 @@
       <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" s="2" t="n">
-        <v>45516</v>
+        <v>45426</v>
       </c>
       <c r="AI237" s="2" t="n">
-        <v>45517</v>
+        <v>45427</v>
       </c>
       <c r="AJ237" s="2" t="n">
-        <v>45701</v>
+        <v>46888</v>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>Dispensa de Licitação - Por valor</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>Compra direta - adm direta, fundação ou autarquia</t>
-        </is>
-      </c>
-      <c r="AN237" t="inlineStr"/>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="AN237" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594692</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=189423</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187887</t>
         </is>
       </c>
       <c r="AP237" t="n">
-        <v>118125.23</v>
+        <v>85330856.28</v>
       </c>
       <c r="AQ237" t="n">
-        <v>118125.23</v>
+        <v>34215072.24</v>
       </c>
       <c r="AR237" t="n">
-        <v>118125.23</v>
+        <v>34214260.27</v>
       </c>
     </row>
     <row r="238">
@@ -34006,27 +34010,27 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>33.548.452/0001-61</t>
+          <t>06.045.864/0001-06</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>PORTO ASSUNCAO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -34036,17 +34040,17 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301617 000002/2024</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>9414354</t>
+          <t>9436677</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>DPEI-001/2024</t>
+          <t>DG/AMA-009436677/2024</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -34056,17 +34060,17 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
+          <t xml:space="preserve"> objeto do presente instrumento é a Prestação de Serviços de Elaboração de Projeto de Recuperação de Áreas Degradadas na rodovia MG-161, trecho: São Romão - Santa Fé de Minas, conforme condições, quantidades e exigências estabelecidas neste Edital e seus anexos.</t>
         </is>
       </c>
       <c r="R238" t="inlineStr"/>
@@ -34086,43 +34090,43 @@
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" s="2" t="n">
-        <v>45362</v>
+        <v>45516</v>
       </c>
       <c r="AI238" s="2" t="n">
-        <v>45363</v>
+        <v>45517</v>
       </c>
       <c r="AJ238" s="2" t="n">
-        <v>46276</v>
+        <v>45701</v>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>Outras Contratações</t>
+          <t>Dispensa de Licitação - Por valor</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>Outras Contratações - Recadastramento de processos</t>
+          <t>Compra direta - adm direta, fundação ou autarquia</t>
         </is>
       </c>
       <c r="AN238" t="inlineStr"/>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187070</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=189423</t>
         </is>
       </c>
       <c r="AP238" t="n">
-        <v>1247750</v>
+        <v>118125.23</v>
       </c>
       <c r="AQ238" t="n">
-        <v>787537.27</v>
+        <v>118125.23</v>
       </c>
       <c r="AR238" t="n">
-        <v>787537.27</v>
+        <v>118125.23</v>
       </c>
     </row>
     <row r="239">
@@ -34179,12 +34183,12 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>9414453</t>
+          <t>9414354</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>DPEI-002/2024</t>
+          <t>DPEI-001/2024</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -34204,7 +34208,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG),</t>
+          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
         </is>
       </c>
       <c r="R239" t="inlineStr"/>
@@ -34250,17 +34254,17 @@
       <c r="AN239" t="inlineStr"/>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187133</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187070</t>
         </is>
       </c>
       <c r="AP239" t="n">
-        <v>1244600</v>
+        <v>1247750</v>
       </c>
       <c r="AQ239" t="n">
-        <v>166388.81</v>
+        <v>787537.27</v>
       </c>
       <c r="AR239" t="n">
-        <v>166388.81</v>
+        <v>787537.27</v>
       </c>
     </row>
     <row r="240">
@@ -34282,27 +34286,27 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>RETA ENGENHARIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RETA ENGENHARIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>00.410.954/0001-72</t>
+          <t>33.548.452/0001-61</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>RETA ENGENHARIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>RETA ENGENHARIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -34312,17 +34316,17 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2301520 000021/2024</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>9447109</t>
+          <t>9414453</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>DC-9447109/2024</t>
+          <t>DPEI-002/2024</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -34332,17 +34336,17 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA DE CONSULTORIA EM ENGENHARIA PARA ELABORAÇÃO DO ESTUDO DE ENGENHARIA DE PLANEJAMENTO, CAPEX E DESENVOLVIMENTO DE PLANILHA ORÇAMENTÁRIA PARA OBRA DE ARTE ESPECIAL - PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC/135 (MANGA) - PORTO DE MATIAS CARDOSO (1.160,00M X 13,80M)</t>
+          <t>serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG),</t>
         </is>
       </c>
       <c r="R240" t="inlineStr"/>
@@ -34362,47 +34366,43 @@
       <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" s="2" t="n">
-        <v>45652</v>
+        <v>45362</v>
       </c>
       <c r="AI240" s="2" t="n">
-        <v>45653</v>
+        <v>45363</v>
       </c>
       <c r="AJ240" s="2" t="n">
-        <v>45803</v>
+        <v>46276</v>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Outras Contratações</t>
         </is>
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência presencial</t>
-        </is>
-      </c>
-      <c r="AN240" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=611123</t>
-        </is>
-      </c>
+          <t>Outras Contratações - Recadastramento de processos</t>
+        </is>
+      </c>
+      <c r="AN240" t="inlineStr"/>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192531</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187133</t>
         </is>
       </c>
       <c r="AP240" t="n">
-        <v>519737.51</v>
+        <v>1244600</v>
       </c>
       <c r="AQ240" t="n">
-        <v>519737.51</v>
+        <v>166388.81</v>
       </c>
       <c r="AR240" t="n">
-        <v>519737.51</v>
+        <v>166388.81</v>
       </c>
     </row>
     <row r="241">
@@ -34424,27 +34424,27 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>RETA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>RETA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>25.708.348/0001-69</t>
+          <t>00.410.954/0001-72</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>RETA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
+          <t>RETA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -34454,17 +34454,17 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301520 000021/2024</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>9440647</t>
+          <t>9447109</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>DM-9440647/2024</t>
+          <t>DC-9447109/2024</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -34474,7 +34474,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -34484,8 +34484,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Contrato: DM-9440647/2024 - Empresa: SEISAN ENGENHARIA E CONSTRUÇÕES LTDA
-Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 1ª Unidade Regional Belo Horizonte - Sul, do DER-MG. Edital 2301762 000008/2024 - LOTE 1.</t>
+          <t>CONTRATAÇÃO DE EMPRESA ESPECIALIZADA DE CONSULTORIA EM ENGENHARIA PARA ELABORAÇÃO DO ESTUDO DE ENGENHARIA DE PLANEJAMENTO, CAPEX E DESENVOLVIMENTO DE PLANILHA ORÇAMENTÁRIA PARA OBRA DE ARTE ESPECIAL - PONTE SOBRE O RIO SÃO FRANCISCO - ENTR. MGC/135 (MANGA) - PORTO DE MATIAS CARDOSO (1.160,00M X 13,80M)</t>
         </is>
       </c>
       <c r="R241" t="inlineStr"/>
@@ -34505,13 +34504,13 @@
       <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" s="2" t="n">
-        <v>45585</v>
+        <v>45652</v>
       </c>
       <c r="AI241" s="2" t="n">
-        <v>45586</v>
+        <v>45653</v>
       </c>
       <c r="AJ241" s="2" t="n">
-        <v>46680</v>
+        <v>45803</v>
       </c>
       <c r="AK241" t="inlineStr">
         <is>
@@ -34525,27 +34524,27 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência - Concorrência presencial</t>
         </is>
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=611123</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190599</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192531</t>
         </is>
       </c>
       <c r="AP241" t="n">
-        <v>47556790.26</v>
+        <v>519737.51</v>
       </c>
       <c r="AQ241" t="n">
-        <v>34676037.57</v>
+        <v>519737.51</v>
       </c>
       <c r="AR241" t="n">
-        <v>34445238.35</v>
+        <v>519737.51</v>
       </c>
     </row>
     <row r="242">
@@ -34567,27 +34566,27 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>09.491.927/0001-46</t>
+          <t>25.708.348/0001-69</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>SEISAN ENGENHARIA E CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -34597,17 +34596,17 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>9414322</t>
+          <t>9440647</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>DPEI-005/2024</t>
+          <t>DM-9440647/2024</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -34622,12 +34621,13 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>contratação de serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
+          <t>Contrato: DM-9440647/2024 - Empresa: SEISAN ENGENHARIA E CONSTRUÇÕES LTDA
+Objeto: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 1ª Unidade Regional Belo Horizonte - Sul, do DER-MG. Edital 2301762 000008/2024 - LOTE 1.</t>
         </is>
       </c>
       <c r="R242" t="inlineStr"/>
@@ -34647,43 +34647,47 @@
       <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" s="2" t="n">
-        <v>45357</v>
+        <v>45585</v>
       </c>
       <c r="AI242" s="2" t="n">
-        <v>45359</v>
+        <v>45586</v>
       </c>
       <c r="AJ242" s="2" t="n">
-        <v>46272</v>
+        <v>46680</v>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL242" t="inlineStr">
         <is>
-          <t>Outras Contratações</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>Outras Contratações - Recadastramento de processos</t>
-        </is>
-      </c>
-      <c r="AN242" t="inlineStr"/>
+          <t>Concorrência - Concorrência eletrônica</t>
+        </is>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=606544</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187078</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=190599</t>
         </is>
       </c>
       <c r="AP242" t="n">
-        <v>797999.85</v>
+        <v>47556790.26</v>
       </c>
       <c r="AQ242" t="n">
-        <v>428070.96</v>
+        <v>35414037.57</v>
       </c>
       <c r="AR242" t="n">
-        <v>428070.96</v>
+        <v>35413266.3</v>
       </c>
     </row>
     <row r="243">
@@ -34705,27 +34709,27 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>18.742.098/0001-18</t>
+          <t>09.491.927/0001-46</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -34735,17 +34739,17 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2301520 000029/2023</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>9426807</t>
+          <t>9414322</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>DC-010/2024</t>
+          <t>DPEI-005/2024</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -34755,17 +34759,17 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Vigente publicado</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>DC 010/2024- Construção da Ponte sobre o Rio Matipó e Implantação de Interseção na Rodovia LMG-840, trecho Entr° BR262 (Padre Fialho) - Pedra Bonita - Dimensões: (54,10 x 10,30)m</t>
+          <t>contratação de serviço comum de engenharia para a realização de estudos topográficos (levantamento topográfico e cadastral) para atender à demanda do Departamento de Estradas de Rodagem de Minas Gerais (DER-MG)</t>
         </is>
       </c>
       <c r="R243" t="inlineStr"/>
@@ -34785,47 +34789,43 @@
       <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" s="2" t="n">
-        <v>45406</v>
+        <v>45357</v>
       </c>
       <c r="AI243" s="2" t="n">
-        <v>45406</v>
+        <v>45359</v>
       </c>
       <c r="AJ243" s="2" t="n">
-        <v>46045</v>
+        <v>46272</v>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
         </is>
       </c>
       <c r="AL243" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Outras Contratações</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>Concorrência</t>
-        </is>
-      </c>
-      <c r="AN243" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594836</t>
-        </is>
-      </c>
+          <t>Outras Contratações - Recadastramento de processos</t>
+        </is>
+      </c>
+      <c r="AN243" t="inlineStr"/>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187835</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187078</t>
         </is>
       </c>
       <c r="AP243" t="n">
-        <v>5784477.99</v>
+        <v>797999.85</v>
       </c>
       <c r="AQ243" t="n">
-        <v>5726999.65</v>
+        <v>428070.96</v>
       </c>
       <c r="AR243" t="n">
-        <v>5726999.65</v>
+        <v>428070.96</v>
       </c>
     </row>
     <row r="244">
@@ -34833,11 +34833,11 @@
         <v>2024</v>
       </c>
       <c r="B244" t="n">
-        <v>2470</v>
+        <v>2300</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE TRANSPORTES</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -34847,27 +34847,27 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>17.210.063/0001-75</t>
+          <t>18.742.098/0001-18</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -34877,17 +34877,17 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>1301017 000012/2024</t>
+          <t>2301520 000029/2023</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>9447043</t>
+          <t>9426807</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>9447043/2024-A</t>
+          <t>DC-010/2024</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -34897,19 +34897,17 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 01 MG-050: Concessão PATROCINADA. Rodovia MG-050: km 57,60 no entr. BR-262 (Juatuba) ao km 402,00 no entr. BR-491 (São Sebastião do Paraíso);
-Rodovia BR-491: km 0,00 no entr. MG-050 (São Sebastião do Paraíso) ao km 4,65 no entr. BR-265;
-Rodovia BR-265: km 637,20 no entr. BR-491 ao km 659,50 na divisa MG/SP.</t>
+          <t>DC 010/2024- Construção da Ponte sobre o Rio Matipó e Implantação de Interseção na Rodovia LMG-840, trecho Entr° BR262 (Padre Fialho) - Pedra Bonita - Dimensões: (54,10 x 10,30)m</t>
         </is>
       </c>
       <c r="R244" t="inlineStr"/>
@@ -34929,17 +34927,17 @@
       <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" s="2" t="n">
-        <v>45646</v>
+        <v>45406</v>
       </c>
       <c r="AI244" s="2" t="n">
-        <v>45650</v>
+        <v>45406</v>
       </c>
       <c r="AJ244" s="2" t="n">
-        <v>46379</v>
+        <v>46045</v>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL244" t="inlineStr">
@@ -34949,27 +34947,27 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência presencial</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=603455</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=594836</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192484</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=187835</t>
         </is>
       </c>
       <c r="AP244" t="n">
-        <v>11402647.35</v>
+        <v>5784477.99</v>
       </c>
       <c r="AQ244" t="n">
-        <v>7042519.45</v>
+        <v>5726999.65</v>
       </c>
       <c r="AR244" t="n">
-        <v>6281201.11</v>
+        <v>5726999.65</v>
       </c>
     </row>
     <row r="245">
@@ -34991,27 +34989,27 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>52.635.422/0001-37</t>
+          <t>17.210.063/0001-75</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -35026,12 +35024,12 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>9447045</t>
+          <t>9447043</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>9447045/2024-A</t>
+          <t>9447043/2024-A</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -35051,13 +35049,9 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 02 Vias do Café: Concessão Outorgada, com 432,80 km:
-Rodovia MG-167: km 0,00 no entr. BR-265 (Santana da Vargem) ao km 43,80 no entr. CMG-491 (Varginha);
-Rodovia BR-265: km 338,40 no entr. BR-381 (Lavras) ao km 403,00 no entr. LMG-863 (Boa Esperança);
-Rodovia LMG-863: km 0,00 ao km 5,00 no entr. BR-265 (Boa Esperança);
-Rodovia CMG-491: km 4,65 no entr. CMG-265 (São Sebastião do Paraíso) ao km 81,05 no entr. BR-146-A/MG-450 (Guaxupé) e entre o km 108,25 no entr. BR-146-B (Muzambinho) ao km 259,95 no entr. BR-381 (Três Corações);
-Rodovia BR-146: km 505,30 no entr. CMG-491 (Guaxupé) ao km 532,50 no entr. CMG-491 (Muzambinho);
-Rodovia CMG-369: km 124,40 no entr. BR-265 (Boa Esperança) ao km 188,50 no entr. CMG-491 (Alfenas).</t>
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 01 MG-050: Concessão PATROCINADA. Rodovia MG-050: km 57,60 no entr. BR-262 (Juatuba) ao km 402,00 no entr. BR-491 (São Sebastião do Paraíso);
+Rodovia BR-491: km 0,00 no entr. MG-050 (São Sebastião do Paraíso) ao km 4,65 no entr. BR-265;
+Rodovia BR-265: km 637,20 no entr. BR-491 ao km 659,50 na divisa MG/SP.</t>
         </is>
       </c>
       <c r="R245" t="inlineStr"/>
@@ -35080,10 +35074,10 @@
         <v>45646</v>
       </c>
       <c r="AI245" s="2" t="n">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="AJ245" s="2" t="n">
-        <v>46376</v>
+        <v>46379</v>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
@@ -35107,29 +35101,29 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192464</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192484</t>
         </is>
       </c>
       <c r="AP245" t="n">
-        <v>5328591.49</v>
+        <v>11402647.35</v>
       </c>
       <c r="AQ245" t="n">
-        <v>3143751.27</v>
+        <v>7042519.45</v>
       </c>
       <c r="AR245" t="n">
-        <v>2997002.8</v>
+        <v>6692673.15</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B246" t="n">
-        <v>2300</v>
+        <v>2470</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM</t>
+          <t>AGENCIA REGULADORA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -35139,27 +35133,27 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>10.957.855/0001-69</t>
+          <t>52.635.422/0001-37</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -35169,17 +35163,17 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>1301017 000012/2024</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9447045</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>9447045/2024-A</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -35194,13 +35188,18 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>DM-9471880/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 26ª Unidade Regional Paracatu</t>
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão LOTE 02 Vias do Café: Concessão Outorgada, com 432,80 km:
+Rodovia MG-167: km 0,00 no entr. BR-265 (Santana da Vargem) ao km 43,80 no entr. CMG-491 (Varginha);
+Rodovia BR-265: km 338,40 no entr. BR-381 (Lavras) ao km 403,00 no entr. LMG-863 (Boa Esperança);
+Rodovia LMG-863: km 0,00 ao km 5,00 no entr. BR-265 (Boa Esperança);
+Rodovia CMG-491: km 4,65 no entr. CMG-265 (São Sebastião do Paraíso) ao km 81,05 no entr. BR-146-A/MG-450 (Guaxupé) e entre o km 108,25 no entr. BR-146-B (Muzambinho) ao km 259,95 no entr. BR-381 (Três Corações);
+Rodovia BR-146: km 505,30 no entr. CMG-491 (Guaxupé) ao km 532,50 no entr. CMG-491 (Muzambinho);
+Rodovia CMG-369: km 124,40 no entr. BR-265 (Boa Esperança) ao km 188,50 no entr. CMG-491 (Alfenas).</t>
         </is>
       </c>
       <c r="R246" t="inlineStr"/>
@@ -35220,17 +35219,17 @@
       <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" s="2" t="n">
-        <v>45855</v>
+        <v>45646</v>
       </c>
       <c r="AI246" s="2" t="n">
-        <v>45860</v>
+        <v>45647</v>
       </c>
       <c r="AJ246" s="2" t="n">
-        <v>46955</v>
+        <v>46376</v>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL246" t="inlineStr">
@@ -35240,27 +35239,27 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência - Concorrência presencial</t>
         </is>
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=603455</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196691</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=192464</t>
         </is>
       </c>
       <c r="AP246" t="n">
-        <v>51814575.44</v>
+        <v>5328591.49</v>
       </c>
       <c r="AQ246" t="n">
-        <v>10462369.13</v>
+        <v>3663751.27</v>
       </c>
       <c r="AR246" t="n">
-        <v>7703559.16</v>
+        <v>3201393.19</v>
       </c>
     </row>
     <row r="247">
@@ -35282,27 +35281,27 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>01.415.130/0001-58</t>
+          <t>10.957.855/0001-69</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -35312,17 +35311,17 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2301520 000031/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>9481581</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>DC-9481581/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -35342,7 +35341,8 @@
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>Contratação de Serviço Técnico Especializado de Apoio ao DER-MG para Desapropriação e Regularização Expropriatória.</t>
+          <t>DM-9471880/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 26ª Unidade Regional Paracatu</t>
         </is>
       </c>
       <c r="R247" t="inlineStr"/>
@@ -35362,13 +35362,13 @@
       <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" s="2" t="n">
-        <v>45959</v>
+        <v>45855</v>
       </c>
       <c r="AI247" s="2" t="n">
-        <v>45961</v>
+        <v>45860</v>
       </c>
       <c r="AJ247" s="2" t="n">
-        <v>47787</v>
+        <v>46955</v>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
@@ -35387,22 +35387,22 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=630475</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199146</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196691</t>
         </is>
       </c>
       <c r="AP247" t="n">
-        <v>21860486.4</v>
+        <v>51814575.44</v>
       </c>
       <c r="AQ247" t="n">
-        <v>8524750</v>
+        <v>10462369.13</v>
       </c>
       <c r="AR247" t="n">
-        <v>4368963.92</v>
+        <v>9802051.75</v>
       </c>
     </row>
     <row r="248">
@@ -35424,27 +35424,27 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>04.810.813/0001-06</t>
+          <t>01.415.130/0001-58</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>BT CONSTRUCOES LTDA</t>
+          <t>ALTA ENGENHARIA DE INFRAESTRUTURA LTDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -35454,17 +35454,17 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2301520 000027/2024</t>
+          <t>2301520 000031/2025</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>9458861</t>
+          <t>9481581</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>DC-9458861/2025</t>
+          <t>DC-9481581/2025</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -35479,12 +35479,12 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>Complementação dos serviços de melhoramento e pavimentação, no Contorno Sul de Uberlândia e Adequação com a MGC-455.</t>
+          <t>Contratação de Serviço Técnico Especializado de Apoio ao DER-MG para Desapropriação e Regularização Expropriatória.</t>
         </is>
       </c>
       <c r="R248" t="inlineStr"/>
@@ -35504,17 +35504,17 @@
       <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" s="2" t="n">
-        <v>45744</v>
+        <v>45959</v>
       </c>
       <c r="AI248" s="2" t="n">
-        <v>45745</v>
+        <v>45961</v>
       </c>
       <c r="AJ248" s="2" t="n">
-        <v>46195</v>
+        <v>47787</v>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
@@ -35529,22 +35529,22 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618592</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=630475</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194392</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199146</t>
         </is>
       </c>
       <c r="AP248" t="n">
-        <v>29717994.42</v>
+        <v>21860486.4</v>
       </c>
       <c r="AQ248" t="n">
-        <v>27434826.73</v>
+        <v>8524750</v>
       </c>
       <c r="AR248" t="n">
-        <v>16632566.89</v>
+        <v>5120891.78</v>
       </c>
     </row>
     <row r="249">
@@ -35566,27 +35566,27 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>66.418.765/0001-54</t>
+          <t>04.810.813/0001-06</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+          <t>BT CONSTRUCOES LTDA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -35596,17 +35596,17 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000027/2024</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9458861</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DC-9458861/2025</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -35616,18 +35616,17 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Vigente publicado</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>DM-9471835/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 34ª Unidade Regional Salinas, do DER-MG.</t>
+          <t>Complementação dos serviços de melhoramento e pavimentação, no Contorno Sul de Uberlândia e Adequação com a MGC-455.</t>
         </is>
       </c>
       <c r="R249" t="inlineStr"/>
@@ -35647,17 +35646,17 @@
       <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" s="2" t="n">
-        <v>45853</v>
+        <v>45744</v>
       </c>
       <c r="AI249" s="2" t="n">
-        <v>45855</v>
+        <v>45745</v>
       </c>
       <c r="AJ249" s="2" t="n">
-        <v>46950</v>
+        <v>46195</v>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
@@ -35672,22 +35671,22 @@
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618592</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196648</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194392</t>
         </is>
       </c>
       <c r="AP249" t="n">
-        <v>44573000</v>
+        <v>29717994.42</v>
       </c>
       <c r="AQ249" t="n">
-        <v>5821337.93</v>
+        <v>27434826.73</v>
       </c>
       <c r="AR249" t="n">
-        <v>5198379.09</v>
+        <v>17853910.27</v>
       </c>
     </row>
     <row r="250">
@@ -35709,27 +35708,27 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>34.038.516/0001-47</t>
+          <t>66.418.765/0001-54</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>CONSTRUTORA CTC LTDA</t>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -35744,12 +35743,12 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -35769,8 +35768,8 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>DM-9471881/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 30ª Unidade Regional Juiz de Fora, do DER-MG.</t>
+          <t>DM-9471835/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 34ª Unidade Regional Salinas, do DER-MG.</t>
         </is>
       </c>
       <c r="R250" t="inlineStr"/>
@@ -35790,13 +35789,13 @@
       <c r="AF250" t="inlineStr"/>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" s="2" t="n">
-        <v>45862</v>
+        <v>45853</v>
       </c>
       <c r="AI250" s="2" t="n">
-        <v>45866</v>
+        <v>45855</v>
       </c>
       <c r="AJ250" s="2" t="n">
-        <v>46961</v>
+        <v>46950</v>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
@@ -35820,17 +35819,17 @@
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196692</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196648</t>
         </is>
       </c>
       <c r="AP250" t="n">
-        <v>53358800</v>
+        <v>44573000</v>
       </c>
       <c r="AQ250" t="n">
-        <v>15689188.17</v>
+        <v>5821337.93</v>
       </c>
       <c r="AR250" t="n">
-        <v>12226202.87</v>
+        <v>5820534.08</v>
       </c>
     </row>
     <row r="251">
@@ -35852,27 +35851,27 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>01.175.068/0001-74</t>
+          <t>34.038.516/0001-47</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>CONSTRUTORA CTC LTDA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -35882,17 +35881,17 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -35907,16 +35906,13 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 5: Contratação de empresa para a
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
-equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 02ª, 08ª, 21ª, 22ª, 23ª, 27ª, 28ª, 34ª e 38ª
-URGs do DER-MG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e
-seus anexos.</t>
+          <t>DM-9471881/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 30ª Unidade Regional Juiz de Fora, do DER-MG.</t>
         </is>
       </c>
       <c r="R251" t="inlineStr"/>
@@ -35936,13 +35932,13 @@
       <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" s="2" t="n">
-        <v>45975</v>
+        <v>45862</v>
       </c>
       <c r="AI251" s="2" t="n">
-        <v>45979</v>
+        <v>45866</v>
       </c>
       <c r="AJ251" s="2" t="n">
-        <v>47074</v>
+        <v>46961</v>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
@@ -35961,22 +35957,22 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199389</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196692</t>
         </is>
       </c>
       <c r="AP251" t="n">
-        <v>32097999.96</v>
+        <v>53358800</v>
       </c>
       <c r="AQ251" t="n">
-        <v>656819.88</v>
+        <v>17016188.17</v>
       </c>
       <c r="AR251" t="n">
-        <v>0</v>
+        <v>17015221.31</v>
       </c>
     </row>
     <row r="252">
@@ -35998,27 +35994,27 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>93.315.190/0001-17</t>
+          <t>01.175.068/0001-74</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>ELISEU KOPP &amp; CIA LTDA</t>
+          <t>DATA TRAFFIC S/A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -36033,12 +36029,12 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -36058,9 +36054,11 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 2: Contratação de empresa para aprestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dosequipamentos fixos de fiscalização eletrônica abrangendo os trechos das 04ª, 10ª, 15ª, 19ª e 30ª URGs do DERMG.
-Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 5: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
+equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 02ª, 08ª, 21ª, 22ª, 23ª, 27ª, 28ª, 34ª e 38ª
+URGs do DER-MG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e
+seus anexos.</t>
         </is>
       </c>
       <c r="R252" t="inlineStr"/>
@@ -36080,13 +36078,13 @@
       <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" s="2" t="n">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="AI252" s="2" t="n">
-        <v>45972</v>
+        <v>45979</v>
       </c>
       <c r="AJ252" s="2" t="n">
-        <v>47067</v>
+        <v>47074</v>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
@@ -36110,17 +36108,17 @@
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199388</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199389</t>
         </is>
       </c>
       <c r="AP252" t="n">
-        <v>45188997.86</v>
+        <v>32097999.96</v>
       </c>
       <c r="AQ252" t="n">
-        <v>653712.8</v>
+        <v>656819.88</v>
       </c>
       <c r="AR252" t="n">
-        <v>0</v>
+        <v>104029.11</v>
       </c>
     </row>
     <row r="253">
@@ -36142,27 +36140,27 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>08.697.901/0001-96</t>
+          <t>93.315.190/0001-17</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -36172,17 +36170,17 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -36197,12 +36195,14 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>Recuperação Funcional do Pavimento na Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 44,300 km / Recomposição de Talude Erodido nas Estacas 145, 525,775 e 2170.</t>
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 2: Contratação de empresa para aprestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dosequipamentos fixos de fiscalização eletrônica abrangendo os trechos das 04ª, 10ª, 15ª, 19ª e 30ª URGs do DERMG.
+Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
       <c r="R253" t="inlineStr"/>
@@ -36222,13 +36222,13 @@
       <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" s="2" t="n">
-        <v>45877</v>
+        <v>45968</v>
       </c>
       <c r="AI253" s="2" t="n">
-        <v>45878</v>
+        <v>45972</v>
       </c>
       <c r="AJ253" s="2" t="n">
-        <v>46478</v>
+        <v>47067</v>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
@@ -36247,22 +36247,22 @@
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621036</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197290</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199388</t>
         </is>
       </c>
       <c r="AP253" t="n">
-        <v>45918998.95</v>
+        <v>45188997.86</v>
       </c>
       <c r="AQ253" t="n">
-        <v>13205099.01</v>
+        <v>653712.8</v>
       </c>
       <c r="AR253" t="n">
-        <v>3970214.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -36284,27 +36284,27 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>18.218.909/0001-86</t>
+          <t>08.697.901/0001-96</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>FUNDACAO CHRISTIANO OTTONI</t>
+          <t>ENC EMPRESA NACIONAL DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -36314,17 +36314,17 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>9478941</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>DPEI-9478941/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de Desenvolvimentos Metodológicos, nos Eixos Inteligência Geográfica e Tráfego Rodoviário, para auxílio na tomada de decisão acerca dos investimentos na malha rodoviária do Estado de Minas Gerais</t>
+          <t>Recuperação Funcional do Pavimento na Rodovia MG-010, trecho Conceição do Mato Dentro - Serro (Distrito de Mato Grosso), com extensão de 44,300 km / Recomposição de Talude Erodido nas Estacas 145, 525,775 e 2170.</t>
         </is>
       </c>
       <c r="R254" t="inlineStr"/>
@@ -36364,13 +36364,13 @@
       <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" s="2" t="n">
-        <v>45926</v>
+        <v>45877</v>
       </c>
       <c r="AI254" s="2" t="n">
-        <v>45930</v>
+        <v>45878</v>
       </c>
       <c r="AJ254" s="2" t="n">
-        <v>46842</v>
+        <v>46478</v>
       </c>
       <c r="AK254" t="inlineStr">
         <is>
@@ -36379,28 +36379,32 @@
       </c>
       <c r="AL254" t="inlineStr">
         <is>
-          <t>Dispensa de Licitação</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>Dispensa de Licitação - Contratação de inst. de pesquisa, ensino, desenvol. inst., estímulo à inovaç</t>
-        </is>
-      </c>
-      <c r="AN254" t="inlineStr"/>
+          <t>Concorrência - Concorrência eletrônica</t>
+        </is>
+      </c>
+      <c r="AN254" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621036</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=198328</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197290</t>
         </is>
       </c>
       <c r="AP254" t="n">
-        <v>2401689.3</v>
+        <v>46359911.33</v>
       </c>
       <c r="AQ254" t="n">
-        <v>1904724.91</v>
+        <v>17205099.01</v>
       </c>
       <c r="AR254" t="n">
-        <v>1355674.86</v>
+        <v>5611559.44</v>
       </c>
     </row>
     <row r="255">
@@ -36422,27 +36426,27 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>01.466.431/0001-00</t>
+          <t>18.218.909/0001-86</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
+          <t>FUNDACAO CHRISTIANO OTTONI</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -36452,17 +36456,17 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9478941</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -36477,14 +36481,12 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>Contratação de empresa para a prestação de serviços de instalação, sinalização,
-aferição,operação, monitoramento e manutenção dos equipamentos fi xos de fi scalização
-eletrônicaabrangendo os trechos das 07ª, 11ª, 14ª, 18ª, 24ª, 25ª, 26ª e 31ª URGs do DER-MG</t>
+          <t>Prestação de Serviços de Desenvolvimentos Metodológicos, nos Eixos Inteligência Geográfica e Tráfego Rodoviário, para auxílio na tomada de decisão acerca dos investimentos na malha rodoviária do Estado de Minas Gerais</t>
         </is>
       </c>
       <c r="R255" t="inlineStr"/>
@@ -36504,13 +36506,13 @@
       <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" s="2" t="n">
-        <v>45968</v>
+        <v>45926</v>
       </c>
       <c r="AI255" s="2" t="n">
-        <v>45973</v>
+        <v>45930</v>
       </c>
       <c r="AJ255" s="2" t="n">
-        <v>47069</v>
+        <v>46842</v>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
@@ -36519,32 +36521,28 @@
       </c>
       <c r="AL255" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Dispensa de Licitação</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
-        </is>
-      </c>
-      <c r="AN255" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
-        </is>
-      </c>
+          <t>Dispensa de Licitação - Contratação de inst. de pesquisa, ensino, desenvol. inst., estímulo à inovaç</t>
+        </is>
+      </c>
+      <c r="AN255" t="inlineStr"/>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199382</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=198328</t>
         </is>
       </c>
       <c r="AP255" t="n">
-        <v>47349998.43</v>
+        <v>2401689.3</v>
       </c>
       <c r="AQ255" t="n">
-        <v>638712.8</v>
+        <v>1904724.91</v>
       </c>
       <c r="AR255" t="n">
-        <v>0</v>
+        <v>1355674.86</v>
       </c>
     </row>
     <row r="256">
@@ -36566,27 +36564,27 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>70.073.275/0001-30</t>
+          <t>01.466.431/0001-00</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
+          <t>GCT - GERENCIAMENTO E CONTROLE DE TRANSITO S/A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -36596,17 +36594,17 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>9470136</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>AEST-9470136/2025</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -36621,12 +36619,14 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 1: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha  odoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 04ª URG - Barbacena, 10ª URG -Varginha, 15ª URG - Poços de Caldas, 16ª URG - Oliveira, 19ª URG - Itajubá, 20ª URG - Formiga, 24ª URG -Passos e 30ª URG - Juiz de Fora.</t>
+          <t>Contratação de empresa para a prestação de serviços de instalação, sinalização,
+aferição,operação, monitoramento e manutenção dos equipamentos fi xos de fi scalização
+eletrônicaabrangendo os trechos das 07ª, 11ª, 14ª, 18ª, 24ª, 25ª, 26ª e 31ª URGs do DER-MG</t>
         </is>
       </c>
       <c r="R256" t="inlineStr"/>
@@ -36646,17 +36646,17 @@
       <c r="AF256" t="inlineStr"/>
       <c r="AG256" t="inlineStr"/>
       <c r="AH256" s="2" t="n">
-        <v>45820</v>
+        <v>45968</v>
       </c>
       <c r="AI256" s="2" t="n">
-        <v>45824</v>
+        <v>45973</v>
       </c>
       <c r="AJ256" s="2" t="n">
-        <v>46553</v>
+        <v>47069</v>
       </c>
       <c r="AK256" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL256" t="inlineStr">
@@ -36671,22 +36671,22 @@
       </c>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195813</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199382</t>
         </is>
       </c>
       <c r="AP256" t="n">
-        <v>9410345.890000001</v>
+        <v>47349998.43</v>
       </c>
       <c r="AQ256" t="n">
-        <v>2816414.71</v>
+        <v>638712.8</v>
       </c>
       <c r="AR256" t="n">
-        <v>1035494.68</v>
+        <v>102098.42</v>
       </c>
     </row>
     <row r="257">
@@ -36708,27 +36708,27 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>19.230.918/0001-55</t>
+          <t>70.073.275/0001-30</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>GUAXIMA ENGENHARIA LTDA</t>
+          <t>GEOSISTEMAS ENGENHARIA E PLANEJAMENTO LTDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -36738,17 +36738,17 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9470136</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>AEST-9470136/2025</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -36763,13 +36763,12 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>DM-9473163/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 29ª Unidade Regional Manhumirim, do DER-MG.</t>
+          <t>serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 1: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha  odoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 04ª URG - Barbacena, 10ª URG -Varginha, 15ª URG - Poços de Caldas, 16ª URG - Oliveira, 19ª URG - Itajubá, 20ª URG - Formiga, 24ª URG -Passos e 30ª URG - Juiz de Fora.</t>
         </is>
       </c>
       <c r="R257" t="inlineStr"/>
@@ -36789,17 +36788,17 @@
       <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="inlineStr"/>
       <c r="AH257" s="2" t="n">
-        <v>45874</v>
+        <v>45820</v>
       </c>
       <c r="AI257" s="2" t="n">
-        <v>45876</v>
+        <v>45824</v>
       </c>
       <c r="AJ257" s="2" t="n">
-        <v>46971</v>
+        <v>46553</v>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
@@ -36814,22 +36813,22 @@
       </c>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197140</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195813</t>
         </is>
       </c>
       <c r="AP257" t="n">
-        <v>59299394.97</v>
+        <v>9410345.890000001</v>
       </c>
       <c r="AQ257" t="n">
-        <v>33169918.01</v>
+        <v>2816414.71</v>
       </c>
       <c r="AR257" t="n">
-        <v>26777072.2</v>
+        <v>1035494.68</v>
       </c>
     </row>
     <row r="258">
@@ -36851,27 +36850,27 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>19.256.565/0001-62</t>
+          <t>19.230.918/0001-55</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -36881,17 +36880,17 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2301762 000016/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>9485592</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>DM-9485592/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -36911,9 +36910,8 @@
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>Contrato: DM-9485592/2025
-Empresa: HWN ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia AMG - 1705 - Trecho: Santa Cruz do Escalvado - Entr° MG 329 , com 17,30 km de extensão.</t>
+          <t>DM-9473163/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 29ª Unidade Regional Manhumirim, do DER-MG.</t>
         </is>
       </c>
       <c r="R258" t="inlineStr"/>
@@ -36933,13 +36931,13 @@
       <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="inlineStr"/>
       <c r="AH258" s="2" t="n">
-        <v>46001</v>
+        <v>45874</v>
       </c>
       <c r="AI258" s="2" t="n">
-        <v>46014</v>
+        <v>45876</v>
       </c>
       <c r="AJ258" s="2" t="n">
-        <v>46743</v>
+        <v>46971</v>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
@@ -36958,22 +36956,22 @@
       </c>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=633935</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199830</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197140</t>
         </is>
       </c>
       <c r="AP258" t="n">
-        <v>10929975.56</v>
+        <v>59299394.97</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1107834.98</v>
+        <v>42023580.62</v>
       </c>
       <c r="AR258" t="n">
-        <v>405673.71</v>
+        <v>28789491.13</v>
       </c>
     </row>
     <row r="259">
@@ -37025,17 +37023,17 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2301762 000017/2025</t>
+          <t>2301762 000016/2025</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>9485591</t>
+          <t>9485592</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>DM-9485591/2025</t>
+          <t>DM-9485592/2025</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -37055,9 +37053,9 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>Contrato: DM-9485591/2025
-Empresa: HWN ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia: LMG-845 - Trecho: Sericita - Entr° 262, com 19,00 km de extensão.</t>
+          <t>Contrato: DM-9485592/2025
+Empresa: HWN ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia AMG - 1705 - Trecho: Santa Cruz do Escalvado - Entr° MG 329 , com 17,30 km de extensão.</t>
         </is>
       </c>
       <c r="R259" t="inlineStr"/>
@@ -37102,22 +37100,22 @@
       </c>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=633951</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=633935</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199829</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199830</t>
         </is>
       </c>
       <c r="AP259" t="n">
-        <v>6199729.76</v>
+        <v>10929975.56</v>
       </c>
       <c r="AQ259" t="n">
-        <v>2578424.04</v>
+        <v>7426192.86</v>
       </c>
       <c r="AR259" t="n">
-        <v>2369404.54</v>
+        <v>7425192.86</v>
       </c>
     </row>
     <row r="260">
@@ -37169,17 +37167,17 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301762 000017/2025</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9485591</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9485591/2025</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -37199,9 +37197,9 @@
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>Contrato: DM-9459013/2025
-Empresa: HWN ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia MG-188, no Trecho Guarda-Mor a Coromandel, com 92,50 km de extensão.</t>
+          <t>Contrato: DM-9485591/2025
+Empresa: HWN ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia: LMG-845 - Trecho: Sericita - Entr° 262, com 19,00 km de extensão.</t>
         </is>
       </c>
       <c r="R260" t="inlineStr"/>
@@ -37221,13 +37219,13 @@
       <c r="AF260" t="inlineStr"/>
       <c r="AG260" t="inlineStr"/>
       <c r="AH260" s="2" t="n">
-        <v>45754</v>
+        <v>46001</v>
       </c>
       <c r="AI260" s="2" t="n">
-        <v>45756</v>
+        <v>46014</v>
       </c>
       <c r="AJ260" s="2" t="n">
-        <v>46485</v>
+        <v>46743</v>
       </c>
       <c r="AK260" t="inlineStr">
         <is>
@@ -37246,22 +37244,22 @@
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618030</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=633951</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194470</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199829</t>
         </is>
       </c>
       <c r="AP260" t="n">
-        <v>52239647.93</v>
+        <v>6199729.76</v>
       </c>
       <c r="AQ260" t="n">
-        <v>49484496.54</v>
+        <v>2578424.04</v>
       </c>
       <c r="AR260" t="n">
-        <v>37883322.64</v>
+        <v>2577424.04</v>
       </c>
     </row>
     <row r="261">
@@ -37313,17 +37311,17 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -37343,9 +37341,9 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Contrato: DM-9492723/2025
-Empresa: HWN ENGENHARIA LTDA
-Objeto: Recuperação do Pavimento na Rodovia: MGC-452, trecho: Tupaciguara - Araporã, com 59,00 Km de extensão.</t>
+          <t>Contrato: DM-9459013/2025
+Empresa: HWN ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia MG-188, no Trecho Guarda-Mor a Coromandel, com 92,50 km de extensão.</t>
         </is>
       </c>
       <c r="R261" t="inlineStr"/>
@@ -37365,13 +37363,13 @@
       <c r="AF261" t="inlineStr"/>
       <c r="AG261" t="inlineStr"/>
       <c r="AH261" s="2" t="n">
-        <v>46021</v>
+        <v>45754</v>
       </c>
       <c r="AI261" s="2" t="n">
-        <v>46028</v>
+        <v>45756</v>
       </c>
       <c r="AJ261" s="2" t="n">
-        <v>47244</v>
+        <v>46485</v>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
@@ -37390,22 +37388,22 @@
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=635946</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618030</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=205464</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194470</t>
         </is>
       </c>
       <c r="AP261" t="n">
-        <v>41984578.11</v>
+        <v>52239647.93</v>
       </c>
       <c r="AQ261" t="n">
-        <v>30683880.42</v>
+        <v>49484496.54</v>
       </c>
       <c r="AR261" t="n">
-        <v>22075692.06</v>
+        <v>49435419.09</v>
       </c>
     </row>
     <row r="262">
@@ -37427,27 +37425,27 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>19.758.842/0001-35</t>
+          <t>19.256.565/0001-62</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -37457,17 +37455,17 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -37487,7 +37485,9 @@
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>Complementação das obras de melhoramentos e pavimentação do trecho Araguari (Distrito de Amanhece) ¿ Divisa MG/GO, na rodovia MG-414.</t>
+          <t>Contrato: DM-9492723/2025
+Empresa: HWN ENGENHARIA LTDA
+Objeto: Recuperação do Pavimento na Rodovia: MGC-452, trecho: Tupaciguara - Araporã, com 59,00 Km de extensão.</t>
         </is>
       </c>
       <c r="R262" t="inlineStr"/>
@@ -37507,13 +37507,13 @@
       <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="inlineStr"/>
       <c r="AH262" s="2" t="n">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="AI262" s="2" t="n">
-        <v>46015</v>
+        <v>46028</v>
       </c>
       <c r="AJ262" s="2" t="n">
-        <v>46795</v>
+        <v>47244</v>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
@@ -37532,22 +37532,22 @@
       </c>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=634079</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=635946</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=203426</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=205464</t>
         </is>
       </c>
       <c r="AP262" t="n">
-        <v>59890000</v>
+        <v>41984578.11</v>
       </c>
       <c r="AQ262" t="n">
-        <v>36674397.45</v>
+        <v>30683880.42</v>
       </c>
       <c r="AR262" t="n">
-        <v>1421648.87</v>
+        <v>30682880.42</v>
       </c>
     </row>
     <row r="263">
@@ -37569,27 +37569,27 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>16.873.137/0001-90</t>
+          <t>19.758.842/0001-35</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
+          <t>LCM CONSTRUCAO E COMERCIO S.A</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -37599,17 +37599,17 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -37629,8 +37629,7 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>DM-9471834/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 31ª Unidade Regional Ituiutaba, do DER-MG.</t>
+          <t>Complementação das obras de melhoramentos e pavimentação do trecho Araguari (Distrito de Amanhece) ¿ Divisa MG/GO, na rodovia MG-414.</t>
         </is>
       </c>
       <c r="R263" t="inlineStr"/>
@@ -37650,13 +37649,13 @@
       <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="inlineStr"/>
       <c r="AH263" s="2" t="n">
-        <v>45856</v>
+        <v>46014</v>
       </c>
       <c r="AI263" s="2" t="n">
-        <v>45860</v>
+        <v>46015</v>
       </c>
       <c r="AJ263" s="2" t="n">
-        <v>46955</v>
+        <v>46795</v>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
@@ -37675,22 +37674,22 @@
       </c>
       <c r="AN263" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=634079</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196647</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=203426</t>
         </is>
       </c>
       <c r="AP263" t="n">
-        <v>50960749.38</v>
+        <v>59890000</v>
       </c>
       <c r="AQ263" t="n">
-        <v>7583539.81</v>
+        <v>36674397.45</v>
       </c>
       <c r="AR263" t="n">
-        <v>6623750.95</v>
+        <v>1852820.31</v>
       </c>
     </row>
     <row r="264">
@@ -37712,27 +37711,27 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>22.026.959/0001-39</t>
+          <t>16.873.137/0001-90</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
+          <t>LF ENGENHARIA RODOVIARIA LTDA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -37747,12 +37746,12 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -37772,8 +37771,8 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>DM-9471830/2025
-LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 20ª Unidade Regional Formiga, do DER-MG. Processo nº: 2300.01.0120269/2025-27</t>
+          <t>DM-9471834/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 31ª Unidade Regional Ituiutaba, do DER-MG.</t>
         </is>
       </c>
       <c r="R264" t="inlineStr"/>
@@ -37793,13 +37792,13 @@
       <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="inlineStr"/>
       <c r="AH264" s="2" t="n">
-        <v>45874</v>
+        <v>45856</v>
       </c>
       <c r="AI264" s="2" t="n">
-        <v>45876</v>
+        <v>45860</v>
       </c>
       <c r="AJ264" s="2" t="n">
-        <v>46971</v>
+        <v>46955</v>
       </c>
       <c r="AK264" t="inlineStr">
         <is>
@@ -37823,17 +37822,17 @@
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196645</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196647</t>
         </is>
       </c>
       <c r="AP264" t="n">
-        <v>53573999.99</v>
+        <v>50960749.38</v>
       </c>
       <c r="AQ264" t="n">
-        <v>10112429.79</v>
+        <v>7583539.81</v>
       </c>
       <c r="AR264" t="n">
-        <v>7795111</v>
+        <v>7511253.9</v>
       </c>
     </row>
     <row r="265">
@@ -37855,27 +37854,27 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>26.383.935/0001-98</t>
+          <t>22.026.959/0001-39</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>MA ENGENHARIA LTDA</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -37890,12 +37889,12 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>9471879</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -37915,8 +37914,8 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>DM-9471879/2025
-Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 18ª Unidade Regional Monte Carmelo, do DER-MG.</t>
+          <t>DM-9471830/2025
+LOTE 3: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 20ª Unidade Regional Formiga, do DER-MG. Processo nº: 2300.01.0120269/2025-27</t>
         </is>
       </c>
       <c r="R265" t="inlineStr"/>
@@ -37936,13 +37935,13 @@
       <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="inlineStr"/>
       <c r="AH265" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="AI265" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="AJ265" s="2" t="n">
-        <v>46961</v>
+        <v>46971</v>
       </c>
       <c r="AK265" t="inlineStr">
         <is>
@@ -37966,17 +37965,17 @@
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196690</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196645</t>
         </is>
       </c>
       <c r="AP265" t="n">
-        <v>53241874.38</v>
+        <v>53573999.99</v>
       </c>
       <c r="AQ265" t="n">
-        <v>15680311</v>
+        <v>17732429.79</v>
       </c>
       <c r="AR265" t="n">
-        <v>13759262.25</v>
+        <v>17729236.66</v>
       </c>
     </row>
     <row r="266">
@@ -37998,27 +37997,27 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>01.744.153/0001-06</t>
+          <t>26.383.935/0001-98</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>PAVIDEZ ENGENHARIA LTDA</t>
+          <t>MA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -38028,17 +38027,17 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2301520 000004/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>9459021</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>DC-9459021/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -38058,7 +38057,8 @@
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>Melhoramento e pavimentação do trecho Curral de Dentro - Entr.º p/ Berizal - Mirandópolis - LMG-626.</t>
+          <t>DM-9471879/2025
+Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 18ª Unidade Regional Monte Carmelo, do DER-MG.</t>
         </is>
       </c>
       <c r="R266" t="inlineStr"/>
@@ -38078,13 +38078,13 @@
       <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="inlineStr"/>
       <c r="AH266" s="2" t="n">
-        <v>45750</v>
+        <v>45862</v>
       </c>
       <c r="AI266" s="2" t="n">
-        <v>45752</v>
+        <v>45866</v>
       </c>
       <c r="AJ266" s="2" t="n">
-        <v>46531</v>
+        <v>46961</v>
       </c>
       <c r="AK266" t="inlineStr">
         <is>
@@ -38103,22 +38103,22 @@
       </c>
       <c r="AN266" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619796</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194485</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196690</t>
         </is>
       </c>
       <c r="AP266" t="n">
-        <v>46672147.37</v>
+        <v>53241874.38</v>
       </c>
       <c r="AQ266" t="n">
-        <v>46672146.38</v>
+        <v>15680311</v>
       </c>
       <c r="AR266" t="n">
-        <v>40483756.11</v>
+        <v>15679621.78</v>
       </c>
     </row>
     <row r="267">
@@ -38170,17 +38170,17 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000004/2025</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9459021</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DC-9459021/2025</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -38200,8 +38200,7 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>DM-9471832/2025
-LOTE 4: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 24ª Unidade Regional Passos, do DER-MG.</t>
+          <t>Melhoramento e pavimentação do trecho Curral de Dentro - Entr.º p/ Berizal - Mirandópolis - LMG-626.</t>
         </is>
       </c>
       <c r="R267" t="inlineStr"/>
@@ -38221,13 +38220,13 @@
       <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="inlineStr"/>
       <c r="AH267" s="2" t="n">
-        <v>45849</v>
+        <v>45750</v>
       </c>
       <c r="AI267" s="2" t="n">
-        <v>45853</v>
+        <v>45752</v>
       </c>
       <c r="AJ267" s="2" t="n">
-        <v>46948</v>
+        <v>46531</v>
       </c>
       <c r="AK267" t="inlineStr">
         <is>
@@ -38246,22 +38245,22 @@
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619796</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196665</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=194485</t>
         </is>
       </c>
       <c r="AP267" t="n">
-        <v>49093539.45</v>
+        <v>46672147.37</v>
       </c>
       <c r="AQ267" t="n">
-        <v>7052723.42</v>
+        <v>46672146.38</v>
       </c>
       <c r="AR267" t="n">
-        <v>5774272.98</v>
+        <v>40890087.14</v>
       </c>
     </row>
     <row r="268">
@@ -38313,17 +38312,17 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -38343,9 +38342,8 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>Contrato: DM-9453530/2025
-Empresa: PAVIDEZ ENGENHARIA LTDA
-Objeto: Recuperação Funcional do Pavimento na Rodovia AMG-1615, no trecho Cristais - Entrº MGC-369, extensão de 11,70 km.</t>
+          <t>DM-9471832/2025
+LOTE 4: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 24ª Unidade Regional Passos, do DER-MG.</t>
         </is>
       </c>
       <c r="R268" t="inlineStr"/>
@@ -38365,13 +38363,13 @@
       <c r="AF268" t="inlineStr"/>
       <c r="AG268" t="inlineStr"/>
       <c r="AH268" s="2" t="n">
-        <v>45722</v>
+        <v>45849</v>
       </c>
       <c r="AI268" s="2" t="n">
-        <v>45724</v>
+        <v>45853</v>
       </c>
       <c r="AJ268" s="2" t="n">
-        <v>46453</v>
+        <v>46948</v>
       </c>
       <c r="AK268" t="inlineStr">
         <is>
@@ -38390,22 +38388,22 @@
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618446</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=193984</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196665</t>
         </is>
       </c>
       <c r="AP268" t="n">
-        <v>7109673.15</v>
+        <v>49093539.45</v>
       </c>
       <c r="AQ268" t="n">
-        <v>4452559.37</v>
+        <v>7052723.42</v>
       </c>
       <c r="AR268" t="n">
-        <v>4309693.56</v>
+        <v>6662219.32</v>
       </c>
     </row>
     <row r="269">
@@ -38427,27 +38425,27 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>10.417.566/0001-77</t>
+          <t>01.744.153/0001-06</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -38457,17 +38455,17 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -38482,12 +38480,14 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 2: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 07ª URG ¿ Araxá, 11ª URG ¿ Uberlândia, 14ª URG - Patos de Minas, 18ª URG - Monte Carmelo, 25ª URG - Uberaba, 26ª URG ¿ Paracatu, 31ª URG ¿ Ituiutaba, 39ª URG - João Pinheiro</t>
+          <t>Contrato: DM-9453530/2025
+Empresa: PAVIDEZ ENGENHARIA LTDA
+Objeto: Recuperação Funcional do Pavimento na Rodovia AMG-1615, no trecho Cristais - Entrº MGC-369, extensão de 11,70 km.</t>
         </is>
       </c>
       <c r="R269" t="inlineStr"/>
@@ -38507,17 +38507,17 @@
       <c r="AF269" t="inlineStr"/>
       <c r="AG269" t="inlineStr"/>
       <c r="AH269" s="2" t="n">
-        <v>45818</v>
+        <v>45722</v>
       </c>
       <c r="AI269" s="2" t="n">
-        <v>45824</v>
+        <v>45724</v>
       </c>
       <c r="AJ269" s="2" t="n">
-        <v>46736</v>
+        <v>46453</v>
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL269" t="inlineStr">
@@ -38532,22 +38532,22 @@
       </c>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618446</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195517</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=193984</t>
         </is>
       </c>
       <c r="AP269" t="n">
-        <v>9147934.25</v>
+        <v>7109673.15</v>
       </c>
       <c r="AQ269" t="n">
-        <v>3415320.91</v>
+        <v>4452559.37</v>
       </c>
       <c r="AR269" t="n">
-        <v>1913570.49</v>
+        <v>4309693.56</v>
       </c>
     </row>
     <row r="270">
@@ -38569,27 +38569,27 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>44.578.594/0001-98</t>
+          <t>10.417.566/0001-77</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>RAUTAKI TECNOLOGIA LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -38599,17 +38599,17 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -38624,12 +38624,12 @@
       </c>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações.</t>
+          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 2: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 07ª URG ¿ Araxá, 11ª URG ¿ Uberlândia, 14ª URG - Patos de Minas, 18ª URG - Monte Carmelo, 25ª URG - Uberaba, 26ª URG ¿ Paracatu, 31ª URG ¿ Ituiutaba, 39ª URG - João Pinheiro</t>
         </is>
       </c>
       <c r="R270" t="inlineStr"/>
@@ -38649,17 +38649,17 @@
       <c r="AF270" t="inlineStr"/>
       <c r="AG270" t="inlineStr"/>
       <c r="AH270" s="2" t="n">
-        <v>45965</v>
+        <v>45818</v>
       </c>
       <c r="AI270" s="2" t="n">
-        <v>45967</v>
+        <v>45824</v>
       </c>
       <c r="AJ270" s="2" t="n">
-        <v>47062</v>
+        <v>46736</v>
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL270" t="inlineStr">
@@ -38674,22 +38674,22 @@
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199359</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195517</t>
         </is>
       </c>
       <c r="AP270" t="n">
-        <v>23434999.8</v>
+        <v>9147934.25</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1396977.52</v>
+        <v>3415320.91</v>
       </c>
       <c r="AR270" t="n">
-        <v>243707.59</v>
+        <v>1913570.49</v>
       </c>
     </row>
     <row r="271">
@@ -38711,27 +38711,27 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>04.208.867/0001-98</t>
+          <t>44.578.594/0001-98</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -38741,17 +38741,17 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>9469794</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -38766,12 +38766,12 @@
       </c>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 4: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 5ª URG - Ubá, 17ª URG - Ponte Nova, 21ª URG ¿ Jequitinhonha, 23ª URG - Gov. Valadares, 27ª URG - Pedra Azul, 28ª URG - Teófilo Otoni, 29ª URG ¿ Manhumirim, 40ª URG - Cel. Fabriciano</t>
+          <t>Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações.</t>
         </is>
       </c>
       <c r="R271" t="inlineStr"/>
@@ -38791,17 +38791,17 @@
       <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="inlineStr"/>
       <c r="AH271" s="2" t="n">
-        <v>45820</v>
+        <v>45965</v>
       </c>
       <c r="AI271" s="2" t="n">
-        <v>45824</v>
+        <v>45967</v>
       </c>
       <c r="AJ271" s="2" t="n">
-        <v>46736</v>
+        <v>47062</v>
       </c>
       <c r="AK271" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL271" t="inlineStr">
@@ -38816,22 +38816,22 @@
       </c>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
         </is>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195609</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199359</t>
         </is>
       </c>
       <c r="AP271" t="n">
-        <v>9284408.859999999</v>
+        <v>23434999.8</v>
       </c>
       <c r="AQ271" t="n">
-        <v>3186565.34</v>
+        <v>1396977.52</v>
       </c>
       <c r="AR271" t="n">
-        <v>1933519.48</v>
+        <v>243707.59</v>
       </c>
     </row>
     <row r="272">
@@ -38853,27 +38853,27 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>16.502.551/0001-93</t>
+          <t>04.208.867/0001-98</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>RTA ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -38883,17 +38883,17 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9469794</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -38908,17 +38908,12 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
-apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
-detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
-equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 01ª, 03ª, 16ª, 20ª e 35ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
+          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 4: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 5ª URG - Ubá, 17ª URG - Ponte Nova, 21ª URG ¿ Jequitinhonha, 23ª URG - Gov. Valadares, 27ª URG - Pedra Azul, 28ª URG - Teófilo Otoni, 29ª URG ¿ Manhumirim, 40ª URG - Cel. Fabriciano</t>
         </is>
       </c>
       <c r="R272" t="inlineStr"/>
@@ -38938,17 +38933,17 @@
       <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="inlineStr"/>
       <c r="AH272" s="2" t="n">
-        <v>45974</v>
+        <v>45820</v>
       </c>
       <c r="AI272" s="2" t="n">
-        <v>45975</v>
+        <v>45824</v>
       </c>
       <c r="AJ272" s="2" t="n">
-        <v>47070</v>
+        <v>46736</v>
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL272" t="inlineStr">
@@ -38963,22 +38958,22 @@
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199380</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195609</t>
         </is>
       </c>
       <c r="AP272" t="n">
-        <v>77898894.3</v>
+        <v>9284408.859999999</v>
       </c>
       <c r="AQ272" t="n">
-        <v>563974</v>
+        <v>3186565.34</v>
       </c>
       <c r="AR272" t="n">
-        <v>86680.78999999999</v>
+        <v>1933519.48</v>
       </c>
     </row>
     <row r="273">
@@ -39040,7 +39035,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DO009482014/2025</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -39060,11 +39055,11 @@
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
-apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
-detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
-administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
-prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
+apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
+detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
 equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 01ª, 03ª, 16ª, 20ª e 35ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
@@ -39147,27 +39142,27 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>38.743.357/0001-32</t>
+          <t>16.502.551/0001-93</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>STRATA ENGENHARIA LTDA</t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -39177,17 +39172,17 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -39202,12 +39197,17 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Serviço</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 3: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 06ª URG - Montes Claros, 13ª URG - Brasília de Minas, 22ª URG ¿ Araçuaí, 32ª URG ¿ Janaúba, 33ª URG ¿ Pirapora, 34ª URG ¿ Salinas, 36ª URG ¿ Arinos e 37ª URG ¿ Januária.</t>
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para
+apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para
+detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio
+administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 1: Contratação de empresa para a
+prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
+equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 01ª, 03ª, 16ª, 20ª e 35ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
       <c r="R274" t="inlineStr"/>
@@ -39227,17 +39227,17 @@
       <c r="AF274" t="inlineStr"/>
       <c r="AG274" t="inlineStr"/>
       <c r="AH274" s="2" t="n">
-        <v>45820</v>
+        <v>45974</v>
       </c>
       <c r="AI274" s="2" t="n">
-        <v>45824</v>
+        <v>45975</v>
       </c>
       <c r="AJ274" s="2" t="n">
-        <v>46736</v>
+        <v>47070</v>
       </c>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 14.133/21</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL274" t="inlineStr">
@@ -39252,22 +39252,22 @@
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195450</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199380</t>
         </is>
       </c>
       <c r="AP274" t="n">
-        <v>9218472.49</v>
+        <v>77898894.3</v>
       </c>
       <c r="AQ274" t="n">
-        <v>2770281.03</v>
+        <v>563974</v>
       </c>
       <c r="AR274" t="n">
-        <v>1293856</v>
+        <v>86680.78999999999</v>
       </c>
     </row>
     <row r="275">
@@ -39289,27 +39289,27 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>52.635.422/0003-07</t>
+          <t>38.743.357/0001-32</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
+          <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -39324,12 +39324,12 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>9468567</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>AEST-9468567/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -39349,8 +39349,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 5: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 01ª URG - Belo Horizonte, 02ª URG ¿
-Guanhães, 03ª URG - Pará de Minas, 08ª URG ¿ Diamantina, 09ª URG - Curvelo, 12ª URG ¿ Itabira, 35ª URG ¿ Abaeté e 38ª URG ¿ Capelinha.</t>
+          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 3: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 06ª URG - Montes Claros, 13ª URG - Brasília de Minas, 22ª URG ¿ Araçuaí, 32ª URG ¿ Janaúba, 33ª URG ¿ Pirapora, 34ª URG ¿ Salinas, 36ª URG ¿ Arinos e 37ª URG ¿ Januária.</t>
         </is>
       </c>
       <c r="R275" t="inlineStr"/>
@@ -39370,7 +39369,7 @@
       <c r="AF275" t="inlineStr"/>
       <c r="AG275" t="inlineStr"/>
       <c r="AH275" s="2" t="n">
-        <v>45818</v>
+        <v>45820</v>
       </c>
       <c r="AI275" s="2" t="n">
         <v>45824</v>
@@ -39400,17 +39399,17 @@
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195462</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195450</t>
         </is>
       </c>
       <c r="AP275" t="n">
-        <v>9200787.869999999</v>
+        <v>9218472.49</v>
       </c>
       <c r="AQ275" t="n">
-        <v>3060612.65</v>
+        <v>2770281.03</v>
       </c>
       <c r="AR275" t="n">
-        <v>1441719.91</v>
+        <v>1293856</v>
       </c>
     </row>
     <row r="276">
@@ -39432,27 +39431,27 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>15.773.416/0001-10</t>
+          <t>52.635.422/0003-07</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>TALENTECH - TECNOLOGIA LTDA</t>
+          <t>SYSTRA ENGENHARIA E CONSULTORIA LTDA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -39462,17 +39461,17 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9468567</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>AEST-9468567/2025</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -39487,13 +39486,13 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Serviço</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 6: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
-equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 05ª, 12ª, 17ª, 29ª e 40ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
+          <t>Contratação de serviços técnicos especializados de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias sob a jurisdição do Departamento de Estradas de Rodagem do Estado de Minas Gerais - DER-MG, divididos em 5 (cinco) lotes: LOTE 5: Contratação de consultoria técnica para levantamentos e avaliações de serviços de engenharia rodoviária nas rodovias do DER-MG, que serão executados na malha rodoviária estadual sob responsabilidade das seguintes Unidades Regionais (URGs) do DER-MG: 01ª URG - Belo Horizonte, 02ª URG ¿
+Guanhães, 03ª URG - Pará de Minas, 08ª URG ¿ Diamantina, 09ª URG - Curvelo, 12ª URG ¿ Itabira, 35ª URG ¿ Abaeté e 38ª URG ¿ Capelinha.</t>
         </is>
       </c>
       <c r="R276" t="inlineStr"/>
@@ -39513,17 +39512,17 @@
       <c r="AF276" t="inlineStr"/>
       <c r="AG276" t="inlineStr"/>
       <c r="AH276" s="2" t="n">
-        <v>45986</v>
+        <v>45818</v>
       </c>
       <c r="AI276" s="2" t="n">
-        <v>45988</v>
+        <v>45824</v>
       </c>
       <c r="AJ276" s="2" t="n">
-        <v>47083</v>
+        <v>46736</v>
       </c>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
+          <t>Bens e serviços - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr">
@@ -39538,22 +39537,22 @@
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=619812</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199384</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=195462</t>
         </is>
       </c>
       <c r="AP276" t="n">
-        <v>35989998.13</v>
+        <v>9200787.869999999</v>
       </c>
       <c r="AQ276" t="n">
-        <v>657822</v>
+        <v>3060612.65</v>
       </c>
       <c r="AR276" t="n">
-        <v>0</v>
+        <v>1441719.91</v>
       </c>
     </row>
     <row r="277">
@@ -39575,27 +39574,27 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>18.742.098/0001-18</t>
+          <t>15.773.416/0001-10</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
+          <t>TALENTECH - TECNOLOGIA LTDA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -39605,17 +39604,17 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -39630,12 +39629,13 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>Recuperação da Ponte sobre o Rio Jequitinhonha, no trecho Diamantina - Couto Magalhães de Minas.</t>
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 6: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos
+equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 05ª, 12ª, 17ª, 29ª e 40ª URGs do DERMG. Incluso no PPAG, conforme condições, quantidades e exigências estabelecidas no Edital e seus anexos.</t>
         </is>
       </c>
       <c r="R277" t="inlineStr"/>
@@ -39655,13 +39655,13 @@
       <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="inlineStr"/>
       <c r="AH277" s="2" t="n">
-        <v>45845</v>
+        <v>45986</v>
       </c>
       <c r="AI277" s="2" t="n">
-        <v>45847</v>
+        <v>45988</v>
       </c>
       <c r="AJ277" s="2" t="n">
-        <v>46297</v>
+        <v>47083</v>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
@@ -39680,22 +39680,22 @@
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=622061</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196541</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=199384</t>
         </is>
       </c>
       <c r="AP277" t="n">
-        <v>9767508.470000001</v>
+        <v>35989998.13</v>
       </c>
       <c r="AQ277" t="n">
-        <v>9767507.859999999</v>
+        <v>657822</v>
       </c>
       <c r="AR277" t="n">
-        <v>3360025.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -39747,17 +39747,17 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -39777,7 +39777,7 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Implantação da Ponte sobre o Rio Casca na Rodovia AMG-1715, trecho Entrº MG-329 - Santo Antônio do Grama, com extensão de 80,000 m</t>
+          <t>Recuperação da Ponte sobre o Rio Jequitinhonha, no trecho Diamantina - Couto Magalhães de Minas.</t>
         </is>
       </c>
       <c r="R278" t="inlineStr"/>
@@ -39797,13 +39797,13 @@
       <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="inlineStr"/>
       <c r="AH278" s="2" t="n">
-        <v>45874</v>
+        <v>45845</v>
       </c>
       <c r="AI278" s="2" t="n">
-        <v>45875</v>
+        <v>45847</v>
       </c>
       <c r="AJ278" s="2" t="n">
-        <v>46235</v>
+        <v>46297</v>
       </c>
       <c r="AK278" t="inlineStr">
         <is>
@@ -39822,22 +39822,22 @@
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624152</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=622061</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197289</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=196541</t>
         </is>
       </c>
       <c r="AP278" t="n">
-        <v>6023620.36</v>
+        <v>9767508.470000001</v>
       </c>
       <c r="AQ278" t="n">
-        <v>6023619.44</v>
+        <v>9767507.859999999</v>
       </c>
       <c r="AR278" t="n">
-        <v>4024250.43</v>
+        <v>3972729.7</v>
       </c>
     </row>
     <row r="279">
@@ -39845,11 +39845,11 @@
         <v>2025</v>
       </c>
       <c r="B279" t="n">
-        <v>2470</v>
+        <v>2300</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE TRANSPORTES</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -39859,27 +39859,27 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>17.210.063/0001-75</t>
+          <t>18.742.098/0001-18</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
+          <t>TRENA - TERRAPLENAGEM E CONSTRUCOES S.A.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -39889,17 +39889,17 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>1301017 000043/2024</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>9473911</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>9473911/2024</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -39919,8 +39919,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão Geral, Monitoramento dos Parâmetros de Desempenho, Avaliação e Análise de Projetos, da exploração mediante Concessão, dos trechos rodoviários abaixo descritos, conforme especificações, exigências e quantidades estabelecidas.
-BR-135: Concessão OUTORGADA, com 374,95 km.</t>
+          <t xml:space="preserve"> Implantação da Ponte sobre o Rio Casca na Rodovia AMG-1715, trecho Entrº MG-329 - Santo Antônio do Grama, com extensão de 80,000 m</t>
         </is>
       </c>
       <c r="R279" t="inlineStr"/>
@@ -39940,13 +39939,13 @@
       <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="inlineStr"/>
       <c r="AH279" s="2" t="n">
-        <v>45890</v>
+        <v>45874</v>
       </c>
       <c r="AI279" s="2" t="n">
-        <v>45894</v>
+        <v>45875</v>
       </c>
       <c r="AJ279" s="2" t="n">
-        <v>46623</v>
+        <v>46235</v>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
@@ -39960,39 +39959,39 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência presencial</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618571</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624152</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197236</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197289</t>
         </is>
       </c>
       <c r="AP279" t="n">
-        <v>5206233.96</v>
+        <v>6023620.36</v>
       </c>
       <c r="AQ279" t="n">
-        <v>2723540.44</v>
+        <v>6023619.44</v>
       </c>
       <c r="AR279" t="n">
-        <v>1923540.42</v>
+        <v>4693572.9</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B280" t="n">
-        <v>2300</v>
+        <v>2470</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM</t>
+          <t>AGENCIA REGULADORA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -40002,27 +40001,27 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>10.957.855/0001-69</t>
+          <t>17.210.063/0001-75</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>AGR BOTELHO ENGENHARIA LTDA</t>
+          <t>CONSOL - ENGENHEIROS CONSULTORES LTDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -40032,17 +40031,17 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>1301017 000043/2024</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9473911</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>9473911/2024</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -40062,9 +40061,8 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Contrato: DM-9493202/2026
-Empresa: AGR Botelho Engenharia Ltda
-Objeto: Recuperação de erosões na MG-406, Km 118,9/120,9/123/123,3/132,4, trecho: Palmópolis - Rio do Prado e Estabilização de aterro de encabeçamento de ponte na MG-205, ponte sobre o Ribeirão José Ferreira.</t>
+          <t>Contratação de natureza continuada na modalidade empreitada por preços unitários dos serviços de Supervisão Geral, Monitoramento dos Parâmetros de Desempenho, Avaliação e Análise de Projetos, da exploração mediante Concessão, dos trechos rodoviários abaixo descritos, conforme especificações, exigências e quantidades estabelecidas.
+BR-135: Concessão OUTORGADA, com 374,95 km.</t>
         </is>
       </c>
       <c r="R280" t="inlineStr"/>
@@ -40084,13 +40082,13 @@
       <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="inlineStr"/>
       <c r="AH280" s="2" t="n">
-        <v>46050</v>
+        <v>45890</v>
       </c>
       <c r="AI280" s="2" t="n">
-        <v>46058</v>
+        <v>45894</v>
       </c>
       <c r="AJ280" s="2" t="n">
-        <v>46665</v>
+        <v>46623</v>
       </c>
       <c r="AK280" t="inlineStr">
         <is>
@@ -40104,27 +40102,27 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>Concorrência - Concorrência presencial</t>
         </is>
       </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=638599</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=618571</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208757</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=197236</t>
         </is>
       </c>
       <c r="AP280" t="n">
-        <v>4557819.64</v>
+        <v>5206233.96</v>
       </c>
       <c r="AQ280" t="n">
-        <v>0</v>
+        <v>2723540.44</v>
       </c>
       <c r="AR280" t="n">
-        <v>0</v>
+        <v>2204976.09</v>
       </c>
     </row>
     <row r="281">
@@ -40146,27 +40144,27 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>17.311.358/0001-38</t>
+          <t>10.957.855/0001-69</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>CONSTRUTORA SAGENDRA LTDA</t>
+          <t>AGR BOTELHO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -40176,17 +40174,17 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -40206,9 +40204,9 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>CONTRATO: DM-9493180/2026
-EMPRESA: Construtora Sagendra Ltda
-OBJETO: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 17ª Unidade Regional Ponte Nova, do DER-MG.</t>
+          <t>Contrato: DM-9493202/2026
+Empresa: AGR Botelho Engenharia Ltda
+Objeto: Recuperação de erosões na MG-406, Km 118,9/120,9/123/123,3/132,4, trecho: Palmópolis - Rio do Prado e Estabilização de aterro de encabeçamento de ponte na MG-205, ponte sobre o Ribeirão José Ferreira.</t>
         </is>
       </c>
       <c r="R281" t="inlineStr"/>
@@ -40228,13 +40226,13 @@
       <c r="AF281" t="inlineStr"/>
       <c r="AG281" t="inlineStr"/>
       <c r="AH281" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="AI281" s="2" t="n">
-        <v>46044</v>
+        <v>46058</v>
       </c>
       <c r="AJ281" s="2" t="n">
-        <v>47139</v>
+        <v>46665</v>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
@@ -40253,22 +40251,22 @@
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=638599</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208457</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208757</t>
         </is>
       </c>
       <c r="AP281" t="n">
-        <v>64984305.34</v>
+        <v>4557819.64</v>
       </c>
       <c r="AQ281" t="n">
-        <v>16467076</v>
+        <v>100000</v>
       </c>
       <c r="AR281" t="n">
-        <v>4492931.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -40290,27 +40288,27 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>09.072.082/0001-54</t>
+          <t>17.311.358/0001-38</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -40320,17 +40318,17 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -40345,13 +40343,14 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Serviço e Fornecimento</t>
+          <t>Obra</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 4: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 06ª, 09ª, 13ª, 32ª, 33ª, 36ª, 37ª e 39ª
-URGs do DER-MG. Incluso no PPAG.</t>
+          <t>CONTRATO: DM-9493180/2026
+EMPRESA: Construtora Sagendra Ltda
+OBJETO: Execução dos serviços de manutenção rodoviária, conservação rotineira e periódica, serviços de urgência e pequenos melhoramentos, bem como reparações do corpo estradal e seus dispositivos. A execução dos serviços descritos está restrita ao âmbito de circunscrição da 17ª Unidade Regional Ponte Nova, do DER-MG.</t>
         </is>
       </c>
       <c r="R282" t="inlineStr"/>
@@ -40371,13 +40370,13 @@
       <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="inlineStr"/>
       <c r="AH282" s="2" t="n">
-        <v>46051</v>
+        <v>46042</v>
       </c>
       <c r="AI282" s="2" t="n">
-        <v>46056</v>
+        <v>46044</v>
       </c>
       <c r="AJ282" s="2" t="n">
-        <v>47151</v>
+        <v>47139</v>
       </c>
       <c r="AK282" t="inlineStr">
         <is>
@@ -40396,22 +40395,22 @@
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=621402</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208797</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208457</t>
         </is>
       </c>
       <c r="AP282" t="n">
-        <v>31699998.96</v>
+        <v>64984305.34</v>
       </c>
       <c r="AQ282" t="n">
-        <v>607981</v>
+        <v>31324521.83</v>
       </c>
       <c r="AR282" t="n">
-        <v>0</v>
+        <v>6401838.79</v>
       </c>
     </row>
     <row r="283">
@@ -40433,27 +40432,27 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>19.256.565/0001-62</t>
+          <t>09.072.082/0001-54</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>HWN ENGENHARIA LTDA</t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -40463,17 +40462,17 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -40488,12 +40487,13 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Obra</t>
+          <t>Serviço e Fornecimento</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Execução da Interseção para Patrocínio - Trevo de Enxó, Km 105, no trecho Entrº MG-187 - Entrº BR-365, na Rodovia MG-230</t>
+          <t>O objeto do presente instrumento é a Prestação de serviços especiais de natureza contínua para apoio ao DER-MG no gerenciamento de trânsito e fiscalização eletrônica com a disponibilização de recursos para detecção, a medição, o registro, o processamento de imagens para notificações de infrações de trânsito e o apoio administrativo nos recursos de infrações, distribuído em 7 (sete) lotes: Lote 4: Contratação de empresa para a prestação de serviços de instalação, sinalização, aferição, operação, monitoramento e manutenção dos equipamentos fixos de fiscalização eletrônica abrangendo os trechos das 06ª, 09ª, 13ª, 32ª, 33ª, 36ª, 37ª e 39ª
+URGs do DER-MG. Incluso no PPAG.</t>
         </is>
       </c>
       <c r="R283" t="inlineStr"/>
@@ -40513,13 +40513,13 @@
       <c r="AF283" t="inlineStr"/>
       <c r="AG283" t="inlineStr"/>
       <c r="AH283" s="2" t="n">
-        <v>46063</v>
+        <v>46051</v>
       </c>
       <c r="AI283" s="2" t="n">
-        <v>46098</v>
+        <v>46056</v>
       </c>
       <c r="AJ283" s="2" t="n">
-        <v>46638</v>
+        <v>47151</v>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
@@ -40528,25 +40528,29 @@
       </c>
       <c r="AL283" t="inlineStr">
         <is>
-          <t>Inexigibilidade</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>Inexigibilidade - Outros motivos</t>
-        </is>
-      </c>
-      <c r="AN283" t="inlineStr"/>
+          <t>Concorrência - Concorrência eletrônica</t>
+        </is>
+      </c>
+      <c r="AN283" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=624190</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=213945</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=208797</t>
         </is>
       </c>
       <c r="AP283" t="n">
-        <v>2962697.76</v>
+        <v>31699998.96</v>
       </c>
       <c r="AQ283" t="n">
-        <v>2962697.73</v>
+        <v>607981</v>
       </c>
       <c r="AR283" t="n">
         <v>0</v>
@@ -40571,27 +40575,27 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>08.156.424/0001-51</t>
+          <t>19.256.565/0001-62</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>MAIA MELO ENGENHARIA LTDA</t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -40601,17 +40605,17 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -40631,7 +40635,7 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>Apoio à supervisão de obras rodoviárias no trecho Entr. MGC-135 (Manga) - Porto de Matias Cardoso (Construção da ponte sobre o Rio São Francisco e Variante de acesso à ponte).</t>
+          <t>Execução da Interseção para Patrocínio - Trevo de Enxó, Km 105, no trecho Entrº MG-187 - Entrº BR-365, na Rodovia MG-230</t>
         </is>
       </c>
       <c r="R284" t="inlineStr"/>
@@ -40651,13 +40655,13 @@
       <c r="AF284" t="inlineStr"/>
       <c r="AG284" t="inlineStr"/>
       <c r="AH284" s="2" t="n">
-        <v>46038</v>
+        <v>46063</v>
       </c>
       <c r="AI284" s="2" t="n">
-        <v>46042</v>
+        <v>46098</v>
       </c>
       <c r="AJ284" s="2" t="n">
-        <v>46942</v>
+        <v>46638</v>
       </c>
       <c r="AK284" t="inlineStr">
         <is>
@@ -40666,32 +40670,28 @@
       </c>
       <c r="AL284" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Inexigibilidade</t>
         </is>
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
-        </is>
-      </c>
-      <c r="AN284" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=632739</t>
-        </is>
-      </c>
+          <t>Inexigibilidade - Outros motivos</t>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr"/>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=207737</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=213945</t>
         </is>
       </c>
       <c r="AP284" t="n">
-        <v>6677404.33</v>
+        <v>2962697.76</v>
       </c>
       <c r="AQ284" t="n">
-        <v>3200000</v>
+        <v>2962697.73</v>
       </c>
       <c r="AR284" t="n">
-        <v>485632.24</v>
+        <v>147857.48</v>
       </c>
     </row>
     <row r="285">
@@ -40743,17 +40743,17 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -40773,9 +40773,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apoio a Supervisão de Obras Rodoviárias da Rodovia MG402, da Complementação
-da Construção da Ponte sobre o Rio São Francisco, dimensões 1.120,00x13,80 m, no trecho São Francisco Pintópolis, e Complementação das obras de Melhoramento e Pavimentação de Variante de acesso à Ponte sobre o Rio São Francisco, com 3,06 km, no trecho São Francisco Pintópolis.
-</t>
+          <t>Apoio à supervisão de obras rodoviárias no trecho Entr. MGC-135 (Manga) - Porto de Matias Cardoso (Construção da ponte sobre o Rio São Francisco e Variante de acesso à ponte).</t>
         </is>
       </c>
       <c r="R285" t="inlineStr"/>
@@ -40801,7 +40799,7 @@
         <v>46042</v>
       </c>
       <c r="AJ285" s="2" t="n">
-        <v>46552</v>
+        <v>46942</v>
       </c>
       <c r="AK285" t="inlineStr">
         <is>
@@ -40820,22 +40818,22 @@
       </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=632742</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=632739</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=205460</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=207737</t>
         </is>
       </c>
       <c r="AP285" t="n">
-        <v>3028048.96</v>
+        <v>6677404.33</v>
       </c>
       <c r="AQ285" t="n">
-        <v>2900000</v>
+        <v>3200000</v>
       </c>
       <c r="AR285" t="n">
-        <v>500111.18</v>
+        <v>485632.24</v>
       </c>
     </row>
     <row r="286">
@@ -40857,27 +40855,27 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>10.417.566/0001-77</t>
+          <t>08.156.424/0001-51</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
+          <t>MAIA MELO ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -40887,17 +40885,17 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -40917,9 +40915,9 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Contrato: DM-9502116/2026
-Empresa: PLANEP Planejamento e Estudos e Projetos Ltda
-Objeto: Prestação de serviços de Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional gerenciados pela Diretoria de Manutenção.</t>
+          <t xml:space="preserve"> Apoio a Supervisão de Obras Rodoviárias da Rodovia MG402, da Complementação
+da Construção da Ponte sobre o Rio São Francisco, dimensões 1.120,00x13,80 m, no trecho São Francisco Pintópolis, e Complementação das obras de Melhoramento e Pavimentação de Variante de acesso à Ponte sobre o Rio São Francisco, com 3,06 km, no trecho São Francisco Pintópolis.
+</t>
         </is>
       </c>
       <c r="R286" t="inlineStr"/>
@@ -40939,13 +40937,13 @@
       <c r="AF286" t="inlineStr"/>
       <c r="AG286" t="inlineStr"/>
       <c r="AH286" s="2" t="n">
-        <v>46125</v>
+        <v>46038</v>
       </c>
       <c r="AI286" s="2" t="n">
-        <v>46128</v>
+        <v>46042</v>
       </c>
       <c r="AJ286" s="2" t="n">
-        <v>46858</v>
+        <v>46552</v>
       </c>
       <c r="AK286" t="inlineStr">
         <is>
@@ -40964,28 +40962,36 @@
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=639929</t>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=632742</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=216897</t>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=205460</t>
         </is>
       </c>
       <c r="AP286" t="n">
-        <v>5342582.88</v>
+        <v>3028048.96</v>
       </c>
       <c r="AQ286" t="n">
-        <v>500000</v>
+        <v>2900000</v>
       </c>
       <c r="AR286" t="n">
-        <v>112220.23</v>
+        <v>500111.18</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="inlineStr"/>
+      <c r="A287" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -40993,27 +40999,27 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>18.258.450/0001-44</t>
+          <t>10.417.566/0001-77</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
+          <t>PLANEP PLANEJAMENTO ESTUDOS E PROJETOS LTDA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -41023,25 +41029,39 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M287" t="inlineStr"/>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr"/>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>Vigente publicado</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Obra</t>
+        </is>
+      </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>Contrato: DM-9502116/2026
+Empresa: PLANEP Planejamento e Estudos e Projetos Ltda
+Objeto: Prestação de serviços de Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional gerenciados pela Diretoria de Manutenção.</t>
         </is>
       </c>
       <c r="R287" t="inlineStr"/>
@@ -41061,35 +41081,47 @@
       <c r="AF287" t="inlineStr"/>
       <c r="AG287" t="inlineStr"/>
       <c r="AH287" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI287" t="inlineStr"/>
-      <c r="AJ287" t="inlineStr"/>
+        <v>46125</v>
+      </c>
+      <c r="AI287" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AJ287" s="2" t="n">
+        <v>46858</v>
+      </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
+          <t>Obras e serviços de engenharia - Lei nº 14.133/21</t>
         </is>
       </c>
       <c r="AL287" t="inlineStr">
         <is>
-          <t>Registro de preços não realizado no SIRP</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>Registro de preços não realizado no SIRP</t>
-        </is>
-      </c>
-      <c r="AN287" t="inlineStr"/>
-      <c r="AO287" t="inlineStr"/>
+          <t>Concorrência - Concorrência eletrônica</t>
+        </is>
+      </c>
+      <c r="AN287" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=639929</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/contrato/gestaocontratos/arquivosContrato.html?idContrato=216897</t>
+        </is>
+      </c>
       <c r="AP287" t="n">
-        <v>540000</v>
+        <v>5342582.88</v>
       </c>
       <c r="AQ287" t="n">
-        <v>120351.39</v>
+        <v>500000</v>
       </c>
       <c r="AR287" t="n">
-        <v>120351.39</v>
+        <v>112220.23</v>
       </c>
     </row>
     <row r="288">
@@ -41103,27 +41135,27 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>25.955.246/0001-48</t>
+          <t>18.258.450/0001-44</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>IPE ENGENHARIA LTDA</t>
+          <t>GESTAO ENGENHARIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -41133,7 +41165,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2301520 000001/2021</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -41142,7 +41174,11 @@
         </is>
       </c>
       <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr"/>
       <c r="Q288" t="inlineStr">
@@ -41173,33 +41209,29 @@
       <c r="AJ288" t="inlineStr"/>
       <c r="AK288" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
         </is>
       </c>
       <c r="AL288" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Registro de preços não realizado no SIRP</t>
         </is>
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>Concorrência</t>
-        </is>
-      </c>
-      <c r="AN288" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=517509</t>
-        </is>
-      </c>
+          <t>Registro de preços não realizado no SIRP</t>
+        </is>
+      </c>
+      <c r="AN288" t="inlineStr"/>
       <c r="AO288" t="inlineStr"/>
       <c r="AP288" t="n">
-        <v>12796116.03</v>
+        <v>540000</v>
       </c>
       <c r="AQ288" t="n">
-        <v>0</v>
+        <v>120351.39</v>
       </c>
       <c r="AR288" t="n">
-        <v>0</v>
+        <v>120351.39</v>
       </c>
     </row>
     <row r="289">
@@ -41213,27 +41245,27 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>24.031.830/0001-44</t>
+          <t>25.955.246/0001-48</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
+          <t>IPE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -41243,7 +41275,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2301601 000001/2023</t>
+          <t>2301520 000001/2021</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -41252,11 +41284,7 @@
         </is>
       </c>
       <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
+      <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr"/>
       <c r="Q289" t="inlineStr">
@@ -41287,29 +41315,33 @@
       <c r="AJ289" t="inlineStr"/>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
         </is>
       </c>
       <c r="AL289" t="inlineStr">
         <is>
-          <t>Registro de preços não realizado no SIRP</t>
+          <t>Concorrência</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>Registro de preços não realizado no SIRP</t>
-        </is>
-      </c>
-      <c r="AN289" t="inlineStr"/>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="AN289" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=517509</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr"/>
       <c r="AP289" t="n">
-        <v>963997</v>
+        <v>12796116.03</v>
       </c>
       <c r="AQ289" t="n">
-        <v>294114.73</v>
+        <v>0</v>
       </c>
       <c r="AR289" t="n">
-        <v>294114.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -41323,27 +41355,27 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>33.548.452/0001-61</t>
+          <t>24.031.830/0001-44</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
+          <t>KALU SERVICOS DE ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -41413,13 +41445,13 @@
       <c r="AN290" t="inlineStr"/>
       <c r="AO290" t="inlineStr"/>
       <c r="AP290" t="n">
-        <v>386990</v>
+        <v>963997</v>
       </c>
       <c r="AQ290" t="n">
-        <v>305894</v>
+        <v>294114.73</v>
       </c>
       <c r="AR290" t="n">
-        <v>305894</v>
+        <v>294114.73</v>
       </c>
     </row>
     <row r="291">
@@ -41433,27 +41465,27 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>09.491.927/0001-46</t>
+          <t>33.548.452/0001-61</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+          <t>PROSEO ESTUDOS &amp; PROJETOS LTDA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -41523,45 +41555,57 @@
       <c r="AN291" t="inlineStr"/>
       <c r="AO291" t="inlineStr"/>
       <c r="AP291" t="n">
-        <v>950900</v>
+        <v>386990</v>
       </c>
       <c r="AQ291" t="n">
-        <v>70885.22</v>
+        <v>305894</v>
       </c>
       <c r="AR291" t="n">
-        <v>70885.22</v>
+        <v>305894</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr"/>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>09.491.927/0001-46</t>
+        </is>
+      </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>INEXISTENTE</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr"/>
+          <t>SURFACE ENGENHARIA E TOPOGRAFIA LTDA</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>PESSOA JURÍDICA</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2301520 000001/2020</t>
+          <t>2301601 000001/2023</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -41570,7 +41614,11 @@
         </is>
       </c>
       <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr"/>
       <c r="Q292" t="inlineStr">
@@ -41601,32 +41649,126 @@
       <c r="AJ292" t="inlineStr"/>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+          <t>Bens e serviços - Lei nº 8.666/93 ou 10.520/02</t>
         </is>
       </c>
       <c r="AL292" t="inlineStr">
         <is>
-          <t>Concorrência</t>
+          <t>Registro de preços não realizado no SIRP</t>
         </is>
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>Concorrência</t>
-        </is>
-      </c>
-      <c r="AN292" t="inlineStr">
-        <is>
-          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=494581</t>
-        </is>
-      </c>
+          <t>Registro de preços não realizado no SIRP</t>
+        </is>
+      </c>
+      <c r="AN292" t="inlineStr"/>
       <c r="AO292" t="inlineStr"/>
       <c r="AP292" t="n">
+        <v>950900</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>70885.22</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>70885.22</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>2301520 000001/2020</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>INEXISTENTE</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="inlineStr"/>
+      <c r="T293" t="inlineStr"/>
+      <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr"/>
+      <c r="W293" t="inlineStr"/>
+      <c r="X293" t="inlineStr"/>
+      <c r="Y293" t="inlineStr"/>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
+      <c r="AB293" t="inlineStr"/>
+      <c r="AC293" t="inlineStr"/>
+      <c r="AD293" t="inlineStr"/>
+      <c r="AE293" t="inlineStr"/>
+      <c r="AF293" t="inlineStr"/>
+      <c r="AG293" t="inlineStr"/>
+      <c r="AH293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI293" t="inlineStr"/>
+      <c r="AJ293" t="inlineStr"/>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Obras e serviços de engenharia - Lei nº 8.666/93</t>
+        </is>
+      </c>
+      <c r="AL293" t="inlineStr">
+        <is>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>Concorrência</t>
+        </is>
+      </c>
+      <c r="AN293" t="inlineStr">
+        <is>
+          <t>https://www1.compras.mg.gov.br/processocompra/processo/consultaEditalRetificaoProcesso.html?metodo=visualizarEditalRetificao&amp;id=494581</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr"/>
+      <c r="AP293" t="n">
         <v>0</v>
       </c>
-      <c r="AQ292" t="n">
+      <c r="AQ293" t="n">
         <v>0</v>
       </c>
-      <c r="AR292" t="n">
+      <c r="AR293" t="n">
         <v>0</v>
       </c>
     </row>
